--- a/hall/resources/sample/BuildingEquipmentTable.xlsx
+++ b/hall/resources/sample/BuildingEquipmentTable.xlsx
@@ -55,12 +55,56 @@
         </r>
       </text>
     </comment>
+    <comment ref="A82" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Administrator:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+没有该物品，废弃编号</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="A470" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Administrator:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+没有该物品，废弃编号</t>
+        </r>
+      </text>
+    </comment>
   </commentList>
 </comments>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1068" uniqueCount="126">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1070" uniqueCount="127">
   <si>
     <t>ID</t>
   </si>
@@ -380,6 +424,9 @@
     <t>装饰物47</t>
   </si>
   <si>
+    <t>装饰物48</t>
+  </si>
+  <si>
     <t>装饰1</t>
   </si>
   <si>
@@ -450,7 +497,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="24">
+  <fonts count="25">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -462,6 +509,12 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="微软雅黑"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0" tint="-0.5"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
     </font>
@@ -627,18 +680,12 @@
       <charset val="134"/>
     </font>
   </fonts>
-  <fills count="35">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="0" tint="-0.05"/>
-        <bgColor indexed="64"/>
-      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -959,16 +1006,13 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -977,119 +1021,122 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1099,19 +1146,13 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -3317,24 +3358,24 @@
         <v>59</v>
       </c>
     </row>
-    <row r="82" spans="1:6">
-      <c r="A82" s="3">
+    <row r="82" s="2" customFormat="1" spans="1:6">
+      <c r="A82" s="2">
         <f t="shared" si="3"/>
         <v>1102263</v>
       </c>
-      <c r="B82" s="3">
-        <v>2</v>
-      </c>
-      <c r="C82" s="3">
+      <c r="B82" s="2">
+        <v>2</v>
+      </c>
+      <c r="C82" s="2">
         <v>63</v>
       </c>
-      <c r="D82" s="3">
+      <c r="D82" s="2">
         <v>1102</v>
       </c>
-      <c r="E82" s="3" t="s">
+      <c r="E82" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="F82" s="3" t="s">
+      <c r="F82" s="2" t="s">
         <v>59</v>
       </c>
     </row>
@@ -4012,7 +4053,7 @@
     </row>
     <row r="115" spans="1:6">
       <c r="A115" s="5">
-        <f>D115*1000+B115*100+C115</f>
+        <f t="shared" si="3"/>
         <v>1103251</v>
       </c>
       <c r="B115" s="5">
@@ -4033,7 +4074,7 @@
     </row>
     <row r="116" spans="1:6">
       <c r="A116" s="5">
-        <f>D116*1000+B116*100+C116</f>
+        <f t="shared" si="3"/>
         <v>1103252</v>
       </c>
       <c r="B116" s="5">
@@ -4054,7 +4095,7 @@
     </row>
     <row r="117" spans="1:6">
       <c r="A117" s="5">
-        <f>D117*1000+B117*100+C117</f>
+        <f t="shared" si="3"/>
         <v>1103253</v>
       </c>
       <c r="B117" s="5">
@@ -4075,7 +4116,7 @@
     </row>
     <row r="118" spans="1:6">
       <c r="A118" s="5">
-        <f>D118*1000+B118*100+C118</f>
+        <f t="shared" si="3"/>
         <v>1103254</v>
       </c>
       <c r="B118" s="5">
@@ -4096,7 +4137,7 @@
     </row>
     <row r="119" spans="1:6">
       <c r="A119" s="5">
-        <f>D119*1000+B119*100+C119</f>
+        <f t="shared" si="3"/>
         <v>1103255</v>
       </c>
       <c r="B119" s="5">
@@ -4117,7 +4158,7 @@
     </row>
     <row r="120" spans="1:6">
       <c r="A120" s="5">
-        <f>D120*1000+B120*100+C120</f>
+        <f t="shared" si="3"/>
         <v>1103256</v>
       </c>
       <c r="B120" s="5">
@@ -4138,7 +4179,7 @@
     </row>
     <row r="121" spans="1:6">
       <c r="A121" s="5">
-        <f>D121*1000+B121*100+C121</f>
+        <f t="shared" si="3"/>
         <v>1103257</v>
       </c>
       <c r="B121" s="5">
@@ -4159,7 +4200,7 @@
     </row>
     <row r="122" spans="1:6">
       <c r="A122" s="5">
-        <f>D122*1000+B122*100+C122</f>
+        <f t="shared" si="3"/>
         <v>1103258</v>
       </c>
       <c r="B122" s="5">
@@ -4180,7 +4221,7 @@
     </row>
     <row r="123" spans="1:6">
       <c r="A123" s="5">
-        <f>D123*1000+B123*100+C123</f>
+        <f t="shared" si="3"/>
         <v>1103259</v>
       </c>
       <c r="B123" s="5">
@@ -4201,7 +4242,7 @@
     </row>
     <row r="124" spans="1:6">
       <c r="A124" s="5">
-        <f>D124*1000+B124*100+C124</f>
+        <f t="shared" si="3"/>
         <v>1103260</v>
       </c>
       <c r="B124" s="5">
@@ -4222,7 +4263,7 @@
     </row>
     <row r="125" spans="1:6">
       <c r="A125" s="5">
-        <f t="shared" ref="A125:A146" si="4">D125*1000+B125*100+C125</f>
+        <f t="shared" ref="A125:A155" si="4">D125*1000+B125*100+C125</f>
         <v>1103261</v>
       </c>
       <c r="B125" s="5">
@@ -4537,7 +4578,7 @@
     </row>
     <row r="140" spans="1:6">
       <c r="A140" s="3">
-        <f>D140*1000+B140*100+C140</f>
+        <f t="shared" si="4"/>
         <v>1104101</v>
       </c>
       <c r="B140" s="3">
@@ -4558,7 +4599,7 @@
     </row>
     <row r="141" spans="1:6">
       <c r="A141" s="3">
-        <f>D141*1000+B141*100+C141</f>
+        <f t="shared" si="4"/>
         <v>1104102</v>
       </c>
       <c r="B141" s="3">
@@ -4579,7 +4620,7 @@
     </row>
     <row r="142" spans="1:6">
       <c r="A142" s="3">
-        <f>D142*1000+B142*100+C142</f>
+        <f t="shared" si="4"/>
         <v>1104103</v>
       </c>
       <c r="B142" s="3">
@@ -4600,7 +4641,7 @@
     </row>
     <row r="143" spans="1:6">
       <c r="A143" s="3">
-        <f>D143*1000+B143*100+C143</f>
+        <f t="shared" si="4"/>
         <v>1104104</v>
       </c>
       <c r="B143" s="3">
@@ -4621,7 +4662,7 @@
     </row>
     <row r="144" spans="1:6">
       <c r="A144" s="3">
-        <f>D144*1000+B144*100+C144</f>
+        <f t="shared" si="4"/>
         <v>1104105</v>
       </c>
       <c r="B144" s="3">
@@ -4642,7 +4683,7 @@
     </row>
     <row r="145" spans="1:6">
       <c r="A145" s="3">
-        <f>D145*1000+B145*100+C145</f>
+        <f t="shared" si="4"/>
         <v>1104106</v>
       </c>
       <c r="B145" s="3">
@@ -4663,7 +4704,7 @@
     </row>
     <row r="146" spans="1:6">
       <c r="A146" s="3">
-        <f>D146*1000+B146*100+C146</f>
+        <f t="shared" si="4"/>
         <v>1104107</v>
       </c>
       <c r="B146" s="3">
@@ -4684,7 +4725,7 @@
     </row>
     <row r="147" spans="1:6">
       <c r="A147" s="3">
-        <f>D147*1000+B147*100+C147</f>
+        <f t="shared" si="4"/>
         <v>1104108</v>
       </c>
       <c r="B147" s="3">
@@ -4705,7 +4746,7 @@
     </row>
     <row r="148" spans="1:6">
       <c r="A148" s="3">
-        <f>D148*1000+B148*100+C148</f>
+        <f t="shared" si="4"/>
         <v>1104109</v>
       </c>
       <c r="B148" s="3">
@@ -4726,7 +4767,7 @@
     </row>
     <row r="149" spans="1:6">
       <c r="A149" s="3">
-        <f>D149*1000+B149*100+C149</f>
+        <f t="shared" si="4"/>
         <v>1104110</v>
       </c>
       <c r="B149" s="3">
@@ -4747,7 +4788,7 @@
     </row>
     <row r="150" spans="1:6">
       <c r="A150" s="3">
-        <f>D150*1000+B150*100+C150</f>
+        <f t="shared" si="4"/>
         <v>1104111</v>
       </c>
       <c r="B150" s="3">
@@ -4768,7 +4809,7 @@
     </row>
     <row r="151" spans="1:6">
       <c r="A151" s="3">
-        <f>D151*1000+B151*100+C151</f>
+        <f t="shared" si="4"/>
         <v>1104112</v>
       </c>
       <c r="B151" s="3">
@@ -4789,7 +4830,7 @@
     </row>
     <row r="152" spans="1:6">
       <c r="A152" s="3">
-        <f>D152*1000+B152*100+C152</f>
+        <f t="shared" si="4"/>
         <v>1104113</v>
       </c>
       <c r="B152" s="3">
@@ -4810,7 +4851,7 @@
     </row>
     <row r="153" spans="1:6">
       <c r="A153" s="3">
-        <f>D153*1000+B153*100+C153</f>
+        <f t="shared" si="4"/>
         <v>1104114</v>
       </c>
       <c r="B153" s="3">
@@ -4831,7 +4872,7 @@
     </row>
     <row r="154" spans="1:6">
       <c r="A154" s="3">
-        <f>D154*1000+B154*100+C154</f>
+        <f t="shared" si="4"/>
         <v>1104115</v>
       </c>
       <c r="B154" s="3">
@@ -4852,7 +4893,7 @@
     </row>
     <row r="155" spans="1:6">
       <c r="A155" s="3">
-        <f>D155*1000+B155*100+C155</f>
+        <f t="shared" si="4"/>
         <v>1104116</v>
       </c>
       <c r="B155" s="3">
@@ -11047,7 +11088,7 @@
     </row>
     <row r="450" spans="1:6">
       <c r="A450" s="3">
-        <f t="shared" ref="A450:A503" si="20">D450*1000+B450*100+C450</f>
+        <f t="shared" ref="A450:A504" si="20">D450*1000+B450*100+C450</f>
         <v>1202261</v>
       </c>
       <c r="B450" s="3">
@@ -11465,24 +11506,24 @@
         <v>87</v>
       </c>
     </row>
-    <row r="470" spans="1:6">
-      <c r="A470" s="3">
+    <row r="470" s="2" customFormat="1" spans="1:6">
+      <c r="A470" s="2">
         <f t="shared" si="20"/>
         <v>1202281</v>
       </c>
-      <c r="B470" s="3">
-        <v>2</v>
-      </c>
-      <c r="C470" s="3">
+      <c r="B470" s="2">
+        <v>2</v>
+      </c>
+      <c r="C470" s="2">
         <v>81</v>
       </c>
-      <c r="D470" s="3">
+      <c r="D470" s="2">
         <v>1202</v>
       </c>
-      <c r="E470" s="3" t="s">
+      <c r="E470" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="F470" s="3" t="s">
+      <c r="F470" s="2" t="s">
         <v>87</v>
       </c>
     </row>
@@ -11823,57 +11864,57 @@
       </c>
     </row>
     <row r="487" spans="1:6">
-      <c r="A487" s="5">
+      <c r="A487" s="3">
         <f t="shared" si="20"/>
-        <v>1302201</v>
-      </c>
-      <c r="B487" s="5">
-        <v>2</v>
-      </c>
-      <c r="C487" s="5">
-        <v>1</v>
-      </c>
-      <c r="D487" s="5">
-        <v>1302</v>
-      </c>
-      <c r="E487" s="5" t="s">
+        <v>1202298</v>
+      </c>
+      <c r="B487" s="3">
+        <v>2</v>
+      </c>
+      <c r="C487" s="3">
+        <v>98</v>
+      </c>
+      <c r="D487" s="3">
+        <v>1202</v>
+      </c>
+      <c r="E487" s="3" t="s">
         <v>106</v>
       </c>
-      <c r="F487" s="5" t="s">
-        <v>107</v>
+      <c r="F487" s="3" t="s">
+        <v>87</v>
       </c>
     </row>
     <row r="488" spans="1:6">
       <c r="A488" s="5">
-        <f t="shared" si="20"/>
-        <v>1302202</v>
+        <f>D488*1000+B488*100+C488</f>
+        <v>1302201</v>
       </c>
       <c r="B488" s="5">
         <v>2</v>
       </c>
       <c r="C488" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D488" s="5">
         <v>1302</v>
       </c>
       <c r="E488" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="F488" s="5" t="s">
         <v>108</v>
-      </c>
-      <c r="F488" s="5" t="s">
-        <v>107</v>
       </c>
     </row>
     <row r="489" spans="1:6">
       <c r="A489" s="5">
-        <f t="shared" si="20"/>
-        <v>1302203</v>
+        <f>D489*1000+B489*100+C489</f>
+        <v>1302202</v>
       </c>
       <c r="B489" s="5">
         <v>2</v>
       </c>
       <c r="C489" s="5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D489" s="5">
         <v>1302</v>
@@ -11882,19 +11923,19 @@
         <v>109</v>
       </c>
       <c r="F489" s="5" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="490" spans="1:6">
       <c r="A490" s="5">
-        <f t="shared" si="20"/>
-        <v>1302204</v>
+        <f>D490*1000+B490*100+C490</f>
+        <v>1302203</v>
       </c>
       <c r="B490" s="5">
         <v>2</v>
       </c>
       <c r="C490" s="5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D490" s="5">
         <v>1302</v>
@@ -11903,19 +11944,19 @@
         <v>110</v>
       </c>
       <c r="F490" s="5" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="491" spans="1:6">
       <c r="A491" s="5">
-        <f t="shared" si="20"/>
-        <v>1302205</v>
+        <f>D491*1000+B491*100+C491</f>
+        <v>1302204</v>
       </c>
       <c r="B491" s="5">
         <v>2</v>
       </c>
       <c r="C491" s="5">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D491" s="5">
         <v>1302</v>
@@ -11924,19 +11965,19 @@
         <v>111</v>
       </c>
       <c r="F491" s="5" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="492" spans="1:6">
       <c r="A492" s="5">
-        <f t="shared" si="20"/>
-        <v>1302206</v>
+        <f>D492*1000+B492*100+C492</f>
+        <v>1302205</v>
       </c>
       <c r="B492" s="5">
         <v>2</v>
       </c>
       <c r="C492" s="5">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D492" s="5">
         <v>1302</v>
@@ -11945,19 +11986,19 @@
         <v>112</v>
       </c>
       <c r="F492" s="5" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="493" spans="1:6">
       <c r="A493" s="5">
-        <f t="shared" si="20"/>
-        <v>1302207</v>
+        <f>D493*1000+B493*100+C493</f>
+        <v>1302206</v>
       </c>
       <c r="B493" s="5">
         <v>2</v>
       </c>
       <c r="C493" s="5">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D493" s="5">
         <v>1302</v>
@@ -11966,19 +12007,19 @@
         <v>113</v>
       </c>
       <c r="F493" s="5" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="494" spans="1:6">
       <c r="A494" s="5">
-        <f t="shared" si="20"/>
-        <v>1302208</v>
+        <f>D494*1000+B494*100+C494</f>
+        <v>1302207</v>
       </c>
       <c r="B494" s="5">
         <v>2</v>
       </c>
       <c r="C494" s="5">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D494" s="5">
         <v>1302</v>
@@ -11987,19 +12028,19 @@
         <v>114</v>
       </c>
       <c r="F494" s="5" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="495" spans="1:6">
       <c r="A495" s="5">
-        <f t="shared" si="20"/>
-        <v>1302209</v>
+        <f>D495*1000+B495*100+C495</f>
+        <v>1302208</v>
       </c>
       <c r="B495" s="5">
         <v>2</v>
       </c>
       <c r="C495" s="5">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D495" s="5">
         <v>1302</v>
@@ -12008,19 +12049,19 @@
         <v>115</v>
       </c>
       <c r="F495" s="5" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="496" spans="1:6">
       <c r="A496" s="5">
-        <f t="shared" si="20"/>
-        <v>1302210</v>
+        <f>D496*1000+B496*100+C496</f>
+        <v>1302209</v>
       </c>
       <c r="B496" s="5">
         <v>2</v>
       </c>
       <c r="C496" s="5">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D496" s="5">
         <v>1302</v>
@@ -12029,19 +12070,19 @@
         <v>116</v>
       </c>
       <c r="F496" s="5" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="497" spans="1:6">
       <c r="A497" s="5">
-        <f t="shared" si="20"/>
-        <v>1302211</v>
+        <f>D497*1000+B497*100+C497</f>
+        <v>1302210</v>
       </c>
       <c r="B497" s="5">
         <v>2</v>
       </c>
       <c r="C497" s="5">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D497" s="5">
         <v>1302</v>
@@ -12050,19 +12091,19 @@
         <v>117</v>
       </c>
       <c r="F497" s="5" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="498" spans="1:6">
       <c r="A498" s="5">
-        <f t="shared" si="20"/>
-        <v>1302212</v>
+        <f>D498*1000+B498*100+C498</f>
+        <v>1302211</v>
       </c>
       <c r="B498" s="5">
         <v>2</v>
       </c>
       <c r="C498" s="5">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D498" s="5">
         <v>1302</v>
@@ -12071,19 +12112,19 @@
         <v>118</v>
       </c>
       <c r="F498" s="5" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="499" spans="1:6">
       <c r="A499" s="5">
-        <f t="shared" si="20"/>
-        <v>1302213</v>
+        <f>D499*1000+B499*100+C499</f>
+        <v>1302212</v>
       </c>
       <c r="B499" s="5">
         <v>2</v>
       </c>
       <c r="C499" s="5">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D499" s="5">
         <v>1302</v>
@@ -12092,19 +12133,19 @@
         <v>119</v>
       </c>
       <c r="F499" s="5" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="500" spans="1:6">
       <c r="A500" s="5">
-        <f t="shared" si="20"/>
-        <v>1302214</v>
+        <f>D500*1000+B500*100+C500</f>
+        <v>1302213</v>
       </c>
       <c r="B500" s="5">
         <v>2</v>
       </c>
       <c r="C500" s="5">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D500" s="5">
         <v>1302</v>
@@ -12113,19 +12154,19 @@
         <v>120</v>
       </c>
       <c r="F500" s="5" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="501" spans="1:6">
       <c r="A501" s="5">
-        <f t="shared" si="20"/>
-        <v>1302215</v>
+        <f>D501*1000+B501*100+C501</f>
+        <v>1302214</v>
       </c>
       <c r="B501" s="5">
         <v>2</v>
       </c>
       <c r="C501" s="5">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D501" s="5">
         <v>1302</v>
@@ -12134,19 +12175,19 @@
         <v>121</v>
       </c>
       <c r="F501" s="5" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="502" spans="1:6">
       <c r="A502" s="5">
-        <f t="shared" si="20"/>
-        <v>1302216</v>
+        <f>D502*1000+B502*100+C502</f>
+        <v>1302215</v>
       </c>
       <c r="B502" s="5">
         <v>2</v>
       </c>
       <c r="C502" s="5">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D502" s="5">
         <v>1302</v>
@@ -12155,625 +12196,638 @@
         <v>122</v>
       </c>
       <c r="F502" s="5" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="503" spans="1:6">
       <c r="A503" s="5">
-        <f t="shared" si="20"/>
-        <v>1302217</v>
+        <f>D503*1000+B503*100+C503</f>
+        <v>1302216</v>
       </c>
       <c r="B503" s="5">
         <v>2</v>
       </c>
       <c r="C503" s="5">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D503" s="5">
         <v>1302</v>
       </c>
       <c r="E503" s="5" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="F503" s="5" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="504" spans="1:6">
+      <c r="A504" s="5">
+        <f>D504*1000+B504*100+C504</f>
+        <v>1302217</v>
+      </c>
+      <c r="B504" s="5">
+        <v>2</v>
+      </c>
+      <c r="C504" s="5">
+        <v>17</v>
+      </c>
+      <c r="D504" s="5">
+        <v>1302</v>
+      </c>
+      <c r="E504" s="5" t="s">
+        <v>123</v>
+      </c>
+      <c r="F504" s="5" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="505" s="3" customFormat="1" spans="1:6">
+      <c r="A505" s="3">
+        <f>D505*1000+B505*100+C505</f>
+        <v>1301201</v>
+      </c>
+      <c r="B505" s="3">
+        <v>2</v>
+      </c>
+      <c r="C505" s="3">
+        <v>1</v>
+      </c>
+      <c r="D505" s="3">
+        <v>1301</v>
+      </c>
+      <c r="E505" s="3" t="s">
         <v>107</v>
       </c>
-    </row>
-    <row r="504" s="2" customFormat="1" spans="1:6">
-      <c r="A504" s="6">
-        <f>D504*1000+B504*100+C504</f>
-        <v>1301201</v>
-      </c>
-      <c r="B504" s="6">
-        <v>2</v>
-      </c>
-      <c r="C504" s="6">
-        <v>1</v>
-      </c>
-      <c r="D504" s="6">
+      <c r="F505" s="3" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="506" spans="1:6">
+      <c r="A506" s="3">
+        <f t="shared" ref="A506:A514" si="21">D506*1000+B506*100+C506</f>
+        <v>1301202</v>
+      </c>
+      <c r="B506" s="3">
+        <v>2</v>
+      </c>
+      <c r="C506" s="3">
+        <v>2</v>
+      </c>
+      <c r="D506" s="3">
         <v>1301</v>
       </c>
-      <c r="E504" s="6" t="s">
-        <v>106</v>
-      </c>
-      <c r="F504" s="6" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="505" spans="1:6">
-      <c r="A505" s="6">
-        <f t="shared" ref="A505:A513" si="21">D505*1000+B505*100+C505</f>
-        <v>1301202</v>
-      </c>
-      <c r="B505" s="3">
-        <v>2</v>
-      </c>
-      <c r="C505" s="3">
-        <v>2</v>
-      </c>
-      <c r="D505" s="6">
-        <v>1301</v>
-      </c>
-      <c r="E505" s="6" t="s">
-        <v>108</v>
-      </c>
-      <c r="F505" s="6" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="506" spans="1:6">
-      <c r="A506" s="6">
+      <c r="E506" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="F506" s="3" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="507" spans="1:6">
+      <c r="A507" s="3">
         <f t="shared" si="21"/>
         <v>1301203</v>
       </c>
-      <c r="B506" s="6">
-        <v>2</v>
-      </c>
-      <c r="C506" s="6">
+      <c r="B507" s="3">
+        <v>2</v>
+      </c>
+      <c r="C507" s="3">
         <v>3</v>
       </c>
-      <c r="D506" s="6">
+      <c r="D507" s="3">
         <v>1301</v>
       </c>
-      <c r="E506" s="6" t="s">
-        <v>109</v>
-      </c>
-      <c r="F506" s="6" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="507" spans="1:6">
-      <c r="A507" s="6">
+      <c r="E507" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="F507" s="3" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="508" spans="1:6">
+      <c r="A508" s="3">
         <f t="shared" si="21"/>
         <v>1301204</v>
       </c>
-      <c r="B507" s="3">
-        <v>2</v>
-      </c>
-      <c r="C507" s="3">
+      <c r="B508" s="3">
+        <v>2</v>
+      </c>
+      <c r="C508" s="3">
         <v>4</v>
       </c>
-      <c r="D507" s="6">
+      <c r="D508" s="3">
         <v>1301</v>
       </c>
-      <c r="E507" s="6" t="s">
-        <v>110</v>
-      </c>
-      <c r="F507" s="6" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="508" spans="1:6">
-      <c r="A508" s="6">
+      <c r="E508" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="F508" s="3" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="509" spans="1:6">
+      <c r="A509" s="3">
         <f t="shared" si="21"/>
         <v>1301205</v>
       </c>
-      <c r="B508" s="6">
-        <v>2</v>
-      </c>
-      <c r="C508" s="6">
+      <c r="B509" s="3">
+        <v>2</v>
+      </c>
+      <c r="C509" s="3">
         <v>5</v>
       </c>
-      <c r="D508" s="6">
+      <c r="D509" s="3">
         <v>1301</v>
       </c>
-      <c r="E508" s="6" t="s">
-        <v>111</v>
-      </c>
-      <c r="F508" s="6" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="509" spans="1:6">
-      <c r="A509" s="6">
+      <c r="E509" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="F509" s="3" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="510" spans="1:6">
+      <c r="A510" s="3">
         <f t="shared" si="21"/>
         <v>1301206</v>
       </c>
-      <c r="B509" s="3">
-        <v>2</v>
-      </c>
-      <c r="C509" s="3">
+      <c r="B510" s="3">
+        <v>2</v>
+      </c>
+      <c r="C510" s="3">
         <v>6</v>
       </c>
-      <c r="D509" s="6">
+      <c r="D510" s="3">
         <v>1301</v>
       </c>
-      <c r="E509" s="6" t="s">
-        <v>112</v>
-      </c>
-      <c r="F509" s="6" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="510" spans="1:6">
-      <c r="A510" s="6">
+      <c r="E510" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="F510" s="3" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="511" spans="1:6">
+      <c r="A511" s="3">
         <f t="shared" si="21"/>
         <v>1301207</v>
       </c>
-      <c r="B510" s="6">
-        <v>2</v>
-      </c>
-      <c r="C510" s="6">
+      <c r="B511" s="3">
+        <v>2</v>
+      </c>
+      <c r="C511" s="3">
         <v>7</v>
       </c>
-      <c r="D510" s="6">
+      <c r="D511" s="3">
         <v>1301</v>
       </c>
-      <c r="E510" s="6" t="s">
-        <v>113</v>
-      </c>
-      <c r="F510" s="6" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="511" spans="1:6">
-      <c r="A511" s="6">
+      <c r="E511" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="F511" s="3" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="512" spans="1:6">
+      <c r="A512" s="3">
         <f t="shared" si="21"/>
         <v>1301208</v>
       </c>
-      <c r="B511" s="3">
-        <v>2</v>
-      </c>
-      <c r="C511" s="3">
+      <c r="B512" s="3">
+        <v>2</v>
+      </c>
+      <c r="C512" s="3">
         <v>8</v>
       </c>
-      <c r="D511" s="6">
+      <c r="D512" s="3">
         <v>1301</v>
       </c>
-      <c r="E511" s="6" t="s">
-        <v>114</v>
-      </c>
-      <c r="F511" s="6" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="512" spans="1:6">
-      <c r="A512" s="6">
+      <c r="E512" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="F512" s="3" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="513" spans="1:6">
+      <c r="A513" s="3">
         <f t="shared" si="21"/>
         <v>1301209</v>
       </c>
-      <c r="B512" s="6">
-        <v>2</v>
-      </c>
-      <c r="C512" s="6">
+      <c r="B513" s="3">
+        <v>2</v>
+      </c>
+      <c r="C513" s="3">
         <v>9</v>
       </c>
-      <c r="D512" s="6">
+      <c r="D513" s="3">
         <v>1301</v>
       </c>
-      <c r="E512" s="6" t="s">
-        <v>115</v>
-      </c>
-      <c r="F512" s="6" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="513" spans="1:6">
-      <c r="A513" s="7">
+      <c r="E513" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="F513" s="3" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="514" spans="1:6">
+      <c r="A514" s="5">
         <f t="shared" si="21"/>
         <v>1303201</v>
       </c>
-      <c r="B513" s="7">
-        <v>2</v>
-      </c>
-      <c r="C513" s="7">
-        <v>1</v>
-      </c>
-      <c r="D513" s="7">
+      <c r="B514" s="5">
+        <v>2</v>
+      </c>
+      <c r="C514" s="5">
+        <v>1</v>
+      </c>
+      <c r="D514" s="5">
         <v>1303</v>
       </c>
-      <c r="E513" s="7" t="s">
-        <v>106</v>
-      </c>
-      <c r="F513" s="7" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="514" spans="1:6">
-      <c r="A514" s="7">
-        <f t="shared" ref="A514:A522" si="22">D514*1000+B514*100+C514</f>
+      <c r="E514" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="F514" s="5" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="515" spans="1:6">
+      <c r="A515" s="5">
+        <f t="shared" ref="A515:A525" si="22">D515*1000+B515*100+C515</f>
         <v>1303202</v>
       </c>
-      <c r="B514" s="7">
-        <v>2</v>
-      </c>
-      <c r="C514" s="7">
-        <v>2</v>
-      </c>
-      <c r="D514" s="7">
+      <c r="B515" s="5">
+        <v>2</v>
+      </c>
+      <c r="C515" s="5">
+        <v>2</v>
+      </c>
+      <c r="D515" s="5">
         <v>1303</v>
       </c>
-      <c r="E514" s="7" t="s">
-        <v>108</v>
-      </c>
-      <c r="F514" s="7" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="515" spans="1:6">
-      <c r="A515" s="7">
+      <c r="E515" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="F515" s="5" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="516" spans="1:6">
+      <c r="A516" s="5">
         <f t="shared" si="22"/>
         <v>1303203</v>
       </c>
-      <c r="B515" s="7">
-        <v>2</v>
-      </c>
-      <c r="C515" s="7">
+      <c r="B516" s="5">
+        <v>2</v>
+      </c>
+      <c r="C516" s="5">
         <v>3</v>
       </c>
-      <c r="D515" s="7">
+      <c r="D516" s="5">
         <v>1303</v>
       </c>
-      <c r="E515" s="7" t="s">
-        <v>109</v>
-      </c>
-      <c r="F515" s="7" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="516" spans="1:6">
-      <c r="A516" s="7">
+      <c r="E516" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="F516" s="5" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="517" spans="1:6">
+      <c r="A517" s="5">
         <f t="shared" si="22"/>
         <v>1303204</v>
       </c>
-      <c r="B516" s="7">
-        <v>2</v>
-      </c>
-      <c r="C516" s="7">
+      <c r="B517" s="5">
+        <v>2</v>
+      </c>
+      <c r="C517" s="5">
         <v>4</v>
       </c>
-      <c r="D516" s="7">
+      <c r="D517" s="5">
         <v>1303</v>
       </c>
-      <c r="E516" s="7" t="s">
-        <v>110</v>
-      </c>
-      <c r="F516" s="7" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="517" spans="1:6">
-      <c r="A517" s="7">
+      <c r="E517" s="5" t="s">
+        <v>111</v>
+      </c>
+      <c r="F517" s="5" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="518" spans="1:6">
+      <c r="A518" s="5">
         <f t="shared" si="22"/>
         <v>1303205</v>
       </c>
-      <c r="B517" s="7">
-        <v>2</v>
-      </c>
-      <c r="C517" s="7">
+      <c r="B518" s="5">
+        <v>2</v>
+      </c>
+      <c r="C518" s="5">
         <v>5</v>
       </c>
-      <c r="D517" s="7">
+      <c r="D518" s="5">
         <v>1303</v>
       </c>
-      <c r="E517" s="7" t="s">
-        <v>111</v>
-      </c>
-      <c r="F517" s="7" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="518" spans="1:6">
-      <c r="A518" s="7">
+      <c r="E518" s="5" t="s">
+        <v>112</v>
+      </c>
+      <c r="F518" s="5" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="519" spans="1:6">
+      <c r="A519" s="5">
         <f t="shared" si="22"/>
         <v>1303206</v>
       </c>
-      <c r="B518" s="7">
-        <v>2</v>
-      </c>
-      <c r="C518" s="7">
+      <c r="B519" s="5">
+        <v>2</v>
+      </c>
+      <c r="C519" s="5">
         <v>6</v>
       </c>
-      <c r="D518" s="7">
+      <c r="D519" s="5">
         <v>1303</v>
       </c>
-      <c r="E518" s="7" t="s">
-        <v>112</v>
-      </c>
-      <c r="F518" s="7" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="519" spans="1:6">
-      <c r="A519" s="7">
+      <c r="E519" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="F519" s="5" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="520" spans="1:6">
+      <c r="A520" s="5">
         <f t="shared" si="22"/>
         <v>1303207</v>
       </c>
-      <c r="B519" s="7">
-        <v>2</v>
-      </c>
-      <c r="C519" s="7">
+      <c r="B520" s="5">
+        <v>2</v>
+      </c>
+      <c r="C520" s="5">
         <v>7</v>
       </c>
-      <c r="D519" s="7">
+      <c r="D520" s="5">
         <v>1303</v>
       </c>
-      <c r="E519" s="7" t="s">
-        <v>113</v>
-      </c>
-      <c r="F519" s="7" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="520" spans="1:6">
-      <c r="A520" s="7">
+      <c r="E520" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="F520" s="5" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="521" spans="1:6">
+      <c r="A521" s="5">
         <f t="shared" si="22"/>
         <v>1303208</v>
       </c>
-      <c r="B520" s="7">
-        <v>2</v>
-      </c>
-      <c r="C520" s="7">
+      <c r="B521" s="5">
+        <v>2</v>
+      </c>
+      <c r="C521" s="5">
         <v>8</v>
       </c>
-      <c r="D520" s="7">
+      <c r="D521" s="5">
         <v>1303</v>
       </c>
-      <c r="E520" s="7" t="s">
-        <v>114</v>
-      </c>
-      <c r="F520" s="7" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="521" spans="1:6">
-      <c r="A521" s="7">
+      <c r="E521" s="5" t="s">
+        <v>115</v>
+      </c>
+      <c r="F521" s="5" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="522" spans="1:6">
+      <c r="A522" s="5">
         <f t="shared" si="22"/>
         <v>1303209</v>
       </c>
-      <c r="B521" s="7">
-        <v>2</v>
-      </c>
-      <c r="C521" s="7">
+      <c r="B522" s="5">
+        <v>2</v>
+      </c>
+      <c r="C522" s="5">
         <v>9</v>
       </c>
-      <c r="D521" s="7">
+      <c r="D522" s="5">
         <v>1303</v>
       </c>
-      <c r="E521" s="7" t="s">
-        <v>115</v>
-      </c>
-      <c r="F521" s="7" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="522" spans="1:6">
-      <c r="A522" s="7">
+      <c r="E522" s="5" t="s">
+        <v>116</v>
+      </c>
+      <c r="F522" s="5" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="523" spans="1:6">
+      <c r="A523" s="5">
         <f t="shared" si="22"/>
         <v>1303210</v>
       </c>
-      <c r="B522" s="7">
-        <v>2</v>
-      </c>
-      <c r="C522" s="7">
+      <c r="B523" s="5">
+        <v>2</v>
+      </c>
+      <c r="C523" s="5">
         <v>10</v>
       </c>
-      <c r="D522" s="7">
+      <c r="D523" s="5">
         <v>1303</v>
       </c>
-      <c r="E522" s="7" t="s">
-        <v>116</v>
-      </c>
-      <c r="F522" s="7" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="523" spans="1:6">
-      <c r="A523" s="7">
-        <f>D523*1000+B523*100+C523</f>
+      <c r="E523" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="F523" s="5" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="524" spans="1:6">
+      <c r="A524" s="5">
+        <f t="shared" si="22"/>
         <v>1303211</v>
       </c>
-      <c r="B523" s="7">
-        <v>2</v>
-      </c>
-      <c r="C523" s="7">
+      <c r="B524" s="5">
+        <v>2</v>
+      </c>
+      <c r="C524" s="5">
         <v>11</v>
       </c>
-      <c r="D523" s="7">
+      <c r="D524" s="5">
         <v>1303</v>
       </c>
-      <c r="E523" s="7" t="s">
-        <v>117</v>
-      </c>
-      <c r="F523" s="7" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="524" spans="1:6">
-      <c r="A524" s="6">
-        <f>D524*1000+B524*100+C524</f>
+      <c r="E524" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="F524" s="5" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="525" spans="1:6">
+      <c r="A525" s="3">
+        <f t="shared" si="22"/>
         <v>1304201</v>
       </c>
-      <c r="B524" s="6">
-        <v>2</v>
-      </c>
-      <c r="C524" s="6">
-        <v>1</v>
-      </c>
-      <c r="D524" s="6">
+      <c r="B525" s="3">
+        <v>2</v>
+      </c>
+      <c r="C525" s="3">
+        <v>1</v>
+      </c>
+      <c r="D525" s="3">
         <v>1304</v>
       </c>
-      <c r="E524" s="6" t="s">
-        <v>106</v>
-      </c>
-      <c r="F524" s="6" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="525" spans="1:6">
-      <c r="A525" s="6">
-        <f t="shared" ref="A525:A532" si="23">D525*1000+B525*100+C525</f>
+      <c r="E525" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="F525" s="3" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="526" spans="1:6">
+      <c r="A526" s="3">
+        <f t="shared" ref="A526:A533" si="23">D526*1000+B526*100+C526</f>
         <v>1304202</v>
       </c>
-      <c r="B525" s="6">
-        <v>2</v>
-      </c>
-      <c r="C525" s="6">
-        <v>2</v>
-      </c>
-      <c r="D525" s="6">
+      <c r="B526" s="3">
+        <v>2</v>
+      </c>
+      <c r="C526" s="3">
+        <v>2</v>
+      </c>
+      <c r="D526" s="3">
         <v>1304</v>
       </c>
-      <c r="E525" s="6" t="s">
-        <v>108</v>
-      </c>
-      <c r="F525" s="6" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="526" spans="1:6">
-      <c r="A526" s="6">
+      <c r="E526" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="F526" s="3" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="527" spans="1:6">
+      <c r="A527" s="3">
         <f t="shared" si="23"/>
         <v>1304203</v>
       </c>
-      <c r="B526" s="6">
-        <v>2</v>
-      </c>
-      <c r="C526" s="6">
+      <c r="B527" s="3">
+        <v>2</v>
+      </c>
+      <c r="C527" s="3">
         <v>3</v>
       </c>
-      <c r="D526" s="6">
+      <c r="D527" s="3">
         <v>1304</v>
       </c>
-      <c r="E526" s="6" t="s">
-        <v>109</v>
-      </c>
-      <c r="F526" s="6" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="527" spans="1:6">
-      <c r="A527" s="6">
+      <c r="E527" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="F527" s="3" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="528" spans="1:6">
+      <c r="A528" s="3">
         <f t="shared" si="23"/>
         <v>1304204</v>
       </c>
-      <c r="B527" s="6">
-        <v>2</v>
-      </c>
-      <c r="C527" s="6">
+      <c r="B528" s="3">
+        <v>2</v>
+      </c>
+      <c r="C528" s="3">
         <v>4</v>
       </c>
-      <c r="D527" s="6">
+      <c r="D528" s="3">
         <v>1304</v>
       </c>
-      <c r="E527" s="6" t="s">
-        <v>110</v>
-      </c>
-      <c r="F527" s="6" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="528" spans="1:6">
-      <c r="A528" s="6">
+      <c r="E528" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="F528" s="3" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="529" spans="1:6">
+      <c r="A529" s="3">
         <f t="shared" si="23"/>
         <v>1304205</v>
       </c>
-      <c r="B528" s="6">
-        <v>2</v>
-      </c>
-      <c r="C528" s="6">
+      <c r="B529" s="3">
+        <v>2</v>
+      </c>
+      <c r="C529" s="3">
         <v>5</v>
       </c>
-      <c r="D528" s="6">
+      <c r="D529" s="3">
         <v>1304</v>
       </c>
-      <c r="E528" s="6" t="s">
-        <v>111</v>
-      </c>
-      <c r="F528" s="6" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="529" spans="1:6">
-      <c r="A529" s="6">
+      <c r="E529" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="F529" s="3" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="530" spans="1:6">
+      <c r="A530" s="3">
         <f t="shared" si="23"/>
         <v>1304206</v>
       </c>
-      <c r="B529" s="6">
-        <v>2</v>
-      </c>
-      <c r="C529" s="6">
+      <c r="B530" s="3">
+        <v>2</v>
+      </c>
+      <c r="C530" s="3">
         <v>6</v>
       </c>
-      <c r="D529" s="6">
+      <c r="D530" s="3">
         <v>1304</v>
       </c>
-      <c r="E529" s="6" t="s">
-        <v>112</v>
-      </c>
-      <c r="F529" s="6" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="530" spans="1:6">
-      <c r="A530" s="6">
+      <c r="E530" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="F530" s="3" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="531" spans="1:6">
+      <c r="A531" s="3">
         <f t="shared" si="23"/>
         <v>1304207</v>
       </c>
-      <c r="B530" s="6">
-        <v>2</v>
-      </c>
-      <c r="C530" s="6">
+      <c r="B531" s="3">
+        <v>2</v>
+      </c>
+      <c r="C531" s="3">
         <v>7</v>
       </c>
-      <c r="D530" s="6">
+      <c r="D531" s="3">
         <v>1304</v>
       </c>
-      <c r="E530" s="6" t="s">
-        <v>113</v>
-      </c>
-      <c r="F530" s="6" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="531" spans="1:6">
-      <c r="A531" s="6">
+      <c r="E531" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="F531" s="3" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="532" spans="1:6">
+      <c r="A532" s="3">
         <f t="shared" si="23"/>
         <v>1304208</v>
       </c>
-      <c r="B531" s="6">
-        <v>2</v>
-      </c>
-      <c r="C531" s="6">
+      <c r="B532" s="3">
+        <v>2</v>
+      </c>
+      <c r="C532" s="3">
         <v>8</v>
       </c>
-      <c r="D531" s="6">
+      <c r="D532" s="3">
         <v>1304</v>
       </c>
-      <c r="E531" s="6" t="s">
-        <v>114</v>
-      </c>
-      <c r="F531" s="6" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="532" spans="1:6">
-      <c r="A532" s="6"/>
-      <c r="B532" s="6"/>
-      <c r="C532" s="6"/>
-      <c r="D532" s="6"/>
-      <c r="E532" s="6"/>
-      <c r="F532" s="6"/>
+      <c r="E532" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="F532" s="3" t="s">
+        <v>126</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/hall/resources/sample/BuildingEquipmentTable.xlsx
+++ b/hall/resources/sample/BuildingEquipmentTable.xlsx
@@ -104,7 +104,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1070" uniqueCount="127">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1126" uniqueCount="148">
   <si>
     <t>ID</t>
   </si>
@@ -430,7 +430,7 @@
     <t>装饰1</t>
   </si>
   <si>
-    <t>研发部</t>
+    <t>研发院</t>
   </si>
   <si>
     <t>装饰2</t>
@@ -476,6 +476,69 @@
   </si>
   <si>
     <t>装饰16</t>
+  </si>
+  <si>
+    <t>装饰17</t>
+  </si>
+  <si>
+    <t>装饰-SLOT机台</t>
+  </si>
+  <si>
+    <t>游戏厅-超级明星</t>
+  </si>
+  <si>
+    <t>游戏厅-财神来了</t>
+  </si>
+  <si>
+    <t>游戏厅-麻将胡了</t>
+  </si>
+  <si>
+    <t>游戏厅-篮球巨星</t>
+  </si>
+  <si>
+    <t>游戏厅-寒冰王座</t>
+  </si>
+  <si>
+    <t>游戏厅-绿巨人</t>
+  </si>
+  <si>
+    <t>游戏厅-雷神</t>
+  </si>
+  <si>
+    <t>游戏厅-杰克船长</t>
+  </si>
+  <si>
+    <t>游戏厅-热血足球</t>
+  </si>
+  <si>
+    <t>游戏厅-宙斯vs哈迪斯</t>
+  </si>
+  <si>
+    <t>恶魔之子</t>
+  </si>
+  <si>
+    <t>圣诞狂欢夜</t>
+  </si>
+  <si>
+    <t>愤怒的小鸟</t>
+  </si>
+  <si>
+    <t>伽罗宝石</t>
+  </si>
+  <si>
+    <t>金矿大亨</t>
+  </si>
+  <si>
+    <t>德古拉黑暗财富</t>
+  </si>
+  <si>
+    <t>糖果派对</t>
+  </si>
+  <si>
+    <t>狼月</t>
+  </si>
+  <si>
+    <t>未指定</t>
   </si>
   <si>
     <t>接待区</t>
@@ -669,12 +732,12 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -1680,12 +1743,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F532"/>
+  <dimension ref="A1:F560"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="4" width="18.375" style="3" customWidth="1"/>
-    <col min="5" max="5" width="13.125" style="3" customWidth="1"/>
-    <col min="6" max="6" width="11.375" style="3" customWidth="1"/>
+    <col min="5" max="5" width="14.875" style="3" customWidth="1"/>
+    <col min="6" max="6" width="30.25" style="3" customWidth="1"/>
     <col min="7" max="7" width="10.625" style="3" customWidth="1"/>
     <col min="8" max="8" width="13.75" style="3" customWidth="1"/>
     <col min="9" max="16384" width="9" style="3"/>
@@ -11088,7 +11151,7 @@
     </row>
     <row r="450" spans="1:6">
       <c r="A450" s="3">
-        <f t="shared" ref="A450:A504" si="20">D450*1000+B450*100+C450</f>
+        <f t="shared" ref="A450:A505" si="20">D450*1000+B450*100+C450</f>
         <v>1202261</v>
       </c>
       <c r="B450" s="3">
@@ -11886,14 +11949,14 @@
     </row>
     <row r="488" spans="1:6">
       <c r="A488" s="5">
-        <f>D488*1000+B488*100+C488</f>
-        <v>1302201</v>
+        <f t="shared" si="20"/>
+        <v>1302251</v>
       </c>
       <c r="B488" s="5">
         <v>2</v>
       </c>
       <c r="C488" s="5">
-        <v>1</v>
+        <v>51</v>
       </c>
       <c r="D488" s="5">
         <v>1302</v>
@@ -11907,14 +11970,14 @@
     </row>
     <row r="489" spans="1:6">
       <c r="A489" s="5">
-        <f>D489*1000+B489*100+C489</f>
-        <v>1302202</v>
+        <f t="shared" si="20"/>
+        <v>1302252</v>
       </c>
       <c r="B489" s="5">
         <v>2</v>
       </c>
       <c r="C489" s="5">
-        <v>2</v>
+        <v>52</v>
       </c>
       <c r="D489" s="5">
         <v>1302</v>
@@ -11928,14 +11991,14 @@
     </row>
     <row r="490" spans="1:6">
       <c r="A490" s="5">
-        <f>D490*1000+B490*100+C490</f>
-        <v>1302203</v>
+        <f t="shared" ref="A490:A532" si="21">D490*1000+B490*100+C490</f>
+        <v>1302253</v>
       </c>
       <c r="B490" s="5">
         <v>2</v>
       </c>
       <c r="C490" s="5">
-        <v>3</v>
+        <v>53</v>
       </c>
       <c r="D490" s="5">
         <v>1302</v>
@@ -11949,14 +12012,14 @@
     </row>
     <row r="491" spans="1:6">
       <c r="A491" s="5">
-        <f>D491*1000+B491*100+C491</f>
-        <v>1302204</v>
+        <f t="shared" si="21"/>
+        <v>1302254</v>
       </c>
       <c r="B491" s="5">
         <v>2</v>
       </c>
       <c r="C491" s="5">
-        <v>4</v>
+        <v>54</v>
       </c>
       <c r="D491" s="5">
         <v>1302</v>
@@ -11970,14 +12033,14 @@
     </row>
     <row r="492" spans="1:6">
       <c r="A492" s="5">
-        <f>D492*1000+B492*100+C492</f>
-        <v>1302205</v>
+        <f t="shared" si="21"/>
+        <v>1302255</v>
       </c>
       <c r="B492" s="5">
         <v>2</v>
       </c>
       <c r="C492" s="5">
-        <v>5</v>
+        <v>55</v>
       </c>
       <c r="D492" s="5">
         <v>1302</v>
@@ -11991,14 +12054,14 @@
     </row>
     <row r="493" spans="1:6">
       <c r="A493" s="5">
-        <f>D493*1000+B493*100+C493</f>
-        <v>1302206</v>
+        <f t="shared" si="21"/>
+        <v>1302256</v>
       </c>
       <c r="B493" s="5">
         <v>2</v>
       </c>
       <c r="C493" s="5">
-        <v>6</v>
+        <v>56</v>
       </c>
       <c r="D493" s="5">
         <v>1302</v>
@@ -12012,14 +12075,14 @@
     </row>
     <row r="494" spans="1:6">
       <c r="A494" s="5">
-        <f>D494*1000+B494*100+C494</f>
-        <v>1302207</v>
+        <f t="shared" si="21"/>
+        <v>1302257</v>
       </c>
       <c r="B494" s="5">
         <v>2</v>
       </c>
       <c r="C494" s="5">
-        <v>7</v>
+        <v>57</v>
       </c>
       <c r="D494" s="5">
         <v>1302</v>
@@ -12033,14 +12096,14 @@
     </row>
     <row r="495" spans="1:6">
       <c r="A495" s="5">
-        <f>D495*1000+B495*100+C495</f>
-        <v>1302208</v>
+        <f t="shared" si="21"/>
+        <v>1302258</v>
       </c>
       <c r="B495" s="5">
         <v>2</v>
       </c>
       <c r="C495" s="5">
-        <v>8</v>
+        <v>58</v>
       </c>
       <c r="D495" s="5">
         <v>1302</v>
@@ -12054,14 +12117,14 @@
     </row>
     <row r="496" spans="1:6">
       <c r="A496" s="5">
-        <f>D496*1000+B496*100+C496</f>
-        <v>1302209</v>
+        <f t="shared" si="21"/>
+        <v>1302259</v>
       </c>
       <c r="B496" s="5">
         <v>2</v>
       </c>
       <c r="C496" s="5">
-        <v>9</v>
+        <v>59</v>
       </c>
       <c r="D496" s="5">
         <v>1302</v>
@@ -12075,14 +12138,14 @@
     </row>
     <row r="497" spans="1:6">
       <c r="A497" s="5">
-        <f>D497*1000+B497*100+C497</f>
-        <v>1302210</v>
+        <f t="shared" si="21"/>
+        <v>1302260</v>
       </c>
       <c r="B497" s="5">
         <v>2</v>
       </c>
       <c r="C497" s="5">
-        <v>10</v>
+        <v>60</v>
       </c>
       <c r="D497" s="5">
         <v>1302</v>
@@ -12096,14 +12159,14 @@
     </row>
     <row r="498" spans="1:6">
       <c r="A498" s="5">
-        <f>D498*1000+B498*100+C498</f>
-        <v>1302211</v>
+        <f t="shared" si="21"/>
+        <v>1302261</v>
       </c>
       <c r="B498" s="5">
         <v>2</v>
       </c>
       <c r="C498" s="5">
-        <v>11</v>
+        <v>61</v>
       </c>
       <c r="D498" s="5">
         <v>1302</v>
@@ -12117,14 +12180,14 @@
     </row>
     <row r="499" spans="1:6">
       <c r="A499" s="5">
-        <f>D499*1000+B499*100+C499</f>
-        <v>1302212</v>
+        <f t="shared" si="21"/>
+        <v>1302262</v>
       </c>
       <c r="B499" s="5">
         <v>2</v>
       </c>
       <c r="C499" s="5">
-        <v>12</v>
+        <v>62</v>
       </c>
       <c r="D499" s="5">
         <v>1302</v>
@@ -12138,14 +12201,14 @@
     </row>
     <row r="500" spans="1:6">
       <c r="A500" s="5">
-        <f>D500*1000+B500*100+C500</f>
-        <v>1302213</v>
+        <f t="shared" si="21"/>
+        <v>1302263</v>
       </c>
       <c r="B500" s="5">
         <v>2</v>
       </c>
       <c r="C500" s="5">
-        <v>13</v>
+        <v>63</v>
       </c>
       <c r="D500" s="5">
         <v>1302</v>
@@ -12159,14 +12222,14 @@
     </row>
     <row r="501" spans="1:6">
       <c r="A501" s="5">
-        <f>D501*1000+B501*100+C501</f>
-        <v>1302214</v>
+        <f t="shared" si="21"/>
+        <v>1302264</v>
       </c>
       <c r="B501" s="5">
         <v>2</v>
       </c>
       <c r="C501" s="5">
-        <v>14</v>
+        <v>64</v>
       </c>
       <c r="D501" s="5">
         <v>1302</v>
@@ -12180,14 +12243,14 @@
     </row>
     <row r="502" spans="1:6">
       <c r="A502" s="5">
-        <f>D502*1000+B502*100+C502</f>
-        <v>1302215</v>
+        <f t="shared" si="21"/>
+        <v>1302265</v>
       </c>
       <c r="B502" s="5">
         <v>2</v>
       </c>
       <c r="C502" s="5">
-        <v>15</v>
+        <v>65</v>
       </c>
       <c r="D502" s="5">
         <v>1302</v>
@@ -12201,14 +12264,14 @@
     </row>
     <row r="503" spans="1:6">
       <c r="A503" s="5">
-        <f>D503*1000+B503*100+C503</f>
-        <v>1302216</v>
+        <f t="shared" si="21"/>
+        <v>1302266</v>
       </c>
       <c r="B503" s="5">
         <v>2</v>
       </c>
       <c r="C503" s="5">
-        <v>16</v>
+        <v>66</v>
       </c>
       <c r="D503" s="5">
         <v>1302</v>
@@ -12222,611 +12285,1199 @@
     </row>
     <row r="504" spans="1:6">
       <c r="A504" s="5">
-        <f>D504*1000+B504*100+C504</f>
-        <v>1302217</v>
+        <f t="shared" si="21"/>
+        <v>1302267</v>
       </c>
       <c r="B504" s="5">
         <v>2</v>
       </c>
       <c r="C504" s="5">
-        <v>17</v>
+        <v>67</v>
       </c>
       <c r="D504" s="5">
         <v>1302</v>
       </c>
       <c r="E504" s="5" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="F504" s="5" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="505" s="3" customFormat="1" spans="1:6">
-      <c r="A505" s="3">
-        <f>D505*1000+B505*100+C505</f>
-        <v>1301201</v>
-      </c>
-      <c r="B505" s="3">
-        <v>2</v>
-      </c>
-      <c r="C505" s="3">
-        <v>1</v>
-      </c>
-      <c r="D505" s="3">
-        <v>1301</v>
-      </c>
-      <c r="E505" s="3" t="s">
-        <v>107</v>
-      </c>
-      <c r="F505" s="3" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="506" spans="1:6">
-      <c r="A506" s="3">
-        <f t="shared" ref="A506:A514" si="21">D506*1000+B506*100+C506</f>
-        <v>1301202</v>
-      </c>
-      <c r="B506" s="3">
-        <v>2</v>
-      </c>
-      <c r="C506" s="3">
-        <v>2</v>
-      </c>
-      <c r="D506" s="3">
-        <v>1301</v>
-      </c>
-      <c r="E506" s="3" t="s">
-        <v>109</v>
-      </c>
-      <c r="F506" s="3" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="507" spans="1:6">
-      <c r="A507" s="3">
+    <row r="505" customFormat="1" spans="1:6">
+      <c r="A505" s="5">
         <f t="shared" si="21"/>
-        <v>1301203</v>
-      </c>
-      <c r="B507" s="3">
-        <v>2</v>
-      </c>
-      <c r="C507" s="3">
-        <v>3</v>
-      </c>
-      <c r="D507" s="3">
-        <v>1301</v>
-      </c>
-      <c r="E507" s="3" t="s">
-        <v>110</v>
-      </c>
-      <c r="F507" s="3" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="508" spans="1:6">
-      <c r="A508" s="3">
+        <v>1302268</v>
+      </c>
+      <c r="B505" s="5">
+        <v>2</v>
+      </c>
+      <c r="C505" s="5">
+        <v>68</v>
+      </c>
+      <c r="D505" s="5">
+        <v>1302</v>
+      </c>
+      <c r="E505" s="5" t="s">
+        <v>125</v>
+      </c>
+      <c r="F505" s="5" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="506" customFormat="1" spans="1:6">
+      <c r="A506" s="5">
         <f t="shared" si="21"/>
-        <v>1301204</v>
-      </c>
-      <c r="B508" s="3">
-        <v>2</v>
-      </c>
-      <c r="C508" s="3">
-        <v>4</v>
-      </c>
-      <c r="D508" s="3">
-        <v>1301</v>
-      </c>
-      <c r="E508" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="F508" s="3" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="509" spans="1:6">
-      <c r="A509" s="3">
+        <v>1302269</v>
+      </c>
+      <c r="B506" s="5">
+        <v>2</v>
+      </c>
+      <c r="C506" s="5">
+        <v>69</v>
+      </c>
+      <c r="D506" s="5">
+        <v>1302</v>
+      </c>
+      <c r="E506" s="5" t="s">
+        <v>125</v>
+      </c>
+      <c r="F506" s="5" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="507" customFormat="1" spans="1:6">
+      <c r="A507" s="5">
         <f t="shared" si="21"/>
-        <v>1301205</v>
-      </c>
-      <c r="B509" s="3">
-        <v>2</v>
-      </c>
-      <c r="C509" s="3">
-        <v>5</v>
-      </c>
-      <c r="D509" s="3">
-        <v>1301</v>
-      </c>
-      <c r="E509" s="3" t="s">
-        <v>112</v>
-      </c>
-      <c r="F509" s="3" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="510" spans="1:6">
-      <c r="A510" s="3">
+        <v>1302270</v>
+      </c>
+      <c r="B507" s="5">
+        <v>2</v>
+      </c>
+      <c r="C507" s="5">
+        <v>70</v>
+      </c>
+      <c r="D507" s="5">
+        <v>1302</v>
+      </c>
+      <c r="E507" s="5" t="s">
+        <v>125</v>
+      </c>
+      <c r="F507" s="5" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="508" customFormat="1" spans="1:6">
+      <c r="A508" s="5">
         <f t="shared" si="21"/>
-        <v>1301206</v>
-      </c>
-      <c r="B510" s="3">
-        <v>2</v>
-      </c>
-      <c r="C510" s="3">
-        <v>6</v>
-      </c>
-      <c r="D510" s="3">
-        <v>1301</v>
-      </c>
-      <c r="E510" s="3" t="s">
-        <v>113</v>
-      </c>
-      <c r="F510" s="3" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="511" spans="1:6">
-      <c r="A511" s="3">
+        <v>1302271</v>
+      </c>
+      <c r="B508" s="5">
+        <v>2</v>
+      </c>
+      <c r="C508" s="5">
+        <v>71</v>
+      </c>
+      <c r="D508" s="5">
+        <v>1302</v>
+      </c>
+      <c r="E508" s="5" t="s">
+        <v>125</v>
+      </c>
+      <c r="F508" s="5" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="509" customFormat="1" spans="1:6">
+      <c r="A509" s="5">
         <f t="shared" si="21"/>
-        <v>1301207</v>
-      </c>
-      <c r="B511" s="3">
-        <v>2</v>
-      </c>
-      <c r="C511" s="3">
-        <v>7</v>
-      </c>
-      <c r="D511" s="3">
-        <v>1301</v>
-      </c>
-      <c r="E511" s="3" t="s">
-        <v>114</v>
-      </c>
-      <c r="F511" s="3" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="512" spans="1:6">
-      <c r="A512" s="3">
+        <v>1302272</v>
+      </c>
+      <c r="B509" s="5">
+        <v>2</v>
+      </c>
+      <c r="C509" s="5">
+        <v>72</v>
+      </c>
+      <c r="D509" s="5">
+        <v>1302</v>
+      </c>
+      <c r="E509" s="5" t="s">
+        <v>125</v>
+      </c>
+      <c r="F509" s="5" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="510" customFormat="1" spans="1:6">
+      <c r="A510" s="5">
         <f t="shared" si="21"/>
-        <v>1301208</v>
-      </c>
-      <c r="B512" s="3">
-        <v>2</v>
-      </c>
-      <c r="C512" s="3">
-        <v>8</v>
-      </c>
-      <c r="D512" s="3">
-        <v>1301</v>
-      </c>
-      <c r="E512" s="3" t="s">
-        <v>115</v>
-      </c>
-      <c r="F512" s="3" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="513" spans="1:6">
-      <c r="A513" s="3">
+        <v>1302273</v>
+      </c>
+      <c r="B510" s="5">
+        <v>2</v>
+      </c>
+      <c r="C510" s="5">
+        <v>73</v>
+      </c>
+      <c r="D510" s="5">
+        <v>1302</v>
+      </c>
+      <c r="E510" s="5" t="s">
+        <v>125</v>
+      </c>
+      <c r="F510" s="5" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="511" customFormat="1" spans="1:6">
+      <c r="A511" s="5">
         <f t="shared" si="21"/>
-        <v>1301209</v>
-      </c>
-      <c r="B513" s="3">
-        <v>2</v>
-      </c>
-      <c r="C513" s="3">
-        <v>9</v>
-      </c>
-      <c r="D513" s="3">
-        <v>1301</v>
-      </c>
-      <c r="E513" s="3" t="s">
-        <v>116</v>
-      </c>
-      <c r="F513" s="3" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="514" spans="1:6">
+        <v>1302274</v>
+      </c>
+      <c r="B511" s="5">
+        <v>2</v>
+      </c>
+      <c r="C511" s="5">
+        <v>74</v>
+      </c>
+      <c r="D511" s="5">
+        <v>1302</v>
+      </c>
+      <c r="E511" s="5" t="s">
+        <v>125</v>
+      </c>
+      <c r="F511" s="5" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="512" customFormat="1" spans="1:6">
+      <c r="A512" s="5">
+        <f t="shared" si="21"/>
+        <v>1302275</v>
+      </c>
+      <c r="B512" s="5">
+        <v>2</v>
+      </c>
+      <c r="C512" s="5">
+        <v>75</v>
+      </c>
+      <c r="D512" s="5">
+        <v>1302</v>
+      </c>
+      <c r="E512" s="5" t="s">
+        <v>125</v>
+      </c>
+      <c r="F512" s="5" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="513" customFormat="1" spans="1:6">
+      <c r="A513" s="5">
+        <f t="shared" si="21"/>
+        <v>1302276</v>
+      </c>
+      <c r="B513" s="5">
+        <v>2</v>
+      </c>
+      <c r="C513" s="5">
+        <v>76</v>
+      </c>
+      <c r="D513" s="5">
+        <v>1302</v>
+      </c>
+      <c r="E513" s="5" t="s">
+        <v>125</v>
+      </c>
+      <c r="F513" s="5" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="514" customFormat="1" spans="1:6">
       <c r="A514" s="5">
         <f t="shared" si="21"/>
+        <v>1302277</v>
+      </c>
+      <c r="B514" s="5">
+        <v>2</v>
+      </c>
+      <c r="C514" s="5">
+        <v>77</v>
+      </c>
+      <c r="D514" s="5">
+        <v>1302</v>
+      </c>
+      <c r="E514" s="5" t="s">
+        <v>125</v>
+      </c>
+      <c r="F514" s="5" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="515" customFormat="1" spans="1:6">
+      <c r="A515" s="5">
+        <f t="shared" si="21"/>
+        <v>1302278</v>
+      </c>
+      <c r="B515" s="5">
+        <v>2</v>
+      </c>
+      <c r="C515" s="5">
+        <v>78</v>
+      </c>
+      <c r="D515" s="5">
+        <v>1302</v>
+      </c>
+      <c r="E515" s="5" t="s">
+        <v>125</v>
+      </c>
+      <c r="F515" s="5" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="516" customFormat="1" spans="1:6">
+      <c r="A516" s="5">
+        <f t="shared" si="21"/>
+        <v>1302279</v>
+      </c>
+      <c r="B516" s="5">
+        <v>2</v>
+      </c>
+      <c r="C516" s="5">
+        <v>79</v>
+      </c>
+      <c r="D516" s="5">
+        <v>1302</v>
+      </c>
+      <c r="E516" s="5" t="s">
+        <v>125</v>
+      </c>
+      <c r="F516" s="5" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="517" customFormat="1" spans="1:6">
+      <c r="A517" s="5">
+        <f t="shared" si="21"/>
+        <v>1302280</v>
+      </c>
+      <c r="B517" s="5">
+        <v>2</v>
+      </c>
+      <c r="C517" s="5">
+        <v>80</v>
+      </c>
+      <c r="D517" s="5">
+        <v>1302</v>
+      </c>
+      <c r="E517" s="5" t="s">
+        <v>125</v>
+      </c>
+      <c r="F517" s="5" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="518" customFormat="1" spans="1:6">
+      <c r="A518" s="5">
+        <f t="shared" si="21"/>
+        <v>1302281</v>
+      </c>
+      <c r="B518" s="5">
+        <v>2</v>
+      </c>
+      <c r="C518" s="5">
+        <v>81</v>
+      </c>
+      <c r="D518" s="5">
+        <v>1302</v>
+      </c>
+      <c r="E518" s="5" t="s">
+        <v>125</v>
+      </c>
+      <c r="F518" s="5" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="519" customFormat="1" spans="1:6">
+      <c r="A519" s="5">
+        <f t="shared" si="21"/>
+        <v>1302282</v>
+      </c>
+      <c r="B519" s="5">
+        <v>2</v>
+      </c>
+      <c r="C519" s="5">
+        <v>82</v>
+      </c>
+      <c r="D519" s="5">
+        <v>1302</v>
+      </c>
+      <c r="E519" s="5" t="s">
+        <v>125</v>
+      </c>
+      <c r="F519" s="5" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="520" customFormat="1" spans="1:6">
+      <c r="A520" s="5">
+        <f t="shared" si="21"/>
+        <v>1302283</v>
+      </c>
+      <c r="B520" s="5">
+        <v>2</v>
+      </c>
+      <c r="C520" s="5">
+        <v>83</v>
+      </c>
+      <c r="D520" s="5">
+        <v>1302</v>
+      </c>
+      <c r="E520" s="5" t="s">
+        <v>125</v>
+      </c>
+      <c r="F520" s="5" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="521" customFormat="1" spans="1:6">
+      <c r="A521" s="5">
+        <f t="shared" si="21"/>
+        <v>1302284</v>
+      </c>
+      <c r="B521" s="5">
+        <v>2</v>
+      </c>
+      <c r="C521" s="5">
+        <v>84</v>
+      </c>
+      <c r="D521" s="5">
+        <v>1302</v>
+      </c>
+      <c r="E521" s="5" t="s">
+        <v>125</v>
+      </c>
+      <c r="F521" s="5" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="522" customFormat="1" spans="1:6">
+      <c r="A522" s="5">
+        <f t="shared" si="21"/>
+        <v>1302285</v>
+      </c>
+      <c r="B522" s="5">
+        <v>2</v>
+      </c>
+      <c r="C522" s="5">
+        <v>85</v>
+      </c>
+      <c r="D522" s="5">
+        <v>1302</v>
+      </c>
+      <c r="E522" s="5" t="s">
+        <v>125</v>
+      </c>
+      <c r="F522" s="5" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="523" customFormat="1" spans="1:6">
+      <c r="A523" s="5">
+        <f t="shared" si="21"/>
+        <v>1302286</v>
+      </c>
+      <c r="B523" s="5">
+        <v>2</v>
+      </c>
+      <c r="C523" s="5">
+        <v>86</v>
+      </c>
+      <c r="D523" s="5">
+        <v>1302</v>
+      </c>
+      <c r="E523" s="5" t="s">
+        <v>125</v>
+      </c>
+      <c r="F523" s="5" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="524" customFormat="1" spans="1:6">
+      <c r="A524" s="5">
+        <f t="shared" si="21"/>
+        <v>1302287</v>
+      </c>
+      <c r="B524" s="5">
+        <v>2</v>
+      </c>
+      <c r="C524" s="5">
+        <v>87</v>
+      </c>
+      <c r="D524" s="5">
+        <v>1302</v>
+      </c>
+      <c r="E524" s="5" t="s">
+        <v>125</v>
+      </c>
+      <c r="F524" s="5" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="525" customFormat="1" spans="1:6">
+      <c r="A525" s="5">
+        <f t="shared" si="21"/>
+        <v>1302288</v>
+      </c>
+      <c r="B525" s="5">
+        <v>2</v>
+      </c>
+      <c r="C525" s="5">
+        <v>88</v>
+      </c>
+      <c r="D525" s="5">
+        <v>1302</v>
+      </c>
+      <c r="E525" s="5" t="s">
+        <v>125</v>
+      </c>
+      <c r="F525" s="5" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="526" customFormat="1" spans="1:6">
+      <c r="A526" s="5">
+        <f t="shared" si="21"/>
+        <v>1302289</v>
+      </c>
+      <c r="B526" s="5">
+        <v>2</v>
+      </c>
+      <c r="C526" s="5">
+        <v>89</v>
+      </c>
+      <c r="D526" s="5">
+        <v>1302</v>
+      </c>
+      <c r="E526" s="5" t="s">
+        <v>125</v>
+      </c>
+      <c r="F526" s="5" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="527" customFormat="1" spans="1:6">
+      <c r="A527" s="5">
+        <f t="shared" si="21"/>
+        <v>1302290</v>
+      </c>
+      <c r="B527" s="5">
+        <v>2</v>
+      </c>
+      <c r="C527" s="5">
+        <v>90</v>
+      </c>
+      <c r="D527" s="5">
+        <v>1302</v>
+      </c>
+      <c r="E527" s="5" t="s">
+        <v>125</v>
+      </c>
+      <c r="F527" s="5" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="528" customFormat="1" spans="1:6">
+      <c r="A528" s="5">
+        <f t="shared" si="21"/>
+        <v>1302291</v>
+      </c>
+      <c r="B528" s="5">
+        <v>2</v>
+      </c>
+      <c r="C528" s="5">
+        <v>91</v>
+      </c>
+      <c r="D528" s="5">
+        <v>1302</v>
+      </c>
+      <c r="E528" s="5" t="s">
+        <v>125</v>
+      </c>
+      <c r="F528" s="5" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="529" customFormat="1" spans="1:6">
+      <c r="A529" s="5">
+        <f t="shared" si="21"/>
+        <v>1302292</v>
+      </c>
+      <c r="B529" s="5">
+        <v>2</v>
+      </c>
+      <c r="C529" s="5">
+        <v>92</v>
+      </c>
+      <c r="D529" s="5">
+        <v>1302</v>
+      </c>
+      <c r="E529" s="5" t="s">
+        <v>125</v>
+      </c>
+      <c r="F529" s="5" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="530" customFormat="1" spans="1:6">
+      <c r="A530" s="5">
+        <f t="shared" si="21"/>
+        <v>1302293</v>
+      </c>
+      <c r="B530" s="5">
+        <v>2</v>
+      </c>
+      <c r="C530" s="5">
+        <v>93</v>
+      </c>
+      <c r="D530" s="5">
+        <v>1302</v>
+      </c>
+      <c r="E530" s="5" t="s">
+        <v>125</v>
+      </c>
+      <c r="F530" s="5" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="531" customFormat="1" spans="1:6">
+      <c r="A531" s="5">
+        <f t="shared" si="21"/>
+        <v>1302294</v>
+      </c>
+      <c r="B531" s="5">
+        <v>2</v>
+      </c>
+      <c r="C531" s="5">
+        <v>94</v>
+      </c>
+      <c r="D531" s="5">
+        <v>1302</v>
+      </c>
+      <c r="E531" s="5" t="s">
+        <v>125</v>
+      </c>
+      <c r="F531" s="5" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="532" customFormat="1" spans="1:6">
+      <c r="A532" s="5">
+        <f t="shared" si="21"/>
+        <v>1302295</v>
+      </c>
+      <c r="B532" s="5">
+        <v>2</v>
+      </c>
+      <c r="C532" s="5">
+        <v>95</v>
+      </c>
+      <c r="D532" s="5">
+        <v>1302</v>
+      </c>
+      <c r="E532" s="5" t="s">
+        <v>125</v>
+      </c>
+      <c r="F532" s="5" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="533" s="3" customFormat="1" spans="1:6">
+      <c r="A533" s="3">
+        <f>D533*1000+B533*100+C533</f>
+        <v>1301201</v>
+      </c>
+      <c r="B533" s="3">
+        <v>2</v>
+      </c>
+      <c r="C533" s="3">
+        <v>1</v>
+      </c>
+      <c r="D533" s="3">
+        <v>1301</v>
+      </c>
+      <c r="E533" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="F533" s="3" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="534" spans="1:6">
+      <c r="A534" s="3">
+        <f t="shared" ref="A534:A542" si="22">D534*1000+B534*100+C534</f>
+        <v>1301202</v>
+      </c>
+      <c r="B534" s="3">
+        <v>2</v>
+      </c>
+      <c r="C534" s="3">
+        <v>2</v>
+      </c>
+      <c r="D534" s="3">
+        <v>1301</v>
+      </c>
+      <c r="E534" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="F534" s="3" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="535" spans="1:6">
+      <c r="A535" s="3">
+        <f t="shared" si="22"/>
+        <v>1301203</v>
+      </c>
+      <c r="B535" s="3">
+        <v>2</v>
+      </c>
+      <c r="C535" s="3">
+        <v>3</v>
+      </c>
+      <c r="D535" s="3">
+        <v>1301</v>
+      </c>
+      <c r="E535" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="F535" s="3" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="536" spans="1:6">
+      <c r="A536" s="3">
+        <f t="shared" si="22"/>
+        <v>1301204</v>
+      </c>
+      <c r="B536" s="3">
+        <v>2</v>
+      </c>
+      <c r="C536" s="3">
+        <v>4</v>
+      </c>
+      <c r="D536" s="3">
+        <v>1301</v>
+      </c>
+      <c r="E536" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="F536" s="3" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="537" spans="1:6">
+      <c r="A537" s="3">
+        <f t="shared" si="22"/>
+        <v>1301205</v>
+      </c>
+      <c r="B537" s="3">
+        <v>2</v>
+      </c>
+      <c r="C537" s="3">
+        <v>5</v>
+      </c>
+      <c r="D537" s="3">
+        <v>1301</v>
+      </c>
+      <c r="E537" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="F537" s="3" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="538" spans="1:6">
+      <c r="A538" s="3">
+        <f t="shared" si="22"/>
+        <v>1301206</v>
+      </c>
+      <c r="B538" s="3">
+        <v>2</v>
+      </c>
+      <c r="C538" s="3">
+        <v>6</v>
+      </c>
+      <c r="D538" s="3">
+        <v>1301</v>
+      </c>
+      <c r="E538" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="F538" s="3" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="539" spans="1:6">
+      <c r="A539" s="3">
+        <f t="shared" si="22"/>
+        <v>1301207</v>
+      </c>
+      <c r="B539" s="3">
+        <v>2</v>
+      </c>
+      <c r="C539" s="3">
+        <v>7</v>
+      </c>
+      <c r="D539" s="3">
+        <v>1301</v>
+      </c>
+      <c r="E539" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="F539" s="3" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="540" spans="1:6">
+      <c r="A540" s="3">
+        <f t="shared" si="22"/>
+        <v>1301208</v>
+      </c>
+      <c r="B540" s="3">
+        <v>2</v>
+      </c>
+      <c r="C540" s="3">
+        <v>8</v>
+      </c>
+      <c r="D540" s="3">
+        <v>1301</v>
+      </c>
+      <c r="E540" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="F540" s="3" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="541" spans="1:6">
+      <c r="A541" s="3">
+        <f t="shared" si="22"/>
+        <v>1301209</v>
+      </c>
+      <c r="B541" s="3">
+        <v>2</v>
+      </c>
+      <c r="C541" s="3">
+        <v>9</v>
+      </c>
+      <c r="D541" s="3">
+        <v>1301</v>
+      </c>
+      <c r="E541" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="F541" s="3" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="542" spans="1:6">
+      <c r="A542" s="5">
+        <f t="shared" si="22"/>
         <v>1303201</v>
       </c>
-      <c r="B514" s="5">
-        <v>2</v>
-      </c>
-      <c r="C514" s="5">
-        <v>1</v>
-      </c>
-      <c r="D514" s="5">
+      <c r="B542" s="5">
+        <v>2</v>
+      </c>
+      <c r="C542" s="5">
+        <v>1</v>
+      </c>
+      <c r="D542" s="5">
         <v>1303</v>
       </c>
-      <c r="E514" s="5" t="s">
+      <c r="E542" s="5" t="s">
         <v>107</v>
       </c>
-      <c r="F514" s="5" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="515" spans="1:6">
-      <c r="A515" s="5">
-        <f t="shared" ref="A515:A525" si="22">D515*1000+B515*100+C515</f>
+      <c r="F542" s="5" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="543" spans="1:6">
+      <c r="A543" s="5">
+        <f t="shared" ref="A543:A553" si="23">D543*1000+B543*100+C543</f>
         <v>1303202</v>
       </c>
-      <c r="B515" s="5">
-        <v>2</v>
-      </c>
-      <c r="C515" s="5">
-        <v>2</v>
-      </c>
-      <c r="D515" s="5">
+      <c r="B543" s="5">
+        <v>2</v>
+      </c>
+      <c r="C543" s="5">
+        <v>2</v>
+      </c>
+      <c r="D543" s="5">
         <v>1303</v>
       </c>
-      <c r="E515" s="5" t="s">
+      <c r="E543" s="5" t="s">
         <v>109</v>
       </c>
-      <c r="F515" s="5" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="516" spans="1:6">
-      <c r="A516" s="5">
-        <f t="shared" si="22"/>
+      <c r="F543" s="5" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="544" spans="1:6">
+      <c r="A544" s="5">
+        <f t="shared" si="23"/>
         <v>1303203</v>
       </c>
-      <c r="B516" s="5">
-        <v>2</v>
-      </c>
-      <c r="C516" s="5">
+      <c r="B544" s="5">
+        <v>2</v>
+      </c>
+      <c r="C544" s="5">
         <v>3</v>
       </c>
-      <c r="D516" s="5">
+      <c r="D544" s="5">
         <v>1303</v>
       </c>
-      <c r="E516" s="5" t="s">
+      <c r="E544" s="5" t="s">
         <v>110</v>
       </c>
-      <c r="F516" s="5" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="517" spans="1:6">
-      <c r="A517" s="5">
-        <f t="shared" si="22"/>
+      <c r="F544" s="5" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="545" spans="1:6">
+      <c r="A545" s="5">
+        <f t="shared" si="23"/>
         <v>1303204</v>
       </c>
-      <c r="B517" s="5">
-        <v>2</v>
-      </c>
-      <c r="C517" s="5">
+      <c r="B545" s="5">
+        <v>2</v>
+      </c>
+      <c r="C545" s="5">
         <v>4</v>
       </c>
-      <c r="D517" s="5">
+      <c r="D545" s="5">
         <v>1303</v>
       </c>
-      <c r="E517" s="5" t="s">
+      <c r="E545" s="5" t="s">
         <v>111</v>
       </c>
-      <c r="F517" s="5" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="518" spans="1:6">
-      <c r="A518" s="5">
-        <f t="shared" si="22"/>
+      <c r="F545" s="5" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="546" spans="1:6">
+      <c r="A546" s="5">
+        <f t="shared" si="23"/>
         <v>1303205</v>
       </c>
-      <c r="B518" s="5">
-        <v>2</v>
-      </c>
-      <c r="C518" s="5">
+      <c r="B546" s="5">
+        <v>2</v>
+      </c>
+      <c r="C546" s="5">
         <v>5</v>
       </c>
-      <c r="D518" s="5">
+      <c r="D546" s="5">
         <v>1303</v>
       </c>
-      <c r="E518" s="5" t="s">
+      <c r="E546" s="5" t="s">
         <v>112</v>
       </c>
-      <c r="F518" s="5" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="519" spans="1:6">
-      <c r="A519" s="5">
-        <f t="shared" si="22"/>
+      <c r="F546" s="5" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="547" spans="1:6">
+      <c r="A547" s="5">
+        <f t="shared" si="23"/>
         <v>1303206</v>
       </c>
-      <c r="B519" s="5">
-        <v>2</v>
-      </c>
-      <c r="C519" s="5">
+      <c r="B547" s="5">
+        <v>2</v>
+      </c>
+      <c r="C547" s="5">
         <v>6</v>
       </c>
-      <c r="D519" s="5">
+      <c r="D547" s="5">
         <v>1303</v>
       </c>
-      <c r="E519" s="5" t="s">
+      <c r="E547" s="5" t="s">
         <v>113</v>
       </c>
-      <c r="F519" s="5" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="520" spans="1:6">
-      <c r="A520" s="5">
-        <f t="shared" si="22"/>
+      <c r="F547" s="5" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="548" spans="1:6">
+      <c r="A548" s="5">
+        <f t="shared" si="23"/>
         <v>1303207</v>
       </c>
-      <c r="B520" s="5">
-        <v>2</v>
-      </c>
-      <c r="C520" s="5">
+      <c r="B548" s="5">
+        <v>2</v>
+      </c>
+      <c r="C548" s="5">
         <v>7</v>
       </c>
-      <c r="D520" s="5">
+      <c r="D548" s="5">
         <v>1303</v>
       </c>
-      <c r="E520" s="5" t="s">
+      <c r="E548" s="5" t="s">
         <v>114</v>
       </c>
-      <c r="F520" s="5" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="521" spans="1:6">
-      <c r="A521" s="5">
-        <f t="shared" si="22"/>
+      <c r="F548" s="5" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="549" spans="1:6">
+      <c r="A549" s="5">
+        <f t="shared" si="23"/>
         <v>1303208</v>
       </c>
-      <c r="B521" s="5">
-        <v>2</v>
-      </c>
-      <c r="C521" s="5">
+      <c r="B549" s="5">
+        <v>2</v>
+      </c>
+      <c r="C549" s="5">
         <v>8</v>
       </c>
-      <c r="D521" s="5">
+      <c r="D549" s="5">
         <v>1303</v>
       </c>
-      <c r="E521" s="5" t="s">
+      <c r="E549" s="5" t="s">
         <v>115</v>
       </c>
-      <c r="F521" s="5" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="522" spans="1:6">
-      <c r="A522" s="5">
-        <f t="shared" si="22"/>
+      <c r="F549" s="5" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="550" spans="1:6">
+      <c r="A550" s="5">
+        <f t="shared" si="23"/>
         <v>1303209</v>
       </c>
-      <c r="B522" s="5">
-        <v>2</v>
-      </c>
-      <c r="C522" s="5">
+      <c r="B550" s="5">
+        <v>2</v>
+      </c>
+      <c r="C550" s="5">
         <v>9</v>
       </c>
-      <c r="D522" s="5">
+      <c r="D550" s="5">
         <v>1303</v>
       </c>
-      <c r="E522" s="5" t="s">
+      <c r="E550" s="5" t="s">
         <v>116</v>
       </c>
-      <c r="F522" s="5" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="523" spans="1:6">
-      <c r="A523" s="5">
-        <f t="shared" si="22"/>
+      <c r="F550" s="5" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="551" spans="1:6">
+      <c r="A551" s="5">
+        <f t="shared" si="23"/>
         <v>1303210</v>
       </c>
-      <c r="B523" s="5">
-        <v>2</v>
-      </c>
-      <c r="C523" s="5">
+      <c r="B551" s="5">
+        <v>2</v>
+      </c>
+      <c r="C551" s="5">
         <v>10</v>
       </c>
-      <c r="D523" s="5">
+      <c r="D551" s="5">
         <v>1303</v>
       </c>
-      <c r="E523" s="5" t="s">
+      <c r="E551" s="5" t="s">
         <v>117</v>
       </c>
-      <c r="F523" s="5" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="524" spans="1:6">
-      <c r="A524" s="5">
-        <f t="shared" si="22"/>
+      <c r="F551" s="5" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="552" spans="1:6">
+      <c r="A552" s="5">
+        <f t="shared" si="23"/>
         <v>1303211</v>
       </c>
-      <c r="B524" s="5">
-        <v>2</v>
-      </c>
-      <c r="C524" s="5">
+      <c r="B552" s="5">
+        <v>2</v>
+      </c>
+      <c r="C552" s="5">
         <v>11</v>
       </c>
-      <c r="D524" s="5">
+      <c r="D552" s="5">
         <v>1303</v>
       </c>
-      <c r="E524" s="5" t="s">
+      <c r="E552" s="5" t="s">
         <v>118</v>
       </c>
-      <c r="F524" s="5" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="525" spans="1:6">
-      <c r="A525" s="3">
-        <f t="shared" si="22"/>
+      <c r="F552" s="5" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="553" spans="1:6">
+      <c r="A553" s="3">
+        <f t="shared" si="23"/>
         <v>1304201</v>
       </c>
-      <c r="B525" s="3">
-        <v>2</v>
-      </c>
-      <c r="C525" s="3">
-        <v>1</v>
-      </c>
-      <c r="D525" s="3">
+      <c r="B553" s="3">
+        <v>2</v>
+      </c>
+      <c r="C553" s="3">
+        <v>1</v>
+      </c>
+      <c r="D553" s="3">
         <v>1304</v>
       </c>
-      <c r="E525" s="3" t="s">
+      <c r="E553" s="3" t="s">
         <v>107</v>
       </c>
-      <c r="F525" s="3" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="526" spans="1:6">
-      <c r="A526" s="3">
-        <f t="shared" ref="A526:A533" si="23">D526*1000+B526*100+C526</f>
+      <c r="F553" s="3" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="554" spans="1:6">
+      <c r="A554" s="3">
+        <f t="shared" ref="A554:A561" si="24">D554*1000+B554*100+C554</f>
         <v>1304202</v>
       </c>
-      <c r="B526" s="3">
-        <v>2</v>
-      </c>
-      <c r="C526" s="3">
-        <v>2</v>
-      </c>
-      <c r="D526" s="3">
+      <c r="B554" s="3">
+        <v>2</v>
+      </c>
+      <c r="C554" s="3">
+        <v>2</v>
+      </c>
+      <c r="D554" s="3">
         <v>1304</v>
       </c>
-      <c r="E526" s="3" t="s">
+      <c r="E554" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="F526" s="3" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="527" spans="1:6">
-      <c r="A527" s="3">
-        <f t="shared" si="23"/>
+      <c r="F554" s="3" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="555" spans="1:6">
+      <c r="A555" s="3">
+        <f t="shared" si="24"/>
         <v>1304203</v>
       </c>
-      <c r="B527" s="3">
-        <v>2</v>
-      </c>
-      <c r="C527" s="3">
+      <c r="B555" s="3">
+        <v>2</v>
+      </c>
+      <c r="C555" s="3">
         <v>3</v>
       </c>
-      <c r="D527" s="3">
+      <c r="D555" s="3">
         <v>1304</v>
       </c>
-      <c r="E527" s="3" t="s">
+      <c r="E555" s="3" t="s">
         <v>110</v>
       </c>
-      <c r="F527" s="3" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="528" spans="1:6">
-      <c r="A528" s="3">
-        <f t="shared" si="23"/>
+      <c r="F555" s="3" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="556" spans="1:6">
+      <c r="A556" s="3">
+        <f t="shared" si="24"/>
         <v>1304204</v>
       </c>
-      <c r="B528" s="3">
-        <v>2</v>
-      </c>
-      <c r="C528" s="3">
+      <c r="B556" s="3">
+        <v>2</v>
+      </c>
+      <c r="C556" s="3">
         <v>4</v>
       </c>
-      <c r="D528" s="3">
+      <c r="D556" s="3">
         <v>1304</v>
       </c>
-      <c r="E528" s="3" t="s">
+      <c r="E556" s="3" t="s">
         <v>111</v>
       </c>
-      <c r="F528" s="3" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="529" spans="1:6">
-      <c r="A529" s="3">
-        <f t="shared" si="23"/>
+      <c r="F556" s="3" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="557" spans="1:6">
+      <c r="A557" s="3">
+        <f t="shared" si="24"/>
         <v>1304205</v>
       </c>
-      <c r="B529" s="3">
-        <v>2</v>
-      </c>
-      <c r="C529" s="3">
+      <c r="B557" s="3">
+        <v>2</v>
+      </c>
+      <c r="C557" s="3">
         <v>5</v>
       </c>
-      <c r="D529" s="3">
+      <c r="D557" s="3">
         <v>1304</v>
       </c>
-      <c r="E529" s="3" t="s">
+      <c r="E557" s="3" t="s">
         <v>112</v>
       </c>
-      <c r="F529" s="3" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="530" spans="1:6">
-      <c r="A530" s="3">
-        <f t="shared" si="23"/>
+      <c r="F557" s="3" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="558" spans="1:6">
+      <c r="A558" s="3">
+        <f t="shared" si="24"/>
         <v>1304206</v>
       </c>
-      <c r="B530" s="3">
-        <v>2</v>
-      </c>
-      <c r="C530" s="3">
+      <c r="B558" s="3">
+        <v>2</v>
+      </c>
+      <c r="C558" s="3">
         <v>6</v>
       </c>
-      <c r="D530" s="3">
+      <c r="D558" s="3">
         <v>1304</v>
       </c>
-      <c r="E530" s="3" t="s">
+      <c r="E558" s="3" t="s">
         <v>113</v>
       </c>
-      <c r="F530" s="3" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="531" spans="1:6">
-      <c r="A531" s="3">
-        <f t="shared" si="23"/>
+      <c r="F558" s="3" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="559" spans="1:6">
+      <c r="A559" s="3">
+        <f t="shared" si="24"/>
         <v>1304207</v>
       </c>
-      <c r="B531" s="3">
-        <v>2</v>
-      </c>
-      <c r="C531" s="3">
+      <c r="B559" s="3">
+        <v>2</v>
+      </c>
+      <c r="C559" s="3">
         <v>7</v>
       </c>
-      <c r="D531" s="3">
+      <c r="D559" s="3">
         <v>1304</v>
       </c>
-      <c r="E531" s="3" t="s">
+      <c r="E559" s="3" t="s">
         <v>114</v>
       </c>
-      <c r="F531" s="3" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="532" spans="1:6">
-      <c r="A532" s="3">
-        <f t="shared" si="23"/>
+      <c r="F559" s="3" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="560" spans="1:6">
+      <c r="A560" s="3">
+        <f t="shared" si="24"/>
         <v>1304208</v>
       </c>
-      <c r="B532" s="3">
-        <v>2</v>
-      </c>
-      <c r="C532" s="3">
+      <c r="B560" s="3">
+        <v>2</v>
+      </c>
+      <c r="C560" s="3">
         <v>8</v>
       </c>
-      <c r="D532" s="3">
+      <c r="D560" s="3">
         <v>1304</v>
       </c>
-      <c r="E532" s="3" t="s">
+      <c r="E560" s="3" t="s">
         <v>115</v>
       </c>
-      <c r="F532" s="3" t="s">
-        <v>126</v>
+      <c r="F560" s="3" t="s">
+        <v>147</v>
       </c>
     </row>
   </sheetData>

--- a/hall/resources/sample/BuildingEquipmentTable.xlsx
+++ b/hall/resources/sample/BuildingEquipmentTable.xlsx
@@ -56,7 +56,8 @@
           </rPr>
           <t xml:space="preserve">
 1-交互设备
-2-装饰物</t>
+2-装饰物
+4-等待点位</t>
         </r>
       </text>
     </comment>
@@ -1764,11 +1765,10 @@
     <col min="5" max="5" width="14.875" style="2" customWidth="1"/>
     <col min="6" max="6" width="30.25" style="2" customWidth="1"/>
     <col min="7" max="7" width="10.625" style="2" customWidth="1"/>
-    <col min="8" max="8" width="13.75" style="2" customWidth="1"/>
-    <col min="9" max="16384" width="9" style="2"/>
+    <col min="8" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="15" spans="1:7">
+    <row r="1" s="1" customFormat="1" spans="1:7">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1791,7 +1791,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" s="1" customFormat="1" ht="15" spans="1:7">
+    <row r="2" s="1" customFormat="1" spans="1:7">
       <c r="A2" s="1" t="s">
         <v>7</v>
       </c>
@@ -1806,7 +1806,7 @@
       </c>
       <c r="E2" s="4"/>
     </row>
-    <row r="3" s="1" customFormat="1" ht="15" spans="1:7">
+    <row r="3" s="1" customFormat="1" spans="1:7">
       <c r="A3" s="1" t="s">
         <v>8</v>
       </c>
@@ -2111,7 +2111,7 @@
     </row>
     <row r="17" s="2" customFormat="1" spans="1:7">
       <c r="A17" s="2">
-        <f>D17*1000+B17*100+C17</f>
+        <f t="shared" si="0"/>
         <v>1101251</v>
       </c>
       <c r="B17" s="2">
@@ -2135,7 +2135,7 @@
     </row>
     <row r="18" s="2" customFormat="1" spans="1:7">
       <c r="A18" s="2">
-        <f>D18*1000+B18*100+C18</f>
+        <f t="shared" si="0"/>
         <v>1101252</v>
       </c>
       <c r="B18" s="2">
@@ -2159,7 +2159,7 @@
     </row>
     <row r="19" s="2" customFormat="1" spans="1:7">
       <c r="A19" s="2">
-        <f>D19*1000+B19*100+C19</f>
+        <f t="shared" si="0"/>
         <v>1101253</v>
       </c>
       <c r="B19" s="2">
@@ -2183,7 +2183,7 @@
     </row>
     <row r="20" s="2" customFormat="1" spans="1:7">
       <c r="A20" s="2">
-        <f>D20*1000+B20*100+C20</f>
+        <f t="shared" si="0"/>
         <v>1101254</v>
       </c>
       <c r="B20" s="2">
@@ -2207,7 +2207,7 @@
     </row>
     <row r="21" s="2" customFormat="1" spans="1:7">
       <c r="A21" s="2">
-        <f>D21*1000+B21*100+C21</f>
+        <f t="shared" si="0"/>
         <v>1101255</v>
       </c>
       <c r="B21" s="2">
@@ -2231,7 +2231,7 @@
     </row>
     <row r="22" s="2" customFormat="1" spans="1:7">
       <c r="A22" s="2">
-        <f>D22*1000+B22*100+C22</f>
+        <f t="shared" si="0"/>
         <v>1101256</v>
       </c>
       <c r="B22" s="2">
@@ -2255,7 +2255,7 @@
     </row>
     <row r="23" s="2" customFormat="1" spans="1:7">
       <c r="A23" s="2">
-        <f>D23*1000+B23*100+C23</f>
+        <f t="shared" si="0"/>
         <v>1101257</v>
       </c>
       <c r="B23" s="2">
@@ -2279,7 +2279,7 @@
     </row>
     <row r="24" s="2" customFormat="1" spans="1:7">
       <c r="A24" s="2">
-        <f>D24*1000+B24*100+C24</f>
+        <f t="shared" si="0"/>
         <v>1101258</v>
       </c>
       <c r="B24" s="2">
@@ -2303,7 +2303,7 @@
     </row>
     <row r="25" s="2" customFormat="1" spans="1:7">
       <c r="A25" s="2">
-        <f>D25*1000+B25*100+C25</f>
+        <f t="shared" si="0"/>
         <v>1101259</v>
       </c>
       <c r="B25" s="2">
@@ -2327,7 +2327,7 @@
     </row>
     <row r="26" s="2" customFormat="1" spans="1:7">
       <c r="A26" s="2">
-        <f>D26*1000+B26*100+C26</f>
+        <f t="shared" si="0"/>
         <v>1101260</v>
       </c>
       <c r="B26" s="2">
@@ -2351,7 +2351,7 @@
     </row>
     <row r="27" s="2" customFormat="1" spans="1:7">
       <c r="A27" s="2">
-        <f t="shared" ref="A27:A45" si="1">D27*1000+B27*100+C27</f>
+        <f t="shared" ref="A27:A54" si="1">D27*1000+B27*100+C27</f>
         <v>1101261</v>
       </c>
       <c r="B27" s="2">
@@ -2735,7 +2735,7 @@
     </row>
     <row r="43" spans="1:7">
       <c r="A43" s="2">
-        <f>D43*1000+B43*100+C43</f>
+        <f t="shared" ref="A43:A54" si="2">D43*1000+B43*100+C43</f>
         <v>1102101</v>
       </c>
       <c r="B43" s="2">
@@ -2759,7 +2759,7 @@
     </row>
     <row r="44" spans="1:7">
       <c r="A44" s="2">
-        <f>D44*1000+B44*100+C44</f>
+        <f t="shared" si="2"/>
         <v>1102102</v>
       </c>
       <c r="B44" s="2">
@@ -2783,7 +2783,7 @@
     </row>
     <row r="45" spans="1:7">
       <c r="A45" s="2">
-        <f>D45*1000+B45*100+C45</f>
+        <f t="shared" si="2"/>
         <v>1102103</v>
       </c>
       <c r="B45" s="2">
@@ -2807,7 +2807,7 @@
     </row>
     <row r="46" spans="1:7">
       <c r="A46" s="2">
-        <f>D46*1000+B46*100+C46</f>
+        <f t="shared" si="2"/>
         <v>1102104</v>
       </c>
       <c r="B46" s="2">
@@ -2831,7 +2831,7 @@
     </row>
     <row r="47" spans="1:7">
       <c r="A47" s="2">
-        <f>D47*1000+B47*100+C47</f>
+        <f t="shared" si="2"/>
         <v>1102105</v>
       </c>
       <c r="B47" s="2">
@@ -2855,7 +2855,7 @@
     </row>
     <row r="48" spans="1:7">
       <c r="A48" s="2">
-        <f>D48*1000+B48*100+C48</f>
+        <f t="shared" si="2"/>
         <v>1102106</v>
       </c>
       <c r="B48" s="2">
@@ -2879,7 +2879,7 @@
     </row>
     <row r="49" spans="1:7">
       <c r="A49" s="2">
-        <f>D49*1000+B49*100+C49</f>
+        <f t="shared" si="2"/>
         <v>1102107</v>
       </c>
       <c r="B49" s="2">
@@ -2903,7 +2903,7 @@
     </row>
     <row r="50" spans="1:7">
       <c r="A50" s="2">
-        <f>D50*1000+B50*100+C50</f>
+        <f t="shared" si="2"/>
         <v>1102108</v>
       </c>
       <c r="B50" s="2">
@@ -2927,7 +2927,7 @@
     </row>
     <row r="51" spans="1:7">
       <c r="A51" s="2">
-        <f>D51*1000+B51*100+C51</f>
+        <f t="shared" si="2"/>
         <v>1102109</v>
       </c>
       <c r="B51" s="2">
@@ -2951,7 +2951,7 @@
     </row>
     <row r="52" spans="1:7">
       <c r="A52" s="2">
-        <f>D52*1000+B52*100+C52</f>
+        <f t="shared" si="2"/>
         <v>1102110</v>
       </c>
       <c r="B52" s="2">
@@ -2975,7 +2975,7 @@
     </row>
     <row r="53" spans="1:7">
       <c r="A53" s="2">
-        <f>D53*1000+B53*100+C53</f>
+        <f t="shared" si="2"/>
         <v>1102111</v>
       </c>
       <c r="B53" s="2">
@@ -2999,7 +2999,7 @@
     </row>
     <row r="54" spans="1:7">
       <c r="A54" s="2">
-        <f>D54*1000+B54*100+C54</f>
+        <f t="shared" si="2"/>
         <v>1102112</v>
       </c>
       <c r="B54" s="2">
@@ -3023,7 +3023,7 @@
     </row>
     <row r="55" spans="1:7">
       <c r="A55" s="2">
-        <f t="shared" ref="A55:A72" si="2">D55*1000+B55*100+C55</f>
+        <f t="shared" ref="A55:A90" si="3">D55*1000+B55*100+C55</f>
         <v>1102251</v>
       </c>
       <c r="B55" s="2">
@@ -3047,7 +3047,7 @@
     </row>
     <row r="56" spans="1:7">
       <c r="A56" s="2">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>1102252</v>
       </c>
       <c r="B56" s="2">
@@ -3071,7 +3071,7 @@
     </row>
     <row r="57" spans="1:7">
       <c r="A57" s="2">
-        <f>D57*1000+B57*100+C57</f>
+        <f t="shared" si="3"/>
         <v>1102253</v>
       </c>
       <c r="B57" s="2">
@@ -3095,7 +3095,7 @@
     </row>
     <row r="58" spans="1:7">
       <c r="A58" s="2">
-        <f>D58*1000+B58*100+C58</f>
+        <f t="shared" si="3"/>
         <v>1102254</v>
       </c>
       <c r="B58" s="2">
@@ -3119,7 +3119,7 @@
     </row>
     <row r="59" spans="1:7">
       <c r="A59" s="2">
-        <f>D59*1000+B59*100+C59</f>
+        <f t="shared" si="3"/>
         <v>1102255</v>
       </c>
       <c r="B59" s="2">
@@ -3143,7 +3143,7 @@
     </row>
     <row r="60" spans="1:7">
       <c r="A60" s="2">
-        <f>D60*1000+B60*100+C60</f>
+        <f t="shared" si="3"/>
         <v>1102256</v>
       </c>
       <c r="B60" s="2">
@@ -3167,7 +3167,7 @@
     </row>
     <row r="61" spans="1:7">
       <c r="A61" s="2">
-        <f>D61*1000+B61*100+C61</f>
+        <f t="shared" si="3"/>
         <v>1102257</v>
       </c>
       <c r="B61" s="2">
@@ -3191,7 +3191,7 @@
     </row>
     <row r="62" spans="1:7">
       <c r="A62" s="2">
-        <f>D62*1000+B62*100+C62</f>
+        <f t="shared" si="3"/>
         <v>1102258</v>
       </c>
       <c r="B62" s="2">
@@ -3215,7 +3215,7 @@
     </row>
     <row r="63" spans="1:7">
       <c r="A63" s="2">
-        <f>D63*1000+B63*100+C63</f>
+        <f t="shared" si="3"/>
         <v>1102259</v>
       </c>
       <c r="B63" s="2">
@@ -3239,7 +3239,7 @@
     </row>
     <row r="64" spans="1:7">
       <c r="A64" s="2">
-        <f>D64*1000+B64*100+C64</f>
+        <f t="shared" si="3"/>
         <v>1102260</v>
       </c>
       <c r="B64" s="2">
@@ -3263,7 +3263,7 @@
     </row>
     <row r="65" spans="1:7">
       <c r="A65" s="2">
-        <f>D65*1000+B65*100+C65</f>
+        <f t="shared" si="3"/>
         <v>1102261</v>
       </c>
       <c r="B65" s="2">
@@ -3287,7 +3287,7 @@
     </row>
     <row r="66" spans="1:7">
       <c r="A66" s="2">
-        <f>D66*1000+B66*100+C66</f>
+        <f t="shared" si="3"/>
         <v>1102262</v>
       </c>
       <c r="B66" s="2">
@@ -3311,7 +3311,7 @@
     </row>
     <row r="67" s="3" customFormat="1" spans="1:7">
       <c r="A67" s="3">
-        <f>D67*1000+B67*100+C67</f>
+        <f t="shared" si="3"/>
         <v>1102263</v>
       </c>
       <c r="B67" s="3">
@@ -3335,7 +3335,7 @@
     </row>
     <row r="68" spans="1:7">
       <c r="A68" s="2">
-        <f>D68*1000+B68*100+C68</f>
+        <f t="shared" si="3"/>
         <v>1102264</v>
       </c>
       <c r="B68" s="2">
@@ -3359,7 +3359,7 @@
     </row>
     <row r="69" spans="1:7">
       <c r="A69" s="2">
-        <f>D69*1000+B69*100+C69</f>
+        <f t="shared" si="3"/>
         <v>1102265</v>
       </c>
       <c r="B69" s="2">
@@ -3383,7 +3383,7 @@
     </row>
     <row r="70" spans="1:7">
       <c r="A70" s="2">
-        <f>D70*1000+B70*100+C70</f>
+        <f t="shared" si="3"/>
         <v>1102266</v>
       </c>
       <c r="B70" s="2">
@@ -3407,7 +3407,7 @@
     </row>
     <row r="71" spans="1:7">
       <c r="A71" s="2">
-        <f>D71*1000+B71*100+C71</f>
+        <f t="shared" si="3"/>
         <v>1102267</v>
       </c>
       <c r="B71" s="2">
@@ -3431,7 +3431,7 @@
     </row>
     <row r="72" spans="1:7">
       <c r="A72" s="2">
-        <f>D72*1000+B72*100+C72</f>
+        <f t="shared" si="3"/>
         <v>1102268</v>
       </c>
       <c r="B72" s="2">
@@ -3455,7 +3455,7 @@
     </row>
     <row r="73" spans="1:7">
       <c r="A73" s="2">
-        <f>D73*1000+B73*100+C73</f>
+        <f t="shared" si="3"/>
         <v>1102269</v>
       </c>
       <c r="B73" s="2">
@@ -3479,7 +3479,7 @@
     </row>
     <row r="74" spans="1:7">
       <c r="A74" s="2">
-        <f>D74*1000+B74*100+C74</f>
+        <f t="shared" si="3"/>
         <v>1102270</v>
       </c>
       <c r="B74" s="2">
@@ -3503,7 +3503,7 @@
     </row>
     <row r="75" spans="1:7">
       <c r="A75" s="2">
-        <f>D75*1000+B75*100+C75</f>
+        <f t="shared" si="3"/>
         <v>1102271</v>
       </c>
       <c r="B75" s="2">
@@ -3527,7 +3527,7 @@
     </row>
     <row r="76" spans="1:7">
       <c r="A76" s="2">
-        <f>D76*1000+B76*100+C76</f>
+        <f t="shared" si="3"/>
         <v>1102272</v>
       </c>
       <c r="B76" s="2">
@@ -3551,7 +3551,7 @@
     </row>
     <row r="77" spans="1:7">
       <c r="A77" s="2">
-        <f>D77*1000+B77*100+C77</f>
+        <f t="shared" si="3"/>
         <v>1102273</v>
       </c>
       <c r="B77" s="2">
@@ -3575,7 +3575,7 @@
     </row>
     <row r="78" spans="1:7">
       <c r="A78" s="2">
-        <f>D78*1000+B78*100+C78</f>
+        <f t="shared" si="3"/>
         <v>1102274</v>
       </c>
       <c r="B78" s="2">
@@ -3599,7 +3599,7 @@
     </row>
     <row r="79" spans="1:7">
       <c r="A79" s="2">
-        <f>D79*1000+B79*100+C79</f>
+        <f t="shared" si="3"/>
         <v>1102275</v>
       </c>
       <c r="B79" s="2">
@@ -3623,7 +3623,7 @@
     </row>
     <row r="80" spans="1:7">
       <c r="A80" s="2">
-        <f>D80*1000+B80*100+C80</f>
+        <f t="shared" si="3"/>
         <v>1102276</v>
       </c>
       <c r="B80" s="2">
@@ -3647,7 +3647,7 @@
     </row>
     <row r="81" spans="1:7">
       <c r="A81" s="5">
-        <f>D81*1000+B81*100+C81</f>
+        <f t="shared" ref="A81:A90" si="4">D81*1000+B81*100+C81</f>
         <v>1103101</v>
       </c>
       <c r="B81" s="5">
@@ -3671,7 +3671,7 @@
     </row>
     <row r="82" spans="1:7">
       <c r="A82" s="5">
-        <f>D82*1000+B82*100+C82</f>
+        <f t="shared" si="4"/>
         <v>1103102</v>
       </c>
       <c r="B82" s="5">
@@ -3695,7 +3695,7 @@
     </row>
     <row r="83" spans="1:7">
       <c r="A83" s="5">
-        <f>D83*1000+B83*100+C83</f>
+        <f t="shared" si="4"/>
         <v>1103103</v>
       </c>
       <c r="B83" s="5">
@@ -3719,7 +3719,7 @@
     </row>
     <row r="84" spans="1:7">
       <c r="A84" s="5">
-        <f>D84*1000+B84*100+C84</f>
+        <f t="shared" si="4"/>
         <v>1103104</v>
       </c>
       <c r="B84" s="5">
@@ -3743,7 +3743,7 @@
     </row>
     <row r="85" spans="1:7">
       <c r="A85" s="5">
-        <f>D85*1000+B85*100+C85</f>
+        <f t="shared" si="4"/>
         <v>1103105</v>
       </c>
       <c r="B85" s="5">
@@ -3767,7 +3767,7 @@
     </row>
     <row r="86" spans="1:7">
       <c r="A86" s="5">
-        <f>D86*1000+B86*100+C86</f>
+        <f t="shared" si="4"/>
         <v>1103106</v>
       </c>
       <c r="B86" s="5">
@@ -3791,7 +3791,7 @@
     </row>
     <row r="87" spans="1:7">
       <c r="A87" s="5">
-        <f>D87*1000+B87*100+C87</f>
+        <f t="shared" si="4"/>
         <v>1103107</v>
       </c>
       <c r="B87" s="5">
@@ -3815,7 +3815,7 @@
     </row>
     <row r="88" spans="1:7">
       <c r="A88" s="5">
-        <f>D88*1000+B88*100+C88</f>
+        <f t="shared" si="4"/>
         <v>1103108</v>
       </c>
       <c r="B88" s="5">
@@ -3839,7 +3839,7 @@
     </row>
     <row r="89" spans="1:7">
       <c r="A89" s="5">
-        <f>D89*1000+B89*100+C89</f>
+        <f t="shared" si="4"/>
         <v>1103109</v>
       </c>
       <c r="B89" s="5">
@@ -3863,7 +3863,7 @@
     </row>
     <row r="90" spans="1:7">
       <c r="A90" s="5">
-        <f>D90*1000+B90*100+C90</f>
+        <f t="shared" si="4"/>
         <v>1103110</v>
       </c>
       <c r="B90" s="5">
@@ -3887,7 +3887,7 @@
     </row>
     <row r="91" spans="1:7">
       <c r="A91" s="5">
-        <f t="shared" ref="A91:A102" si="3">D91*1000+B91*100+C91</f>
+        <f t="shared" ref="A91:A115" si="5">D91*1000+B91*100+C91</f>
         <v>1103251</v>
       </c>
       <c r="B91" s="5">
@@ -3911,7 +3911,7 @@
     </row>
     <row r="92" spans="1:7">
       <c r="A92" s="5">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>1103252</v>
       </c>
       <c r="B92" s="5">
@@ -3935,7 +3935,7 @@
     </row>
     <row r="93" spans="1:7">
       <c r="A93" s="5">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>1103253</v>
       </c>
       <c r="B93" s="5">
@@ -3959,7 +3959,7 @@
     </row>
     <row r="94" spans="1:7">
       <c r="A94" s="5">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>1103254</v>
       </c>
       <c r="B94" s="5">
@@ -3983,7 +3983,7 @@
     </row>
     <row r="95" spans="1:7">
       <c r="A95" s="5">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>1103255</v>
       </c>
       <c r="B95" s="5">
@@ -4007,7 +4007,7 @@
     </row>
     <row r="96" spans="1:7">
       <c r="A96" s="5">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>1103256</v>
       </c>
       <c r="B96" s="5">
@@ -4031,7 +4031,7 @@
     </row>
     <row r="97" spans="1:7">
       <c r="A97" s="5">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>1103257</v>
       </c>
       <c r="B97" s="5">
@@ -4055,7 +4055,7 @@
     </row>
     <row r="98" spans="1:7">
       <c r="A98" s="5">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>1103258</v>
       </c>
       <c r="B98" s="5">
@@ -4079,7 +4079,7 @@
     </row>
     <row r="99" spans="1:7">
       <c r="A99" s="5">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>1103259</v>
       </c>
       <c r="B99" s="5">
@@ -4103,7 +4103,7 @@
     </row>
     <row r="100" spans="1:7">
       <c r="A100" s="5">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>1103260</v>
       </c>
       <c r="B100" s="5">
@@ -4127,7 +4127,7 @@
     </row>
     <row r="101" spans="1:7">
       <c r="A101" s="5">
-        <f t="shared" ref="A101:A131" si="4">D101*1000+B101*100+C101</f>
+        <f t="shared" si="5"/>
         <v>1103261</v>
       </c>
       <c r="B101" s="5">
@@ -4151,7 +4151,7 @@
     </row>
     <row r="102" spans="1:7">
       <c r="A102" s="5">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>1103262</v>
       </c>
       <c r="B102" s="5">
@@ -4175,7 +4175,7 @@
     </row>
     <row r="103" spans="1:7">
       <c r="A103" s="5">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>1103263</v>
       </c>
       <c r="B103" s="5">
@@ -4199,7 +4199,7 @@
     </row>
     <row r="104" spans="1:7">
       <c r="A104" s="5">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>1103264</v>
       </c>
       <c r="B104" s="5">
@@ -4223,7 +4223,7 @@
     </row>
     <row r="105" spans="1:7">
       <c r="A105" s="5">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>1103265</v>
       </c>
       <c r="B105" s="5">
@@ -4247,7 +4247,7 @@
     </row>
     <row r="106" spans="1:7">
       <c r="A106" s="5">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>1103266</v>
       </c>
       <c r="B106" s="5">
@@ -4271,7 +4271,7 @@
     </row>
     <row r="107" spans="1:7">
       <c r="A107" s="5">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>1103267</v>
       </c>
       <c r="B107" s="5">
@@ -4295,7 +4295,7 @@
     </row>
     <row r="108" spans="1:7">
       <c r="A108" s="5">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>1103268</v>
       </c>
       <c r="B108" s="5">
@@ -4319,7 +4319,7 @@
     </row>
     <row r="109" spans="1:7">
       <c r="A109" s="5">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>1103269</v>
       </c>
       <c r="B109" s="5">
@@ -4343,7 +4343,7 @@
     </row>
     <row r="110" spans="1:7">
       <c r="A110" s="5">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>1103270</v>
       </c>
       <c r="B110" s="5">
@@ -4367,7 +4367,7 @@
     </row>
     <row r="111" spans="1:7">
       <c r="A111" s="5">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>1103271</v>
       </c>
       <c r="B111" s="5">
@@ -4391,7 +4391,7 @@
     </row>
     <row r="112" spans="1:7">
       <c r="A112" s="5">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>1103272</v>
       </c>
       <c r="B112" s="5">
@@ -4415,7 +4415,7 @@
     </row>
     <row r="113" spans="1:7">
       <c r="A113" s="5">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>1103273</v>
       </c>
       <c r="B113" s="5">
@@ -4439,7 +4439,7 @@
     </row>
     <row r="114" spans="1:7">
       <c r="A114" s="5">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>1103274</v>
       </c>
       <c r="B114" s="5">
@@ -4463,7 +4463,7 @@
     </row>
     <row r="115" spans="1:7">
       <c r="A115" s="5">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>1103275</v>
       </c>
       <c r="B115" s="5">
@@ -4487,7 +4487,7 @@
     </row>
     <row r="116" spans="1:7">
       <c r="A116" s="2">
-        <f t="shared" si="4"/>
+        <f t="shared" ref="A116:A131" si="6">D116*1000+B116*100+C116</f>
         <v>1104101</v>
       </c>
       <c r="B116" s="2">
@@ -4511,7 +4511,7 @@
     </row>
     <row r="117" spans="1:7">
       <c r="A117" s="2">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>1104102</v>
       </c>
       <c r="B117" s="2">
@@ -4535,7 +4535,7 @@
     </row>
     <row r="118" spans="1:7">
       <c r="A118" s="2">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>1104103</v>
       </c>
       <c r="B118" s="2">
@@ -4559,7 +4559,7 @@
     </row>
     <row r="119" spans="1:7">
       <c r="A119" s="2">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>1104104</v>
       </c>
       <c r="B119" s="2">
@@ -4583,7 +4583,7 @@
     </row>
     <row r="120" spans="1:7">
       <c r="A120" s="2">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>1104105</v>
       </c>
       <c r="B120" s="2">
@@ -4607,7 +4607,7 @@
     </row>
     <row r="121" spans="1:7">
       <c r="A121" s="2">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>1104106</v>
       </c>
       <c r="B121" s="2">
@@ -4631,7 +4631,7 @@
     </row>
     <row r="122" spans="1:7">
       <c r="A122" s="2">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>1104107</v>
       </c>
       <c r="B122" s="2">
@@ -4655,7 +4655,7 @@
     </row>
     <row r="123" spans="1:7">
       <c r="A123" s="2">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>1104108</v>
       </c>
       <c r="B123" s="2">
@@ -4679,7 +4679,7 @@
     </row>
     <row r="124" spans="1:7">
       <c r="A124" s="2">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>1104109</v>
       </c>
       <c r="B124" s="2">
@@ -4703,7 +4703,7 @@
     </row>
     <row r="125" spans="1:7">
       <c r="A125" s="2">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>1104110</v>
       </c>
       <c r="B125" s="2">
@@ -4727,7 +4727,7 @@
     </row>
     <row r="126" spans="1:7">
       <c r="A126" s="2">
-        <f t="shared" ref="A126:A151" si="5">D126*1000+B126*100+C126</f>
+        <f t="shared" ref="A126:A151" si="7">D126*1000+B126*100+C126</f>
         <v>1104251</v>
       </c>
       <c r="B126" s="2">
@@ -4751,7 +4751,7 @@
     </row>
     <row r="127" spans="1:7">
       <c r="A127" s="2">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>1104252</v>
       </c>
       <c r="B127" s="2">
@@ -4775,7 +4775,7 @@
     </row>
     <row r="128" spans="1:7">
       <c r="A128" s="2">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>1104253</v>
       </c>
       <c r="B128" s="2">
@@ -4799,7 +4799,7 @@
     </row>
     <row r="129" spans="1:7">
       <c r="A129" s="2">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>1104254</v>
       </c>
       <c r="B129" s="2">
@@ -4823,7 +4823,7 @@
     </row>
     <row r="130" spans="1:7">
       <c r="A130" s="2">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>1104255</v>
       </c>
       <c r="B130" s="2">
@@ -4847,7 +4847,7 @@
     </row>
     <row r="131" spans="1:7">
       <c r="A131" s="2">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>1104256</v>
       </c>
       <c r="B131" s="2">
@@ -4871,7 +4871,7 @@
     </row>
     <row r="132" spans="1:7">
       <c r="A132" s="2">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>1104257</v>
       </c>
       <c r="B132" s="2">
@@ -4895,7 +4895,7 @@
     </row>
     <row r="133" spans="1:7">
       <c r="A133" s="2">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>1104258</v>
       </c>
       <c r="B133" s="2">
@@ -4919,7 +4919,7 @@
     </row>
     <row r="134" spans="1:7">
       <c r="A134" s="2">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>1104259</v>
       </c>
       <c r="B134" s="2">
@@ -4943,7 +4943,7 @@
     </row>
     <row r="135" spans="1:7">
       <c r="A135" s="2">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>1104260</v>
       </c>
       <c r="B135" s="2">
@@ -4967,7 +4967,7 @@
     </row>
     <row r="136" spans="1:7">
       <c r="A136" s="2">
-        <f t="shared" ref="A136:A173" si="6">D136*1000+B136*100+C136</f>
+        <f t="shared" si="7"/>
         <v>1104261</v>
       </c>
       <c r="B136" s="2">
@@ -4991,7 +4991,7 @@
     </row>
     <row r="137" spans="1:7">
       <c r="A137" s="2">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>1104262</v>
       </c>
       <c r="B137" s="2">
@@ -5015,7 +5015,7 @@
     </row>
     <row r="138" spans="1:7">
       <c r="A138" s="2">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>1104263</v>
       </c>
       <c r="B138" s="2">
@@ -5039,7 +5039,7 @@
     </row>
     <row r="139" spans="1:7">
       <c r="A139" s="2">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>1104264</v>
       </c>
       <c r="B139" s="2">
@@ -5063,7 +5063,7 @@
     </row>
     <row r="140" spans="1:7">
       <c r="A140" s="2">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>1104265</v>
       </c>
       <c r="B140" s="2">
@@ -5087,7 +5087,7 @@
     </row>
     <row r="141" spans="1:7">
       <c r="A141" s="2">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>1104266</v>
       </c>
       <c r="B141" s="2">
@@ -5111,7 +5111,7 @@
     </row>
     <row r="142" spans="1:7">
       <c r="A142" s="2">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>1104267</v>
       </c>
       <c r="B142" s="2">
@@ -5135,7 +5135,7 @@
     </row>
     <row r="143" spans="1:7">
       <c r="A143" s="2">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>1104268</v>
       </c>
       <c r="B143" s="2">
@@ -5159,7 +5159,7 @@
     </row>
     <row r="144" spans="1:7">
       <c r="A144" s="2">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>1104269</v>
       </c>
       <c r="B144" s="2">
@@ -5183,7 +5183,7 @@
     </row>
     <row r="145" spans="1:7">
       <c r="A145" s="2">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>1104270</v>
       </c>
       <c r="B145" s="2">
@@ -5207,7 +5207,7 @@
     </row>
     <row r="146" spans="1:7">
       <c r="A146" s="2">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>1104271</v>
       </c>
       <c r="B146" s="2">
@@ -5231,7 +5231,7 @@
     </row>
     <row r="147" spans="1:7">
       <c r="A147" s="2">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>1104272</v>
       </c>
       <c r="B147" s="2">
@@ -5255,7 +5255,7 @@
     </row>
     <row r="148" spans="1:7">
       <c r="A148" s="5">
-        <f t="shared" si="6"/>
+        <f t="shared" ref="A148:A181" si="8">D148*1000+B148*100+C148</f>
         <v>1105101</v>
       </c>
       <c r="B148" s="5">
@@ -5279,7 +5279,7 @@
     </row>
     <row r="149" spans="1:7">
       <c r="A149" s="5">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>1105102</v>
       </c>
       <c r="B149" s="5">
@@ -5303,7 +5303,7 @@
     </row>
     <row r="150" spans="1:7">
       <c r="A150" s="5">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>1105103</v>
       </c>
       <c r="B150" s="5">
@@ -5327,7 +5327,7 @@
     </row>
     <row r="151" spans="1:7">
       <c r="A151" s="5">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>1105104</v>
       </c>
       <c r="B151" s="5">
@@ -5351,7 +5351,7 @@
     </row>
     <row r="152" spans="1:7">
       <c r="A152" s="5">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>1105105</v>
       </c>
       <c r="B152" s="5">
@@ -5375,7 +5375,7 @@
     </row>
     <row r="153" spans="1:7">
       <c r="A153" s="5">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>1105106</v>
       </c>
       <c r="B153" s="5">
@@ -5399,7 +5399,7 @@
     </row>
     <row r="154" spans="1:7">
       <c r="A154" s="5">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>1105107</v>
       </c>
       <c r="B154" s="5">
@@ -5423,7 +5423,7 @@
     </row>
     <row r="155" spans="1:7">
       <c r="A155" s="5">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>1105108</v>
       </c>
       <c r="B155" s="5">
@@ -5447,7 +5447,7 @@
     </row>
     <row r="156" spans="1:7">
       <c r="A156" s="5">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>1105109</v>
       </c>
       <c r="B156" s="5">
@@ -5471,7 +5471,7 @@
     </row>
     <row r="157" spans="1:7">
       <c r="A157" s="5">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>1105110</v>
       </c>
       <c r="B157" s="5">
@@ -5495,7 +5495,7 @@
     </row>
     <row r="158" spans="1:7">
       <c r="A158" s="5">
-        <f>D158*1000+B158*100+C158</f>
+        <f t="shared" si="8"/>
         <v>1105251</v>
       </c>
       <c r="B158" s="5">
@@ -5519,7 +5519,7 @@
     </row>
     <row r="159" spans="1:7">
       <c r="A159" s="5">
-        <f>D159*1000+B159*100+C159</f>
+        <f t="shared" si="8"/>
         <v>1105252</v>
       </c>
       <c r="B159" s="5">
@@ -5543,7 +5543,7 @@
     </row>
     <row r="160" spans="1:7">
       <c r="A160" s="5">
-        <f>D160*1000+B160*100+C160</f>
+        <f t="shared" si="8"/>
         <v>1105253</v>
       </c>
       <c r="B160" s="5">
@@ -5567,7 +5567,7 @@
     </row>
     <row r="161" spans="1:7">
       <c r="A161" s="5">
-        <f>D161*1000+B161*100+C161</f>
+        <f t="shared" si="8"/>
         <v>1105254</v>
       </c>
       <c r="B161" s="5">
@@ -5591,7 +5591,7 @@
     </row>
     <row r="162" spans="1:7">
       <c r="A162" s="5">
-        <f>D162*1000+B162*100+C162</f>
+        <f t="shared" si="8"/>
         <v>1105255</v>
       </c>
       <c r="B162" s="5">
@@ -5615,7 +5615,7 @@
     </row>
     <row r="163" spans="1:7">
       <c r="A163" s="5">
-        <f>D163*1000+B163*100+C163</f>
+        <f t="shared" si="8"/>
         <v>1105256</v>
       </c>
       <c r="B163" s="5">
@@ -5639,7 +5639,7 @@
     </row>
     <row r="164" spans="1:7">
       <c r="A164" s="5">
-        <f>D164*1000+B164*100+C164</f>
+        <f t="shared" si="8"/>
         <v>1105257</v>
       </c>
       <c r="B164" s="5">
@@ -5663,7 +5663,7 @@
     </row>
     <row r="165" spans="1:7">
       <c r="A165" s="5">
-        <f>D165*1000+B165*100+C165</f>
+        <f t="shared" si="8"/>
         <v>1105258</v>
       </c>
       <c r="B165" s="5">
@@ -5687,7 +5687,7 @@
     </row>
     <row r="166" spans="1:7">
       <c r="A166" s="5">
-        <f>D166*1000+B166*100+C166</f>
+        <f t="shared" si="8"/>
         <v>1105259</v>
       </c>
       <c r="B166" s="5">
@@ -5711,7 +5711,7 @@
     </row>
     <row r="167" spans="1:7">
       <c r="A167" s="5">
-        <f>D167*1000+B167*100+C167</f>
+        <f t="shared" si="8"/>
         <v>1105260</v>
       </c>
       <c r="B167" s="5">
@@ -5735,7 +5735,7 @@
     </row>
     <row r="168" spans="1:7">
       <c r="A168" s="5">
-        <f>D168*1000+B168*100+C168</f>
+        <f t="shared" si="8"/>
         <v>1105261</v>
       </c>
       <c r="B168" s="5">
@@ -5759,7 +5759,7 @@
     </row>
     <row r="169" spans="1:7">
       <c r="A169" s="5">
-        <f>D169*1000+B169*100+C169</f>
+        <f t="shared" si="8"/>
         <v>1105262</v>
       </c>
       <c r="B169" s="5">
@@ -5783,7 +5783,7 @@
     </row>
     <row r="170" spans="1:7">
       <c r="A170" s="5">
-        <f>D170*1000+B170*100+C170</f>
+        <f t="shared" si="8"/>
         <v>1105263</v>
       </c>
       <c r="B170" s="5">
@@ -5807,7 +5807,7 @@
     </row>
     <row r="171" spans="1:7">
       <c r="A171" s="5">
-        <f>D171*1000+B171*100+C171</f>
+        <f t="shared" si="8"/>
         <v>1105264</v>
       </c>
       <c r="B171" s="5">
@@ -5831,7 +5831,7 @@
     </row>
     <row r="172" spans="1:7">
       <c r="A172" s="5">
-        <f>D172*1000+B172*100+C172</f>
+        <f t="shared" si="8"/>
         <v>1105265</v>
       </c>
       <c r="B172" s="5">
@@ -5855,7 +5855,7 @@
     </row>
     <row r="173" spans="1:7">
       <c r="A173" s="5">
-        <f>D173*1000+B173*100+C173</f>
+        <f t="shared" si="8"/>
         <v>1105266</v>
       </c>
       <c r="B173" s="5">
@@ -5879,7 +5879,7 @@
     </row>
     <row r="174" spans="1:7">
       <c r="A174" s="5">
-        <f>D174*1000+B174*100+C174</f>
+        <f t="shared" si="8"/>
         <v>1105267</v>
       </c>
       <c r="B174" s="5">
@@ -5903,7 +5903,7 @@
     </row>
     <row r="175" spans="1:7">
       <c r="A175" s="5">
-        <f>D175*1000+B175*100+C175</f>
+        <f t="shared" si="8"/>
         <v>1105268</v>
       </c>
       <c r="B175" s="5">
@@ -5927,7 +5927,7 @@
     </row>
     <row r="176" spans="1:7">
       <c r="A176" s="5">
-        <f>D176*1000+B176*100+C176</f>
+        <f t="shared" si="8"/>
         <v>1105269</v>
       </c>
       <c r="B176" s="5">
@@ -5951,7 +5951,7 @@
     </row>
     <row r="177" spans="1:7">
       <c r="A177" s="5">
-        <f>D177*1000+B177*100+C177</f>
+        <f t="shared" si="8"/>
         <v>1105270</v>
       </c>
       <c r="B177" s="5">
@@ -5975,7 +5975,7 @@
     </row>
     <row r="178" spans="1:7">
       <c r="A178" s="5">
-        <f>D178*1000+B178*100+C178</f>
+        <f t="shared" si="8"/>
         <v>1105271</v>
       </c>
       <c r="B178" s="5">
@@ -5999,7 +5999,7 @@
     </row>
     <row r="179" spans="1:7">
       <c r="A179" s="5">
-        <f>D179*1000+B179*100+C179</f>
+        <f t="shared" si="8"/>
         <v>1105272</v>
       </c>
       <c r="B179" s="5">
@@ -6023,7 +6023,7 @@
     </row>
     <row r="180" spans="1:7">
       <c r="A180" s="5">
-        <f>D180*1000+B180*100+C180</f>
+        <f t="shared" si="8"/>
         <v>1105273</v>
       </c>
       <c r="B180" s="5">
@@ -6047,7 +6047,7 @@
     </row>
     <row r="181" spans="1:7">
       <c r="A181" s="5">
-        <f>D181*1000+B181*100+C181</f>
+        <f t="shared" si="8"/>
         <v>1105274</v>
       </c>
       <c r="B181" s="5">
@@ -6071,7 +6071,7 @@
     </row>
     <row r="182" spans="1:7">
       <c r="A182" s="2">
-        <f t="shared" ref="A182:A197" si="7">D182*1000+B182*100+C182</f>
+        <f t="shared" ref="A182:A197" si="9">D182*1000+B182*100+C182</f>
         <v>1106101</v>
       </c>
       <c r="B182" s="2">
@@ -6095,7 +6095,7 @@
     </row>
     <row r="183" spans="1:7">
       <c r="A183" s="2">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>1106102</v>
       </c>
       <c r="B183" s="2">
@@ -6119,7 +6119,7 @@
     </row>
     <row r="184" spans="1:7">
       <c r="A184" s="2">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>1106103</v>
       </c>
       <c r="B184" s="2">
@@ -6143,7 +6143,7 @@
     </row>
     <row r="185" spans="1:7">
       <c r="A185" s="2">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>1106104</v>
       </c>
       <c r="B185" s="2">
@@ -6167,7 +6167,7 @@
     </row>
     <row r="186" spans="1:7">
       <c r="A186" s="2">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>1106105</v>
       </c>
       <c r="B186" s="2">
@@ -6191,7 +6191,7 @@
     </row>
     <row r="187" spans="1:7">
       <c r="A187" s="2">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>1106106</v>
       </c>
       <c r="B187" s="2">
@@ -6215,7 +6215,7 @@
     </row>
     <row r="188" spans="1:7">
       <c r="A188" s="2">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>1106107</v>
       </c>
       <c r="B188" s="2">
@@ -6239,7 +6239,7 @@
     </row>
     <row r="189" spans="1:7">
       <c r="A189" s="2">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>1106108</v>
       </c>
       <c r="B189" s="2">
@@ -6263,7 +6263,7 @@
     </row>
     <row r="190" spans="1:7">
       <c r="A190" s="2">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>1106109</v>
       </c>
       <c r="B190" s="2">
@@ -6287,7 +6287,7 @@
     </row>
     <row r="191" spans="1:7">
       <c r="A191" s="2">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>1106110</v>
       </c>
       <c r="B191" s="2">
@@ -6311,7 +6311,7 @@
     </row>
     <row r="192" spans="1:7">
       <c r="A192" s="2">
-        <f t="shared" ref="A192:A225" si="8">D192*1000+B192*100+C192</f>
+        <f t="shared" ref="A192:A225" si="10">D192*1000+B192*100+C192</f>
         <v>1106251</v>
       </c>
       <c r="B192" s="2">
@@ -6335,7 +6335,7 @@
     </row>
     <row r="193" spans="1:7">
       <c r="A193" s="2">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>1106252</v>
       </c>
       <c r="B193" s="2">
@@ -6359,7 +6359,7 @@
     </row>
     <row r="194" spans="1:7">
       <c r="A194" s="2">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>1106253</v>
       </c>
       <c r="B194" s="2">
@@ -6383,7 +6383,7 @@
     </row>
     <row r="195" spans="1:7">
       <c r="A195" s="2">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>1106254</v>
       </c>
       <c r="B195" s="2">
@@ -6407,7 +6407,7 @@
     </row>
     <row r="196" spans="1:7">
       <c r="A196" s="2">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>1106255</v>
       </c>
       <c r="B196" s="2">
@@ -6431,7 +6431,7 @@
     </row>
     <row r="197" spans="1:7">
       <c r="A197" s="2">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>1106256</v>
       </c>
       <c r="B197" s="2">
@@ -6455,7 +6455,7 @@
     </row>
     <row r="198" spans="1:7">
       <c r="A198" s="2">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>1106257</v>
       </c>
       <c r="B198" s="2">
@@ -6479,7 +6479,7 @@
     </row>
     <row r="199" spans="1:7">
       <c r="A199" s="2">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>1106258</v>
       </c>
       <c r="B199" s="2">
@@ -6503,7 +6503,7 @@
     </row>
     <row r="200" spans="1:7">
       <c r="A200" s="2">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>1106259</v>
       </c>
       <c r="B200" s="2">
@@ -6527,7 +6527,7 @@
     </row>
     <row r="201" spans="1:7">
       <c r="A201" s="2">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>1106260</v>
       </c>
       <c r="B201" s="2">
@@ -6551,7 +6551,7 @@
     </row>
     <row r="202" spans="1:7">
       <c r="A202" s="2">
-        <f t="shared" ref="A202:A217" si="9">D202*1000+B202*100+C202</f>
+        <f t="shared" ref="A202:A217" si="11">D202*1000+B202*100+C202</f>
         <v>1106261</v>
       </c>
       <c r="B202" s="2">
@@ -6575,7 +6575,7 @@
     </row>
     <row r="203" spans="1:7">
       <c r="A203" s="2">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>1106262</v>
       </c>
       <c r="B203" s="2">
@@ -6599,7 +6599,7 @@
     </row>
     <row r="204" spans="1:7">
       <c r="A204" s="2">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>1106263</v>
       </c>
       <c r="B204" s="2">
@@ -6623,7 +6623,7 @@
     </row>
     <row r="205" spans="1:7">
       <c r="A205" s="2">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>1106264</v>
       </c>
       <c r="B205" s="2">
@@ -6647,7 +6647,7 @@
     </row>
     <row r="206" spans="1:7">
       <c r="A206" s="2">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>1106265</v>
       </c>
       <c r="B206" s="2">
@@ -6671,7 +6671,7 @@
     </row>
     <row r="207" spans="1:7">
       <c r="A207" s="2">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>1106266</v>
       </c>
       <c r="B207" s="2">
@@ -6695,7 +6695,7 @@
     </row>
     <row r="208" spans="1:7">
       <c r="A208" s="2">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>1106267</v>
       </c>
       <c r="B208" s="2">
@@ -6719,7 +6719,7 @@
     </row>
     <row r="209" spans="1:7">
       <c r="A209" s="2">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>1106268</v>
       </c>
       <c r="B209" s="2">
@@ -6743,7 +6743,7 @@
     </row>
     <row r="210" spans="1:7">
       <c r="A210" s="2">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>1106269</v>
       </c>
       <c r="B210" s="2">
@@ -6767,7 +6767,7 @@
     </row>
     <row r="211" spans="1:7">
       <c r="A211" s="2">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>1106270</v>
       </c>
       <c r="B211" s="2">
@@ -6791,7 +6791,7 @@
     </row>
     <row r="212" spans="1:7">
       <c r="A212" s="2">
-        <f>D212*1000+B212*100+C212</f>
+        <f t="shared" si="11"/>
         <v>1106271</v>
       </c>
       <c r="B212" s="2">
@@ -6911,7 +6911,7 @@
     </row>
     <row r="217" spans="1:7">
       <c r="A217" s="5">
-        <f t="shared" ref="A217:A224" si="10">D217*1000+B217*100+C217</f>
+        <f t="shared" ref="A217:A226" si="12">D217*1000+B217*100+C217</f>
         <v>1107105</v>
       </c>
       <c r="B217" s="5">
@@ -6935,7 +6935,7 @@
     </row>
     <row r="218" spans="1:7">
       <c r="A218" s="5">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>1107106</v>
       </c>
       <c r="B218" s="5">
@@ -6959,7 +6959,7 @@
     </row>
     <row r="219" spans="1:7">
       <c r="A219" s="5">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>1107107</v>
       </c>
       <c r="B219" s="5">
@@ -6983,7 +6983,7 @@
     </row>
     <row r="220" spans="1:7">
       <c r="A220" s="5">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>1107108</v>
       </c>
       <c r="B220" s="5">
@@ -7007,7 +7007,7 @@
     </row>
     <row r="221" spans="1:7">
       <c r="A221" s="5">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>1107109</v>
       </c>
       <c r="B221" s="5">
@@ -7031,7 +7031,7 @@
     </row>
     <row r="222" spans="1:7">
       <c r="A222" s="5">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>1107110</v>
       </c>
       <c r="B222" s="5">
@@ -7055,7 +7055,7 @@
     </row>
     <row r="223" spans="1:7">
       <c r="A223" s="5">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>1107111</v>
       </c>
       <c r="B223" s="5">
@@ -7079,7 +7079,7 @@
     </row>
     <row r="224" spans="1:7">
       <c r="A224" s="5">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>1107112</v>
       </c>
       <c r="B224" s="5">
@@ -7103,7 +7103,7 @@
     </row>
     <row r="225" spans="1:7">
       <c r="A225" s="5">
-        <f>D225*1000+B225*100+C225</f>
+        <f t="shared" si="12"/>
         <v>1107251</v>
       </c>
       <c r="B225" s="5">
@@ -7127,7 +7127,7 @@
     </row>
     <row r="226" spans="1:7">
       <c r="A226" s="5">
-        <f>D226*1000+B226*100+C226</f>
+        <f t="shared" si="12"/>
         <v>1107252</v>
       </c>
       <c r="B226" s="5">
@@ -7151,7 +7151,7 @@
     </row>
     <row r="227" spans="1:7">
       <c r="A227" s="5">
-        <f t="shared" ref="A227:A255" si="11">D227*1000+B227*100+C227</f>
+        <f t="shared" ref="A227:A255" si="13">D227*1000+B227*100+C227</f>
         <v>1107253</v>
       </c>
       <c r="B227" s="5">
@@ -7175,7 +7175,7 @@
     </row>
     <row r="228" spans="1:7">
       <c r="A228" s="5">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>1107254</v>
       </c>
       <c r="B228" s="5">
@@ -7199,7 +7199,7 @@
     </row>
     <row r="229" spans="1:7">
       <c r="A229" s="5">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>1107255</v>
       </c>
       <c r="B229" s="5">
@@ -7223,7 +7223,7 @@
     </row>
     <row r="230" spans="1:7">
       <c r="A230" s="5">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>1107256</v>
       </c>
       <c r="B230" s="5">
@@ -7247,7 +7247,7 @@
     </row>
     <row r="231" spans="1:7">
       <c r="A231" s="5">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>1107257</v>
       </c>
       <c r="B231" s="5">
@@ -7271,7 +7271,7 @@
     </row>
     <row r="232" spans="1:7">
       <c r="A232" s="5">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>1107258</v>
       </c>
       <c r="B232" s="5">
@@ -7295,7 +7295,7 @@
     </row>
     <row r="233" spans="1:7">
       <c r="A233" s="5">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>1107259</v>
       </c>
       <c r="B233" s="5">
@@ -7319,7 +7319,7 @@
     </row>
     <row r="234" spans="1:7">
       <c r="A234" s="5">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>1107260</v>
       </c>
       <c r="B234" s="5">
@@ -7343,7 +7343,7 @@
     </row>
     <row r="235" spans="1:7">
       <c r="A235" s="5">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>1107261</v>
       </c>
       <c r="B235" s="5">
@@ -7367,7 +7367,7 @@
     </row>
     <row r="236" spans="1:7">
       <c r="A236" s="5">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>1107262</v>
       </c>
       <c r="B236" s="5">
@@ -7391,7 +7391,7 @@
     </row>
     <row r="237" spans="1:7">
       <c r="A237" s="5">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>1107263</v>
       </c>
       <c r="B237" s="5">
@@ -7415,7 +7415,7 @@
     </row>
     <row r="238" spans="1:7">
       <c r="A238" s="5">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>1107264</v>
       </c>
       <c r="B238" s="5">
@@ -7439,7 +7439,7 @@
     </row>
     <row r="239" spans="1:7">
       <c r="A239" s="5">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>1107265</v>
       </c>
       <c r="B239" s="5">
@@ -7463,7 +7463,7 @@
     </row>
     <row r="240" spans="1:7">
       <c r="A240" s="5">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>1107266</v>
       </c>
       <c r="B240" s="5">
@@ -7487,7 +7487,7 @@
     </row>
     <row r="241" spans="1:7">
       <c r="A241" s="5">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>1107267</v>
       </c>
       <c r="B241" s="5">
@@ -7511,7 +7511,7 @@
     </row>
     <row r="242" spans="1:7">
       <c r="A242" s="5">
-        <f>D242*1000+B242*100+C242</f>
+        <f t="shared" si="13"/>
         <v>1107268</v>
       </c>
       <c r="B242" s="5">
@@ -7631,7 +7631,7 @@
     </row>
     <row r="247" spans="1:7">
       <c r="A247" s="2">
-        <f t="shared" ref="A247:A252" si="12">D247*1000+B247*100+C247</f>
+        <f t="shared" ref="A247:A262" si="14">D247*1000+B247*100+C247</f>
         <v>1108105</v>
       </c>
       <c r="B247" s="2">
@@ -7655,7 +7655,7 @@
     </row>
     <row r="248" spans="1:7">
       <c r="A248" s="2">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>1108106</v>
       </c>
       <c r="B248" s="2">
@@ -7679,7 +7679,7 @@
     </row>
     <row r="249" spans="1:7">
       <c r="A249" s="2">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>1108107</v>
       </c>
       <c r="B249" s="2">
@@ -7703,7 +7703,7 @@
     </row>
     <row r="250" spans="1:7">
       <c r="A250" s="2">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>1108108</v>
       </c>
       <c r="B250" s="2">
@@ -7727,7 +7727,7 @@
     </row>
     <row r="251" spans="1:7">
       <c r="A251" s="2">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>1108109</v>
       </c>
       <c r="B251" s="2">
@@ -7751,7 +7751,7 @@
     </row>
     <row r="252" spans="1:7">
       <c r="A252" s="2">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>1108110</v>
       </c>
       <c r="B252" s="2">
@@ -7775,7 +7775,7 @@
     </row>
     <row r="253" spans="1:7">
       <c r="A253" s="2">
-        <f>D253*1000+B253*100+C253</f>
+        <f t="shared" si="14"/>
         <v>1108251</v>
       </c>
       <c r="B253" s="2">
@@ -7799,7 +7799,7 @@
     </row>
     <row r="254" spans="1:7">
       <c r="A254" s="2">
-        <f>D254*1000+B254*100+C254</f>
+        <f t="shared" si="14"/>
         <v>1108252</v>
       </c>
       <c r="B254" s="2">
@@ -7823,7 +7823,7 @@
     </row>
     <row r="255" spans="1:7">
       <c r="A255" s="2">
-        <f>D255*1000+B255*100+C255</f>
+        <f t="shared" si="14"/>
         <v>1108253</v>
       </c>
       <c r="B255" s="2">
@@ -7847,7 +7847,7 @@
     </row>
     <row r="256" spans="1:7">
       <c r="A256" s="2">
-        <f>D256*1000+B256*100+C256</f>
+        <f t="shared" si="14"/>
         <v>1108254</v>
       </c>
       <c r="B256" s="2">
@@ -7871,7 +7871,7 @@
     </row>
     <row r="257" spans="1:7">
       <c r="A257" s="2">
-        <f>D257*1000+B257*100+C257</f>
+        <f t="shared" si="14"/>
         <v>1108255</v>
       </c>
       <c r="B257" s="2">
@@ -7895,7 +7895,7 @@
     </row>
     <row r="258" spans="1:7">
       <c r="A258" s="2">
-        <f>D258*1000+B258*100+C258</f>
+        <f t="shared" si="14"/>
         <v>1108256</v>
       </c>
       <c r="B258" s="2">
@@ -7919,7 +7919,7 @@
     </row>
     <row r="259" spans="1:7">
       <c r="A259" s="2">
-        <f>D259*1000+B259*100+C259</f>
+        <f t="shared" si="14"/>
         <v>1108257</v>
       </c>
       <c r="B259" s="2">
@@ -7943,7 +7943,7 @@
     </row>
     <row r="260" spans="1:7">
       <c r="A260" s="2">
-        <f>D260*1000+B260*100+C260</f>
+        <f t="shared" si="14"/>
         <v>1108258</v>
       </c>
       <c r="B260" s="2">
@@ -7967,7 +7967,7 @@
     </row>
     <row r="261" spans="1:7">
       <c r="A261" s="2">
-        <f>D261*1000+B261*100+C261</f>
+        <f t="shared" si="14"/>
         <v>1108259</v>
       </c>
       <c r="B261" s="2">
@@ -7991,7 +7991,7 @@
     </row>
     <row r="262" spans="1:7">
       <c r="A262" s="2">
-        <f>D262*1000+B262*100+C262</f>
+        <f t="shared" si="14"/>
         <v>1108260</v>
       </c>
       <c r="B262" s="2">
@@ -8015,7 +8015,7 @@
     </row>
     <row r="263" spans="1:7">
       <c r="A263" s="2">
-        <f t="shared" ref="A263:A276" si="13">D263*1000+B263*100+C263</f>
+        <f t="shared" ref="A263:A276" si="15">D263*1000+B263*100+C263</f>
         <v>1108261</v>
       </c>
       <c r="B263" s="2">
@@ -8039,7 +8039,7 @@
     </row>
     <row r="264" spans="1:7">
       <c r="A264" s="2">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>1108262</v>
       </c>
       <c r="B264" s="2">
@@ -8063,7 +8063,7 @@
     </row>
     <row r="265" spans="1:7">
       <c r="A265" s="2">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>1108263</v>
       </c>
       <c r="B265" s="2">
@@ -8087,7 +8087,7 @@
     </row>
     <row r="266" spans="1:7">
       <c r="A266" s="2">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>1108264</v>
       </c>
       <c r="B266" s="2">
@@ -8111,7 +8111,7 @@
     </row>
     <row r="267" spans="1:7">
       <c r="A267" s="2">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>1108265</v>
       </c>
       <c r="B267" s="2">
@@ -8135,7 +8135,7 @@
     </row>
     <row r="268" spans="1:7">
       <c r="A268" s="2">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>1108266</v>
       </c>
       <c r="B268" s="2">
@@ -8159,7 +8159,7 @@
     </row>
     <row r="269" spans="1:7">
       <c r="A269" s="2">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>1108267</v>
       </c>
       <c r="B269" s="2">
@@ -8183,7 +8183,7 @@
     </row>
     <row r="270" spans="1:7">
       <c r="A270" s="2">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>1108268</v>
       </c>
       <c r="B270" s="2">
@@ -8207,7 +8207,7 @@
     </row>
     <row r="271" spans="1:7">
       <c r="A271" s="2">
-        <f>D271*1000+B271*100+C271</f>
+        <f t="shared" si="15"/>
         <v>1108269</v>
       </c>
       <c r="B271" s="2">
@@ -8327,7 +8327,7 @@
     </row>
     <row r="276" spans="1:7">
       <c r="A276" s="5">
-        <f t="shared" ref="A276:A281" si="14">D276*1000+B276*100+C276</f>
+        <f t="shared" ref="A276:A283" si="16">D276*1000+B276*100+C276</f>
         <v>1109105</v>
       </c>
       <c r="B276" s="5">
@@ -8351,7 +8351,7 @@
     </row>
     <row r="277" spans="1:7">
       <c r="A277" s="5">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>1109106</v>
       </c>
       <c r="B277" s="5">
@@ -8375,7 +8375,7 @@
     </row>
     <row r="278" spans="1:7">
       <c r="A278" s="5">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>1109107</v>
       </c>
       <c r="B278" s="5">
@@ -8399,7 +8399,7 @@
     </row>
     <row r="279" spans="1:7">
       <c r="A279" s="5">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>1109108</v>
       </c>
       <c r="B279" s="5">
@@ -8423,7 +8423,7 @@
     </row>
     <row r="280" spans="1:7">
       <c r="A280" s="5">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>1109109</v>
       </c>
       <c r="B280" s="5">
@@ -8447,7 +8447,7 @@
     </row>
     <row r="281" spans="1:7">
       <c r="A281" s="5">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>1109110</v>
       </c>
       <c r="B281" s="5">
@@ -8471,7 +8471,7 @@
     </row>
     <row r="282" spans="1:7">
       <c r="A282" s="5">
-        <f>D282*1000+B282*100+C282</f>
+        <f t="shared" si="16"/>
         <v>1109251</v>
       </c>
       <c r="B282" s="5">
@@ -8495,7 +8495,7 @@
     </row>
     <row r="283" spans="1:7">
       <c r="A283" s="5">
-        <f>D283*1000+B283*100+C283</f>
+        <f t="shared" si="16"/>
         <v>1109252</v>
       </c>
       <c r="B283" s="5">
@@ -8519,7 +8519,7 @@
     </row>
     <row r="284" spans="1:7">
       <c r="A284" s="5">
-        <f t="shared" ref="A284:A305" si="15">D284*1000+B284*100+C284</f>
+        <f t="shared" ref="A284:A305" si="17">D284*1000+B284*100+C284</f>
         <v>1109253</v>
       </c>
       <c r="B284" s="5">
@@ -8543,7 +8543,7 @@
     </row>
     <row r="285" spans="1:7">
       <c r="A285" s="5">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>1109254</v>
       </c>
       <c r="B285" s="5">
@@ -8567,7 +8567,7 @@
     </row>
     <row r="286" spans="1:7">
       <c r="A286" s="5">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>1109255</v>
       </c>
       <c r="B286" s="5">
@@ -8591,7 +8591,7 @@
     </row>
     <row r="287" spans="1:7">
       <c r="A287" s="5">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>1109256</v>
       </c>
       <c r="B287" s="5">
@@ -8615,7 +8615,7 @@
     </row>
     <row r="288" spans="1:7">
       <c r="A288" s="5">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>1109257</v>
       </c>
       <c r="B288" s="5">
@@ -8639,7 +8639,7 @@
     </row>
     <row r="289" spans="1:7">
       <c r="A289" s="5">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>1109258</v>
       </c>
       <c r="B289" s="5">
@@ -8663,7 +8663,7 @@
     </row>
     <row r="290" spans="1:7">
       <c r="A290" s="5">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>1109259</v>
       </c>
       <c r="B290" s="5">
@@ -8687,7 +8687,7 @@
     </row>
     <row r="291" spans="1:7">
       <c r="A291" s="5">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>1109260</v>
       </c>
       <c r="B291" s="5">
@@ -8711,7 +8711,7 @@
     </row>
     <row r="292" spans="1:7">
       <c r="A292" s="5">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>1109261</v>
       </c>
       <c r="B292" s="5">
@@ -8735,7 +8735,7 @@
     </row>
     <row r="293" spans="1:7">
       <c r="A293" s="5">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>1109262</v>
       </c>
       <c r="B293" s="5">
@@ -8759,7 +8759,7 @@
     </row>
     <row r="294" spans="1:7">
       <c r="A294" s="5">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>1109263</v>
       </c>
       <c r="B294" s="5">
@@ -8783,7 +8783,7 @@
     </row>
     <row r="295" spans="1:7">
       <c r="A295" s="5">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>1109264</v>
       </c>
       <c r="B295" s="5">
@@ -8807,7 +8807,7 @@
     </row>
     <row r="296" spans="1:7">
       <c r="A296" s="5">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>1109265</v>
       </c>
       <c r="B296" s="5">
@@ -8831,7 +8831,7 @@
     </row>
     <row r="297" spans="1:7">
       <c r="A297" s="5">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>1109266</v>
       </c>
       <c r="B297" s="5">
@@ -8855,7 +8855,7 @@
     </row>
     <row r="298" spans="1:7">
       <c r="A298" s="5">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>1109267</v>
       </c>
       <c r="B298" s="5">
@@ -8879,7 +8879,7 @@
     </row>
     <row r="299" spans="1:7">
       <c r="A299" s="5">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>1109268</v>
       </c>
       <c r="B299" s="5">
@@ -8903,7 +8903,7 @@
     </row>
     <row r="300" spans="1:7">
       <c r="A300" s="5">
-        <f>D300*1000+B300*100+C300</f>
+        <f t="shared" si="17"/>
         <v>1109269</v>
       </c>
       <c r="B300" s="5">
@@ -9023,7 +9023,7 @@
     </row>
     <row r="305" spans="1:7">
       <c r="A305" s="2">
-        <f t="shared" ref="A305:A312" si="16">D305*1000+B305*100+C305</f>
+        <f t="shared" ref="A305:A314" si="18">D305*1000+B305*100+C305</f>
         <v>1110105</v>
       </c>
       <c r="B305" s="2">
@@ -9047,7 +9047,7 @@
     </row>
     <row r="306" spans="1:7">
       <c r="A306" s="2">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>1110106</v>
       </c>
       <c r="B306" s="2">
@@ -9071,7 +9071,7 @@
     </row>
     <row r="307" spans="1:7">
       <c r="A307" s="2">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>1110107</v>
       </c>
       <c r="B307" s="2">
@@ -9095,7 +9095,7 @@
     </row>
     <row r="308" spans="1:7">
       <c r="A308" s="2">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>1110108</v>
       </c>
       <c r="B308" s="2">
@@ -9119,7 +9119,7 @@
     </row>
     <row r="309" spans="1:7">
       <c r="A309" s="2">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>1110109</v>
       </c>
       <c r="B309" s="2">
@@ -9143,7 +9143,7 @@
     </row>
     <row r="310" spans="1:7">
       <c r="A310" s="2">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>1110110</v>
       </c>
       <c r="B310" s="2">
@@ -9167,7 +9167,7 @@
     </row>
     <row r="311" spans="1:7">
       <c r="A311" s="2">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>1110111</v>
       </c>
       <c r="B311" s="2">
@@ -9191,7 +9191,7 @@
     </row>
     <row r="312" spans="1:7">
       <c r="A312" s="2">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>1110112</v>
       </c>
       <c r="B312" s="2">
@@ -9215,7 +9215,7 @@
     </row>
     <row r="313" spans="1:7">
       <c r="A313" s="2">
-        <f>D313*1000+B313*100+C313</f>
+        <f t="shared" si="18"/>
         <v>1110251</v>
       </c>
       <c r="B313" s="2">
@@ -9239,7 +9239,7 @@
     </row>
     <row r="314" spans="1:7">
       <c r="A314" s="2">
-        <f>D314*1000+B314*100+C314</f>
+        <f t="shared" si="18"/>
         <v>1110252</v>
       </c>
       <c r="B314" s="2">
@@ -9263,7 +9263,7 @@
     </row>
     <row r="315" spans="1:7">
       <c r="A315" s="2">
-        <f t="shared" ref="A315:A332" si="17">D315*1000+B315*100+C315</f>
+        <f t="shared" ref="A315:A336" si="19">D315*1000+B315*100+C315</f>
         <v>1110253</v>
       </c>
       <c r="B315" s="2">
@@ -9287,7 +9287,7 @@
     </row>
     <row r="316" spans="1:7">
       <c r="A316" s="2">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>1110254</v>
       </c>
       <c r="B316" s="2">
@@ -9311,7 +9311,7 @@
     </row>
     <row r="317" spans="1:7">
       <c r="A317" s="2">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>1110255</v>
       </c>
       <c r="B317" s="2">
@@ -9335,7 +9335,7 @@
     </row>
     <row r="318" spans="1:7">
       <c r="A318" s="2">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>1110256</v>
       </c>
       <c r="B318" s="2">
@@ -9359,7 +9359,7 @@
     </row>
     <row r="319" spans="1:7">
       <c r="A319" s="2">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>1110257</v>
       </c>
       <c r="B319" s="2">
@@ -9383,7 +9383,7 @@
     </row>
     <row r="320" spans="1:7">
       <c r="A320" s="2">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>1110258</v>
       </c>
       <c r="B320" s="2">
@@ -9407,7 +9407,7 @@
     </row>
     <row r="321" spans="1:7">
       <c r="A321" s="2">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>1110259</v>
       </c>
       <c r="B321" s="2">
@@ -9431,7 +9431,7 @@
     </row>
     <row r="322" spans="1:7">
       <c r="A322" s="2">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>1110260</v>
       </c>
       <c r="B322" s="2">
@@ -9455,7 +9455,7 @@
     </row>
     <row r="323" spans="1:7">
       <c r="A323" s="2">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>1110261</v>
       </c>
       <c r="B323" s="2">
@@ -9479,7 +9479,7 @@
     </row>
     <row r="324" spans="1:7">
       <c r="A324" s="2">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>1110262</v>
       </c>
       <c r="B324" s="2">
@@ -9503,7 +9503,7 @@
     </row>
     <row r="325" spans="1:7">
       <c r="A325" s="2">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>1110263</v>
       </c>
       <c r="B325" s="2">
@@ -9527,7 +9527,7 @@
     </row>
     <row r="326" spans="1:7">
       <c r="A326" s="2">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>1110264</v>
       </c>
       <c r="B326" s="2">
@@ -9551,7 +9551,7 @@
     </row>
     <row r="327" spans="1:7">
       <c r="A327" s="2">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>1110265</v>
       </c>
       <c r="B327" s="2">
@@ -9575,7 +9575,7 @@
     </row>
     <row r="328" spans="1:7">
       <c r="A328" s="2">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>1110266</v>
       </c>
       <c r="B328" s="2">
@@ -9599,7 +9599,7 @@
     </row>
     <row r="329" spans="1:7">
       <c r="A329" s="2">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>1110267</v>
       </c>
       <c r="B329" s="2">
@@ -9623,7 +9623,7 @@
     </row>
     <row r="330" spans="1:7">
       <c r="A330" s="2">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>1110268</v>
       </c>
       <c r="B330" s="2">
@@ -9647,7 +9647,7 @@
     </row>
     <row r="331" spans="1:7">
       <c r="A331" s="2">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>1110269</v>
       </c>
       <c r="B331" s="2">
@@ -9671,7 +9671,7 @@
     </row>
     <row r="332" spans="1:7">
       <c r="A332" s="2">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>1110270</v>
       </c>
       <c r="B332" s="2">
@@ -9791,7 +9791,7 @@
     </row>
     <row r="337" spans="1:7">
       <c r="A337" s="5">
-        <f t="shared" ref="A337:A343" si="18">D337*1000+B337*100+C337</f>
+        <f t="shared" ref="A337:A343" si="20">D337*1000+B337*100+C337</f>
         <v>1111105</v>
       </c>
       <c r="B337" s="5">
@@ -9815,7 +9815,7 @@
     </row>
     <row r="338" spans="1:7">
       <c r="A338" s="5">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>1111106</v>
       </c>
       <c r="B338" s="5">
@@ -9839,7 +9839,7 @@
     </row>
     <row r="339" spans="1:7">
       <c r="A339" s="5">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>1111107</v>
       </c>
       <c r="B339" s="5">
@@ -9863,7 +9863,7 @@
     </row>
     <row r="340" spans="1:7">
       <c r="A340" s="5">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>1111108</v>
       </c>
       <c r="B340" s="5">
@@ -9887,7 +9887,7 @@
     </row>
     <row r="341" spans="1:7">
       <c r="A341" s="5">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>1111109</v>
       </c>
       <c r="B341" s="5">
@@ -9911,7 +9911,7 @@
     </row>
     <row r="342" spans="1:7">
       <c r="A342" s="5">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>1111110</v>
       </c>
       <c r="B342" s="5">
@@ -9935,7 +9935,7 @@
     </row>
     <row r="343" spans="1:7">
       <c r="A343" s="5">
-        <f t="shared" ref="A343:A356" si="19">D343*1000+B343*100+C343</f>
+        <f t="shared" ref="A343:A367" si="21">D343*1000+B343*100+C343</f>
         <v>1111251</v>
       </c>
       <c r="B343" s="5">
@@ -9959,7 +9959,7 @@
     </row>
     <row r="344" spans="1:7">
       <c r="A344" s="5">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>1111252</v>
       </c>
       <c r="B344" s="5">
@@ -9983,7 +9983,7 @@
     </row>
     <row r="345" spans="1:7">
       <c r="A345" s="5">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>1111253</v>
       </c>
       <c r="B345" s="5">
@@ -10007,7 +10007,7 @@
     </row>
     <row r="346" spans="1:7">
       <c r="A346" s="5">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>1111254</v>
       </c>
       <c r="B346" s="5">
@@ -10031,7 +10031,7 @@
     </row>
     <row r="347" spans="1:7">
       <c r="A347" s="5">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>1111255</v>
       </c>
       <c r="B347" s="5">
@@ -10055,7 +10055,7 @@
     </row>
     <row r="348" spans="1:7">
       <c r="A348" s="5">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>1111256</v>
       </c>
       <c r="B348" s="5">
@@ -10079,7 +10079,7 @@
     </row>
     <row r="349" spans="1:7">
       <c r="A349" s="5">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>1111257</v>
       </c>
       <c r="B349" s="5">
@@ -10103,7 +10103,7 @@
     </row>
     <row r="350" spans="1:7">
       <c r="A350" s="5">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>1111258</v>
       </c>
       <c r="B350" s="5">
@@ -10127,7 +10127,7 @@
     </row>
     <row r="351" spans="1:7">
       <c r="A351" s="5">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>1111259</v>
       </c>
       <c r="B351" s="5">
@@ -10151,7 +10151,7 @@
     </row>
     <row r="352" spans="1:7">
       <c r="A352" s="5">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>1111260</v>
       </c>
       <c r="B352" s="5">
@@ -10175,7 +10175,7 @@
     </row>
     <row r="353" spans="1:7">
       <c r="A353" s="5">
-        <f>D353*1000+B353*100+C353</f>
+        <f t="shared" si="21"/>
         <v>1111261</v>
       </c>
       <c r="B353" s="5">
@@ -10199,7 +10199,7 @@
     </row>
     <row r="354" spans="1:7">
       <c r="A354" s="5">
-        <f>D354*1000+B354*100+C354</f>
+        <f t="shared" si="21"/>
         <v>1111262</v>
       </c>
       <c r="B354" s="5">
@@ -10223,7 +10223,7 @@
     </row>
     <row r="355" spans="1:7">
       <c r="A355" s="5">
-        <f>D355*1000+B355*100+C355</f>
+        <f t="shared" si="21"/>
         <v>1111263</v>
       </c>
       <c r="B355" s="5">
@@ -10247,7 +10247,7 @@
     </row>
     <row r="356" spans="1:7">
       <c r="A356" s="5">
-        <f>D356*1000+B356*100+C356</f>
+        <f t="shared" si="21"/>
         <v>1111264</v>
       </c>
       <c r="B356" s="5">
@@ -10271,7 +10271,7 @@
     </row>
     <row r="357" spans="1:7">
       <c r="A357" s="5">
-        <f>D357*1000+B357*100+C357</f>
+        <f t="shared" si="21"/>
         <v>1111265</v>
       </c>
       <c r="B357" s="5">
@@ -10295,7 +10295,7 @@
     </row>
     <row r="358" spans="1:7">
       <c r="A358" s="5">
-        <f>D358*1000+B358*100+C358</f>
+        <f t="shared" si="21"/>
         <v>1111266</v>
       </c>
       <c r="B358" s="5">
@@ -10319,7 +10319,7 @@
     </row>
     <row r="359" spans="1:7">
       <c r="A359" s="5">
-        <f>D359*1000+B359*100+C359</f>
+        <f t="shared" si="21"/>
         <v>1111267</v>
       </c>
       <c r="B359" s="5">
@@ -10343,7 +10343,7 @@
     </row>
     <row r="360" spans="1:7">
       <c r="A360" s="5">
-        <f>D360*1000+B360*100+C360</f>
+        <f t="shared" si="21"/>
         <v>1111268</v>
       </c>
       <c r="B360" s="5">
@@ -10367,7 +10367,7 @@
     </row>
     <row r="361" spans="1:7">
       <c r="A361" s="5">
-        <f>D361*1000+B361*100+C361</f>
+        <f t="shared" si="21"/>
         <v>1111269</v>
       </c>
       <c r="B361" s="5">
@@ -10391,7 +10391,7 @@
     </row>
     <row r="362" spans="1:7">
       <c r="A362" s="5">
-        <f>D362*1000+B362*100+C362</f>
+        <f t="shared" si="21"/>
         <v>1111270</v>
       </c>
       <c r="B362" s="5">
@@ -10415,7 +10415,7 @@
     </row>
     <row r="363" spans="1:7">
       <c r="A363" s="5">
-        <f>D363*1000+B363*100+C363</f>
+        <f t="shared" si="21"/>
         <v>1111271</v>
       </c>
       <c r="B363" s="5">
@@ -10535,7 +10535,7 @@
     </row>
     <row r="368" spans="1:7">
       <c r="A368" s="2">
-        <f t="shared" ref="A368:A373" si="20">D368*1000+B368*100+C368</f>
+        <f t="shared" ref="A368:A373" si="22">D368*1000+B368*100+C368</f>
         <v>1112105</v>
       </c>
       <c r="B368" s="2">
@@ -10559,7 +10559,7 @@
     </row>
     <row r="369" spans="1:7">
       <c r="A369" s="2">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>1112106</v>
       </c>
       <c r="B369" s="2">
@@ -10583,7 +10583,7 @@
     </row>
     <row r="370" spans="1:7">
       <c r="A370" s="2">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>1112107</v>
       </c>
       <c r="B370" s="2">
@@ -10607,7 +10607,7 @@
     </row>
     <row r="371" spans="1:7">
       <c r="A371" s="2">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>1112108</v>
       </c>
       <c r="B371" s="2">
@@ -10631,7 +10631,7 @@
     </row>
     <row r="372" spans="1:7">
       <c r="A372" s="2">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>1112109</v>
       </c>
       <c r="B372" s="2">
@@ -10655,7 +10655,7 @@
     </row>
     <row r="373" spans="1:7">
       <c r="A373" s="2">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>1112110</v>
       </c>
       <c r="B373" s="2">
@@ -10679,7 +10679,7 @@
     </row>
     <row r="374" spans="1:7">
       <c r="A374" s="2">
-        <f t="shared" ref="A374:A383" si="21">D374*1000+B374*100+C374</f>
+        <f t="shared" ref="A374:A394" si="23">D374*1000+B374*100+C374</f>
         <v>1112251</v>
       </c>
       <c r="B374" s="2">
@@ -10703,7 +10703,7 @@
     </row>
     <row r="375" spans="1:7">
       <c r="A375" s="2">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>1112252</v>
       </c>
       <c r="B375" s="2">
@@ -10727,7 +10727,7 @@
     </row>
     <row r="376" spans="1:7">
       <c r="A376" s="2">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>1112253</v>
       </c>
       <c r="B376" s="2">
@@ -10751,7 +10751,7 @@
     </row>
     <row r="377" spans="1:7">
       <c r="A377" s="2">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>1112254</v>
       </c>
       <c r="B377" s="2">
@@ -10775,7 +10775,7 @@
     </row>
     <row r="378" spans="1:7">
       <c r="A378" s="2">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>1112255</v>
       </c>
       <c r="B378" s="2">
@@ -10799,7 +10799,7 @@
     </row>
     <row r="379" spans="1:7">
       <c r="A379" s="2">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>1112256</v>
       </c>
       <c r="B379" s="2">
@@ -10823,7 +10823,7 @@
     </row>
     <row r="380" spans="1:7">
       <c r="A380" s="2">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>1112257</v>
       </c>
       <c r="B380" s="2">
@@ -10847,7 +10847,7 @@
     </row>
     <row r="381" spans="1:7">
       <c r="A381" s="2">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>1112258</v>
       </c>
       <c r="B381" s="2">
@@ -10871,7 +10871,7 @@
     </row>
     <row r="382" spans="1:7">
       <c r="A382" s="2">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>1112259</v>
       </c>
       <c r="B382" s="2">
@@ -10895,7 +10895,7 @@
     </row>
     <row r="383" spans="1:7">
       <c r="A383" s="2">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>1112260</v>
       </c>
       <c r="B383" s="2">
@@ -10919,7 +10919,7 @@
     </row>
     <row r="384" spans="1:7">
       <c r="A384" s="2">
-        <f>D384*1000+B384*100+C384</f>
+        <f t="shared" si="23"/>
         <v>1112261</v>
       </c>
       <c r="B384" s="2">
@@ -10943,7 +10943,7 @@
     </row>
     <row r="385" spans="1:7">
       <c r="A385" s="2">
-        <f>D385*1000+B385*100+C385</f>
+        <f t="shared" si="23"/>
         <v>1112262</v>
       </c>
       <c r="B385" s="2">
@@ -10967,7 +10967,7 @@
     </row>
     <row r="386" spans="1:7">
       <c r="A386" s="2">
-        <f>D386*1000+B386*100+C386</f>
+        <f t="shared" si="23"/>
         <v>1112263</v>
       </c>
       <c r="B386" s="2">
@@ -10991,7 +10991,7 @@
     </row>
     <row r="387" spans="1:7">
       <c r="A387" s="2">
-        <f>D387*1000+B387*100+C387</f>
+        <f t="shared" si="23"/>
         <v>1112264</v>
       </c>
       <c r="B387" s="2">
@@ -11015,7 +11015,7 @@
     </row>
     <row r="388" spans="1:7">
       <c r="A388" s="2">
-        <f>D388*1000+B388*100+C388</f>
+        <f t="shared" si="23"/>
         <v>1112265</v>
       </c>
       <c r="B388" s="2">
@@ -11039,7 +11039,7 @@
     </row>
     <row r="389" spans="1:7">
       <c r="A389" s="2">
-        <f>D389*1000+B389*100+C389</f>
+        <f t="shared" si="23"/>
         <v>1112266</v>
       </c>
       <c r="B389" s="2">
@@ -11063,7 +11063,7 @@
     </row>
     <row r="390" spans="1:7">
       <c r="A390" s="2">
-        <f>D390*1000+B390*100+C390</f>
+        <f t="shared" si="23"/>
         <v>1112267</v>
       </c>
       <c r="B390" s="2">
@@ -11087,7 +11087,7 @@
     </row>
     <row r="391" spans="1:7">
       <c r="A391" s="2">
-        <f>D391*1000+B391*100+C391</f>
+        <f t="shared" si="23"/>
         <v>1112268</v>
       </c>
       <c r="B391" s="2">
@@ -11111,7 +11111,7 @@
     </row>
     <row r="392" spans="1:7">
       <c r="A392" s="2">
-        <f>D392*1000+B392*100+C392</f>
+        <f t="shared" si="23"/>
         <v>1112269</v>
       </c>
       <c r="B392" s="2">
@@ -11177,7 +11177,7 @@
     </row>
     <row r="395" spans="1:7">
       <c r="A395" s="2">
-        <f t="shared" ref="A395:A404" si="22">D395*1000+B395*100+C395</f>
+        <f t="shared" ref="A395:A404" si="24">D395*1000+B395*100+C395</f>
         <v>1202103</v>
       </c>
       <c r="B395" s="2">
@@ -11198,7 +11198,7 @@
     </row>
     <row r="396" spans="1:7">
       <c r="A396" s="2">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>1202104</v>
       </c>
       <c r="B396" s="2">
@@ -11219,7 +11219,7 @@
     </row>
     <row r="397" spans="1:7">
       <c r="A397" s="2">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>1202105</v>
       </c>
       <c r="B397" s="2">
@@ -11240,7 +11240,7 @@
     </row>
     <row r="398" spans="1:7">
       <c r="A398" s="2">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>1202106</v>
       </c>
       <c r="B398" s="2">
@@ -11261,7 +11261,7 @@
     </row>
     <row r="399" spans="1:7">
       <c r="A399" s="2">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>1202107</v>
       </c>
       <c r="B399" s="2">
@@ -11282,7 +11282,7 @@
     </row>
     <row r="400" spans="1:7">
       <c r="A400" s="2">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>1202108</v>
       </c>
       <c r="B400" s="2">
@@ -11303,7 +11303,7 @@
     </row>
     <row r="401" spans="1:6">
       <c r="A401" s="2">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>1202109</v>
       </c>
       <c r="B401" s="2">
@@ -11324,7 +11324,7 @@
     </row>
     <row r="402" spans="1:6">
       <c r="A402" s="2">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>1202110</v>
       </c>
       <c r="B402" s="2">
@@ -11345,7 +11345,7 @@
     </row>
     <row r="403" spans="1:6">
       <c r="A403" s="2">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>1202111</v>
       </c>
       <c r="B403" s="2">
@@ -11366,7 +11366,7 @@
     </row>
     <row r="404" spans="1:6">
       <c r="A404" s="2">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>1202112</v>
       </c>
       <c r="B404" s="2">
@@ -11387,7 +11387,7 @@
     </row>
     <row r="405" spans="1:6">
       <c r="A405" s="2">
-        <f t="shared" ref="A405:A424" si="23">D405*1000+B405*100+C405</f>
+        <f t="shared" ref="A405:A424" si="25">D405*1000+B405*100+C405</f>
         <v>1202113</v>
       </c>
       <c r="B405" s="2">
@@ -11408,7 +11408,7 @@
     </row>
     <row r="406" spans="1:6">
       <c r="A406" s="2">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>1202114</v>
       </c>
       <c r="B406" s="2">
@@ -11429,7 +11429,7 @@
     </row>
     <row r="407" spans="1:6">
       <c r="A407" s="2">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>1202115</v>
       </c>
       <c r="B407" s="2">
@@ -11450,7 +11450,7 @@
     </row>
     <row r="408" spans="1:6">
       <c r="A408" s="2">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>1202116</v>
       </c>
       <c r="B408" s="2">
@@ -11471,7 +11471,7 @@
     </row>
     <row r="409" spans="1:6">
       <c r="A409" s="2">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>1202117</v>
       </c>
       <c r="B409" s="2">
@@ -11492,7 +11492,7 @@
     </row>
     <row r="410" spans="1:6">
       <c r="A410" s="2">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>1202118</v>
       </c>
       <c r="B410" s="2">
@@ -11513,7 +11513,7 @@
     </row>
     <row r="411" spans="1:6">
       <c r="A411" s="2">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>1202119</v>
       </c>
       <c r="B411" s="2">
@@ -11534,7 +11534,7 @@
     </row>
     <row r="412" spans="1:6">
       <c r="A412" s="2">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>1202120</v>
       </c>
       <c r="B412" s="2">
@@ -11555,7 +11555,7 @@
     </row>
     <row r="413" spans="1:6">
       <c r="A413" s="2">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>1202121</v>
       </c>
       <c r="B413" s="2">
@@ -11576,7 +11576,7 @@
     </row>
     <row r="414" spans="1:6">
       <c r="A414" s="2">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>1202122</v>
       </c>
       <c r="B414" s="2">
@@ -11597,7 +11597,7 @@
     </row>
     <row r="415" spans="1:6">
       <c r="A415" s="2">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>1202123</v>
       </c>
       <c r="B415" s="2">
@@ -11618,7 +11618,7 @@
     </row>
     <row r="416" spans="1:6">
       <c r="A416" s="2">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>1202124</v>
       </c>
       <c r="B416" s="2">
@@ -11639,7 +11639,7 @@
     </row>
     <row r="417" spans="1:6">
       <c r="A417" s="2">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>1202125</v>
       </c>
       <c r="B417" s="2">
@@ -11660,7 +11660,7 @@
     </row>
     <row r="418" spans="1:6">
       <c r="A418" s="2">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>1202126</v>
       </c>
       <c r="B418" s="2">
@@ -11681,7 +11681,7 @@
     </row>
     <row r="419" spans="1:6">
       <c r="A419" s="2">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>1202127</v>
       </c>
       <c r="B419" s="2">
@@ -11702,7 +11702,7 @@
     </row>
     <row r="420" spans="1:6">
       <c r="A420" s="2">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>1202128</v>
       </c>
       <c r="B420" s="2">
@@ -11723,7 +11723,7 @@
     </row>
     <row r="421" spans="1:6">
       <c r="A421" s="2">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>1202129</v>
       </c>
       <c r="B421" s="2">
@@ -11744,7 +11744,7 @@
     </row>
     <row r="422" spans="1:6">
       <c r="A422" s="2">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>1202130</v>
       </c>
       <c r="B422" s="2">
@@ -11765,7 +11765,7 @@
     </row>
     <row r="423" spans="1:6">
       <c r="A423" s="2">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>1202131</v>
       </c>
       <c r="B423" s="2">
@@ -11786,7 +11786,7 @@
     </row>
     <row r="424" spans="1:6">
       <c r="A424" s="2">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>1202132</v>
       </c>
       <c r="B424" s="2">
@@ -11807,7 +11807,7 @@
     </row>
     <row r="425" spans="1:6">
       <c r="A425" s="2">
-        <f t="shared" ref="A425:A451" si="24">D425*1000+B425*100+C425</f>
+        <f t="shared" ref="A425:A451" si="26">D425*1000+B425*100+C425</f>
         <v>1202251</v>
       </c>
       <c r="B425" s="2">
@@ -11828,7 +11828,7 @@
     </row>
     <row r="426" spans="1:6">
       <c r="A426" s="2">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>1202252</v>
       </c>
       <c r="B426" s="2">
@@ -11849,7 +11849,7 @@
     </row>
     <row r="427" spans="1:6">
       <c r="A427" s="2">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>1202253</v>
       </c>
       <c r="B427" s="2">
@@ -11870,7 +11870,7 @@
     </row>
     <row r="428" spans="1:6">
       <c r="A428" s="2">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>1202254</v>
       </c>
       <c r="B428" s="2">
@@ -11891,7 +11891,7 @@
     </row>
     <row r="429" spans="1:6">
       <c r="A429" s="2">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>1202255</v>
       </c>
       <c r="B429" s="2">
@@ -11912,7 +11912,7 @@
     </row>
     <row r="430" spans="1:6">
       <c r="A430" s="2">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>1202256</v>
       </c>
       <c r="B430" s="2">
@@ -11933,7 +11933,7 @@
     </row>
     <row r="431" spans="1:6">
       <c r="A431" s="2">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>1202257</v>
       </c>
       <c r="B431" s="2">
@@ -11954,7 +11954,7 @@
     </row>
     <row r="432" spans="1:6">
       <c r="A432" s="2">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>1202258</v>
       </c>
       <c r="B432" s="2">
@@ -11975,7 +11975,7 @@
     </row>
     <row r="433" spans="1:6">
       <c r="A433" s="2">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>1202259</v>
       </c>
       <c r="B433" s="2">
@@ -11996,7 +11996,7 @@
     </row>
     <row r="434" spans="1:6">
       <c r="A434" s="2">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>1202260</v>
       </c>
       <c r="B434" s="2">
@@ -12017,7 +12017,7 @@
     </row>
     <row r="435" spans="1:6">
       <c r="A435" s="2">
-        <f t="shared" ref="A435:A490" si="25">D435*1000+B435*100+C435</f>
+        <f t="shared" ref="A435:A490" si="27">D435*1000+B435*100+C435</f>
         <v>1202261</v>
       </c>
       <c r="B435" s="2">
@@ -12038,7 +12038,7 @@
     </row>
     <row r="436" spans="1:6">
       <c r="A436" s="2">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>1202262</v>
       </c>
       <c r="B436" s="2">
@@ -12059,7 +12059,7 @@
     </row>
     <row r="437" spans="1:6">
       <c r="A437" s="2">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>1202263</v>
       </c>
       <c r="B437" s="2">
@@ -12080,7 +12080,7 @@
     </row>
     <row r="438" spans="1:6">
       <c r="A438" s="2">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>1202264</v>
       </c>
       <c r="B438" s="2">
@@ -12101,7 +12101,7 @@
     </row>
     <row r="439" spans="1:6">
       <c r="A439" s="2">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>1202265</v>
       </c>
       <c r="B439" s="2">
@@ -12122,7 +12122,7 @@
     </row>
     <row r="440" spans="1:6">
       <c r="A440" s="2">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>1202266</v>
       </c>
       <c r="B440" s="2">
@@ -12143,7 +12143,7 @@
     </row>
     <row r="441" spans="1:6">
       <c r="A441" s="2">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>1202267</v>
       </c>
       <c r="B441" s="2">
@@ -12164,7 +12164,7 @@
     </row>
     <row r="442" spans="1:6">
       <c r="A442" s="2">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>1202268</v>
       </c>
       <c r="B442" s="2">
@@ -12185,7 +12185,7 @@
     </row>
     <row r="443" spans="1:6">
       <c r="A443" s="2">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>1202269</v>
       </c>
       <c r="B443" s="2">
@@ -12206,7 +12206,7 @@
     </row>
     <row r="444" spans="1:6">
       <c r="A444" s="2">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>1202270</v>
       </c>
       <c r="B444" s="2">
@@ -12227,7 +12227,7 @@
     </row>
     <row r="445" spans="1:6">
       <c r="A445" s="2">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>1202271</v>
       </c>
       <c r="B445" s="2">
@@ -12248,7 +12248,7 @@
     </row>
     <row r="446" spans="1:6">
       <c r="A446" s="2">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>1202272</v>
       </c>
       <c r="B446" s="2">
@@ -12269,7 +12269,7 @@
     </row>
     <row r="447" spans="1:6">
       <c r="A447" s="2">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>1202273</v>
       </c>
       <c r="B447" s="2">
@@ -12290,7 +12290,7 @@
     </row>
     <row r="448" spans="1:6">
       <c r="A448" s="2">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>1202274</v>
       </c>
       <c r="B448" s="2">
@@ -12311,7 +12311,7 @@
     </row>
     <row r="449" spans="1:6">
       <c r="A449" s="2">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>1202275</v>
       </c>
       <c r="B449" s="2">
@@ -12332,7 +12332,7 @@
     </row>
     <row r="450" spans="1:6">
       <c r="A450" s="2">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>1202276</v>
       </c>
       <c r="B450" s="2">
@@ -12353,7 +12353,7 @@
     </row>
     <row r="451" spans="1:6">
       <c r="A451" s="2">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>1202277</v>
       </c>
       <c r="B451" s="2">
@@ -12374,7 +12374,7 @@
     </row>
     <row r="452" spans="1:6">
       <c r="A452" s="2">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>1202278</v>
       </c>
       <c r="B452" s="2">
@@ -12395,7 +12395,7 @@
     </row>
     <row r="453" spans="1:6">
       <c r="A453" s="2">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>1202279</v>
       </c>
       <c r="B453" s="2">
@@ -12416,7 +12416,7 @@
     </row>
     <row r="454" spans="1:6">
       <c r="A454" s="2">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>1202280</v>
       </c>
       <c r="B454" s="2">
@@ -12437,7 +12437,7 @@
     </row>
     <row r="455" s="3" customFormat="1" spans="1:6">
       <c r="A455" s="3">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>1202281</v>
       </c>
       <c r="B455" s="3">
@@ -12458,7 +12458,7 @@
     </row>
     <row r="456" spans="1:6">
       <c r="A456" s="2">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>1202282</v>
       </c>
       <c r="B456" s="2">
@@ -12479,7 +12479,7 @@
     </row>
     <row r="457" spans="1:6">
       <c r="A457" s="2">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>1202283</v>
       </c>
       <c r="B457" s="2">
@@ -12500,7 +12500,7 @@
     </row>
     <row r="458" spans="1:6">
       <c r="A458" s="2">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>1202284</v>
       </c>
       <c r="B458" s="2">
@@ -12521,7 +12521,7 @@
     </row>
     <row r="459" spans="1:6">
       <c r="A459" s="2">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>1202285</v>
       </c>
       <c r="B459" s="2">
@@ -12542,7 +12542,7 @@
     </row>
     <row r="460" spans="1:6">
       <c r="A460" s="2">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>1202286</v>
       </c>
       <c r="B460" s="2">
@@ -12563,7 +12563,7 @@
     </row>
     <row r="461" spans="1:6">
       <c r="A461" s="2">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>1202287</v>
       </c>
       <c r="B461" s="2">
@@ -12584,7 +12584,7 @@
     </row>
     <row r="462" spans="1:6">
       <c r="A462" s="2">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>1202288</v>
       </c>
       <c r="B462" s="2">
@@ -12605,7 +12605,7 @@
     </row>
     <row r="463" spans="1:6">
       <c r="A463" s="2">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>1202289</v>
       </c>
       <c r="B463" s="2">
@@ -12626,7 +12626,7 @@
     </row>
     <row r="464" spans="1:6">
       <c r="A464" s="2">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>1202290</v>
       </c>
       <c r="B464" s="2">
@@ -12647,7 +12647,7 @@
     </row>
     <row r="465" spans="1:6">
       <c r="A465" s="2">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>1202291</v>
       </c>
       <c r="B465" s="2">
@@ -12668,7 +12668,7 @@
     </row>
     <row r="466" spans="1:6">
       <c r="A466" s="2">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>1202292</v>
       </c>
       <c r="B466" s="2">
@@ -12689,7 +12689,7 @@
     </row>
     <row r="467" spans="1:6">
       <c r="A467" s="2">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>1202293</v>
       </c>
       <c r="B467" s="2">
@@ -12710,7 +12710,7 @@
     </row>
     <row r="468" spans="1:6">
       <c r="A468" s="2">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>1202294</v>
       </c>
       <c r="B468" s="2">
@@ -12731,7 +12731,7 @@
     </row>
     <row r="469" spans="1:6">
       <c r="A469" s="2">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>1202295</v>
       </c>
       <c r="B469" s="2">
@@ -12752,7 +12752,7 @@
     </row>
     <row r="470" spans="1:6">
       <c r="A470" s="2">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>1202296</v>
       </c>
       <c r="B470" s="2">
@@ -12773,7 +12773,7 @@
     </row>
     <row r="471" spans="1:6">
       <c r="A471" s="2">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>1202297</v>
       </c>
       <c r="B471" s="2">
@@ -12794,7 +12794,7 @@
     </row>
     <row r="472" spans="1:6">
       <c r="A472" s="2">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>1202298</v>
       </c>
       <c r="B472" s="2">
@@ -12815,7 +12815,7 @@
     </row>
     <row r="473" spans="1:6">
       <c r="A473" s="2">
-        <f t="shared" ref="A473:A481" si="26">D473*1000+B473*100+C473</f>
+        <f t="shared" ref="A473:A482" si="28">D473*1000+B473*100+C473</f>
         <v>1202299</v>
       </c>
       <c r="B473" s="2">
@@ -12836,7 +12836,7 @@
     </row>
     <row r="474" spans="1:6">
       <c r="A474" s="2">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>1202300</v>
       </c>
       <c r="B474" s="2">
@@ -12857,7 +12857,7 @@
     </row>
     <row r="475" spans="1:6">
       <c r="A475" s="2">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>1202301</v>
       </c>
       <c r="B475" s="2">
@@ -12878,7 +12878,7 @@
     </row>
     <row r="476" spans="1:6">
       <c r="A476" s="2">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>1202302</v>
       </c>
       <c r="B476" s="2">
@@ -12899,7 +12899,7 @@
     </row>
     <row r="477" spans="1:6">
       <c r="A477" s="2">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>1202303</v>
       </c>
       <c r="B477" s="2">
@@ -12920,7 +12920,7 @@
     </row>
     <row r="478" spans="1:6">
       <c r="A478" s="2">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>1202304</v>
       </c>
       <c r="B478" s="2">
@@ -12941,7 +12941,7 @@
     </row>
     <row r="479" spans="1:6">
       <c r="A479" s="2">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>1202305</v>
       </c>
       <c r="B479" s="2">
@@ -12962,7 +12962,7 @@
     </row>
     <row r="480" spans="1:6">
       <c r="A480" s="2">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>1202306</v>
       </c>
       <c r="B480" s="2">
@@ -12983,7 +12983,7 @@
     </row>
     <row r="481" spans="1:6">
       <c r="A481" s="2">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>1202307</v>
       </c>
       <c r="B481" s="2">
@@ -13025,7 +13025,7 @@
     </row>
     <row r="483" spans="1:6">
       <c r="A483" s="2">
-        <f t="shared" ref="A483:A491" si="27">D483*1000+B483*100+C483</f>
+        <f t="shared" ref="A483:A492" si="29">D483*1000+B483*100+C483</f>
         <v>1301252</v>
       </c>
       <c r="B483" s="2">
@@ -13046,7 +13046,7 @@
     </row>
     <row r="484" spans="1:6">
       <c r="A484" s="2">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>1301253</v>
       </c>
       <c r="B484" s="2">
@@ -13067,7 +13067,7 @@
     </row>
     <row r="485" spans="1:6">
       <c r="A485" s="2">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>1301254</v>
       </c>
       <c r="B485" s="2">
@@ -13088,7 +13088,7 @@
     </row>
     <row r="486" spans="1:6">
       <c r="A486" s="2">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>1301255</v>
       </c>
       <c r="B486" s="2">
@@ -13109,7 +13109,7 @@
     </row>
     <row r="487" spans="1:6">
       <c r="A487" s="2">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>1301256</v>
       </c>
       <c r="B487" s="2">
@@ -13130,7 +13130,7 @@
     </row>
     <row r="488" spans="1:6">
       <c r="A488" s="2">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>1301257</v>
       </c>
       <c r="B488" s="2">
@@ -13151,7 +13151,7 @@
     </row>
     <row r="489" spans="1:6">
       <c r="A489" s="2">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>1301258</v>
       </c>
       <c r="B489" s="2">
@@ -13172,7 +13172,7 @@
     </row>
     <row r="490" spans="1:6">
       <c r="A490" s="2">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>1301259</v>
       </c>
       <c r="B490" s="2">
@@ -13193,7 +13193,7 @@
     </row>
     <row r="491" spans="1:6">
       <c r="A491" s="2">
-        <f>D491*1000+B491*100+C491</f>
+        <f t="shared" si="29"/>
         <v>1301260</v>
       </c>
       <c r="B491" s="2">
@@ -13214,7 +13214,7 @@
     </row>
     <row r="492" spans="1:6">
       <c r="A492" s="5">
-        <f>D492*1000+B492*100+C492</f>
+        <f t="shared" si="29"/>
         <v>1303251</v>
       </c>
       <c r="B492" s="5">
@@ -13235,7 +13235,7 @@
     </row>
     <row r="493" spans="1:6">
       <c r="A493" s="5">
-        <f t="shared" ref="A493:A503" si="28">D493*1000+B493*100+C493</f>
+        <f t="shared" ref="A493:A503" si="30">D493*1000+B493*100+C493</f>
         <v>1303252</v>
       </c>
       <c r="B493" s="5">
@@ -13256,7 +13256,7 @@
     </row>
     <row r="494" spans="1:6">
       <c r="A494" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>1303253</v>
       </c>
       <c r="B494" s="5">
@@ -13277,7 +13277,7 @@
     </row>
     <row r="495" spans="1:6">
       <c r="A495" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>1303254</v>
       </c>
       <c r="B495" s="5">
@@ -13298,7 +13298,7 @@
     </row>
     <row r="496" spans="1:6">
       <c r="A496" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>1303255</v>
       </c>
       <c r="B496" s="5">
@@ -13319,7 +13319,7 @@
     </row>
     <row r="497" spans="1:6">
       <c r="A497" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>1303256</v>
       </c>
       <c r="B497" s="5">
@@ -13340,7 +13340,7 @@
     </row>
     <row r="498" spans="1:6">
       <c r="A498" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>1303257</v>
       </c>
       <c r="B498" s="5">
@@ -13361,7 +13361,7 @@
     </row>
     <row r="499" spans="1:6">
       <c r="A499" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>1303258</v>
       </c>
       <c r="B499" s="5">
@@ -13382,7 +13382,7 @@
     </row>
     <row r="500" spans="1:6">
       <c r="A500" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>1303259</v>
       </c>
       <c r="B500" s="5">
@@ -13403,7 +13403,7 @@
     </row>
     <row r="501" spans="1:6">
       <c r="A501" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>1303260</v>
       </c>
       <c r="B501" s="5">
@@ -13424,7 +13424,7 @@
     </row>
     <row r="502" spans="1:6">
       <c r="A502" s="2">
-        <f>D502*1000+B502*100+C502</f>
+        <f t="shared" si="30"/>
         <v>1304251</v>
       </c>
       <c r="B502" s="2">
@@ -13445,7 +13445,7 @@
     </row>
     <row r="503" spans="1:6">
       <c r="A503" s="2">
-        <f t="shared" ref="A503:A510" si="29">D503*1000+B503*100+C503</f>
+        <f t="shared" ref="A503:A510" si="31">D503*1000+B503*100+C503</f>
         <v>1304252</v>
       </c>
       <c r="B503" s="2">
@@ -13466,7 +13466,7 @@
     </row>
     <row r="504" spans="1:6">
       <c r="A504" s="2">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>1304253</v>
       </c>
       <c r="B504" s="2">
@@ -13487,7 +13487,7 @@
     </row>
     <row r="505" spans="1:6">
       <c r="A505" s="2">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>1304254</v>
       </c>
       <c r="B505" s="2">
@@ -13508,7 +13508,7 @@
     </row>
     <row r="506" spans="1:6">
       <c r="A506" s="2">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>1304255</v>
       </c>
       <c r="B506" s="2">
@@ -13529,7 +13529,7 @@
     </row>
     <row r="507" spans="1:6">
       <c r="A507" s="2">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>1304256</v>
       </c>
       <c r="B507" s="2">
@@ -13550,7 +13550,7 @@
     </row>
     <row r="508" spans="1:6">
       <c r="A508" s="2">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>1304257</v>
       </c>
       <c r="B508" s="2">
@@ -13571,7 +13571,7 @@
     </row>
     <row r="509" spans="1:6">
       <c r="A509" s="2">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>1304258</v>
       </c>
       <c r="B509" s="2">

--- a/hall/resources/sample/BuildingEquipmentTable.xlsx
+++ b/hall/resources/sample/BuildingEquipmentTable.xlsx
@@ -132,7 +132,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1575" uniqueCount="157">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1583" uniqueCount="161">
   <si>
     <t>ID</t>
   </si>
@@ -597,6 +597,18 @@
   </si>
   <si>
     <t>装饰10</t>
+  </si>
+  <si>
+    <t>装饰11</t>
+  </si>
+  <si>
+    <t>装饰12</t>
+  </si>
+  <si>
+    <t>装饰13</t>
+  </si>
+  <si>
+    <t>装饰14</t>
   </si>
   <si>
     <t>运营部</t>
@@ -1812,7 +1824,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G563"/>
+  <dimension ref="A1:G567"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" outlineLevelCol="6"/>
   <cols>
     <col min="1" max="4" width="18.375" style="2" customWidth="1"/>
@@ -4445,7 +4457,7 @@
     </row>
     <row r="112" spans="1:7">
       <c r="A112" s="2">
-        <f t="shared" ref="A112:A132" si="7">D112*1000+B112*100+C112</f>
+        <f t="shared" ref="A112:A134" si="7">D112*1000+B112*100+C112</f>
         <v>1102277</v>
       </c>
       <c r="B112" s="2">
@@ -4949,7 +4961,7 @@
     </row>
     <row r="133" spans="1:7">
       <c r="A133" s="2">
-        <f>D133*1000+B133*100+C133</f>
+        <f t="shared" si="7"/>
         <v>1102298</v>
       </c>
       <c r="B133" s="2">
@@ -4973,7 +4985,7 @@
     </row>
     <row r="134" spans="1:7">
       <c r="A134" s="2">
-        <f>D134*1000+B134*100+C134</f>
+        <f t="shared" si="7"/>
         <v>1102299</v>
       </c>
       <c r="B134" s="2">
@@ -14563,381 +14575,465 @@
       </c>
     </row>
     <row r="546" spans="1:6">
-      <c r="A546" s="6">
-        <f t="shared" si="33"/>
-        <v>1303251</v>
-      </c>
-      <c r="B546" s="6">
-        <v>2</v>
-      </c>
-      <c r="C546" s="6">
-        <v>51</v>
-      </c>
-      <c r="D546" s="6">
-        <v>1303</v>
-      </c>
-      <c r="E546" s="6" t="s">
-        <v>144</v>
-      </c>
-      <c r="F546" s="6" t="s">
+      <c r="A546" s="2">
+        <f>D546*1000+B546*100+C546</f>
+        <v>1301261</v>
+      </c>
+      <c r="B546" s="2">
+        <v>2</v>
+      </c>
+      <c r="C546" s="2">
+        <v>61</v>
+      </c>
+      <c r="D546" s="2">
+        <v>1301</v>
+      </c>
+      <c r="E546" s="2" t="s">
         <v>155</v>
       </c>
+      <c r="F546" s="2" t="s">
+        <v>145</v>
+      </c>
     </row>
     <row r="547" spans="1:6">
-      <c r="A547" s="6">
-        <f t="shared" ref="A547:A557" si="34">D547*1000+B547*100+C547</f>
-        <v>1303252</v>
-      </c>
-      <c r="B547" s="6">
-        <v>2</v>
-      </c>
-      <c r="C547" s="6">
-        <v>52</v>
-      </c>
-      <c r="D547" s="6">
-        <v>1303</v>
-      </c>
-      <c r="E547" s="6" t="s">
-        <v>146</v>
-      </c>
-      <c r="F547" s="6" t="s">
-        <v>155</v>
+      <c r="A547" s="2">
+        <f>D547*1000+B547*100+C547</f>
+        <v>1301262</v>
+      </c>
+      <c r="B547" s="2">
+        <v>2</v>
+      </c>
+      <c r="C547" s="2">
+        <v>62</v>
+      </c>
+      <c r="D547" s="2">
+        <v>1301</v>
+      </c>
+      <c r="E547" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="F547" s="2" t="s">
+        <v>145</v>
       </c>
     </row>
     <row r="548" spans="1:6">
-      <c r="A548" s="6">
-        <f t="shared" si="34"/>
-        <v>1303253</v>
-      </c>
-      <c r="B548" s="6">
-        <v>2</v>
-      </c>
-      <c r="C548" s="6">
-        <v>53</v>
-      </c>
-      <c r="D548" s="6">
-        <v>1303</v>
-      </c>
-      <c r="E548" s="6" t="s">
-        <v>147</v>
-      </c>
-      <c r="F548" s="6" t="s">
-        <v>155</v>
+      <c r="A548" s="2">
+        <f>D548*1000+B548*100+C548</f>
+        <v>1301263</v>
+      </c>
+      <c r="B548" s="2">
+        <v>2</v>
+      </c>
+      <c r="C548" s="2">
+        <v>63</v>
+      </c>
+      <c r="D548" s="2">
+        <v>1301</v>
+      </c>
+      <c r="E548" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="F548" s="2" t="s">
+        <v>145</v>
       </c>
     </row>
     <row r="549" spans="1:6">
-      <c r="A549" s="6">
-        <f t="shared" si="34"/>
-        <v>1303254</v>
-      </c>
-      <c r="B549" s="6">
-        <v>2</v>
-      </c>
-      <c r="C549" s="6">
-        <v>54</v>
-      </c>
-      <c r="D549" s="6">
-        <v>1303</v>
-      </c>
-      <c r="E549" s="6" t="s">
-        <v>148</v>
-      </c>
-      <c r="F549" s="6" t="s">
-        <v>155</v>
+      <c r="A549" s="2">
+        <f>D549*1000+B549*100+C549</f>
+        <v>1301264</v>
+      </c>
+      <c r="B549" s="2">
+        <v>2</v>
+      </c>
+      <c r="C549" s="2">
+        <v>64</v>
+      </c>
+      <c r="D549" s="2">
+        <v>1301</v>
+      </c>
+      <c r="E549" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="F549" s="2" t="s">
+        <v>145</v>
       </c>
     </row>
     <row r="550" spans="1:6">
       <c r="A550" s="6">
-        <f t="shared" si="34"/>
-        <v>1303255</v>
+        <f>D550*1000+B550*100+C550</f>
+        <v>1303251</v>
       </c>
       <c r="B550" s="6">
         <v>2</v>
       </c>
       <c r="C550" s="6">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="D550" s="6">
         <v>1303</v>
       </c>
       <c r="E550" s="6" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="F550" s="6" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
     </row>
     <row r="551" spans="1:6">
       <c r="A551" s="6">
-        <f t="shared" si="34"/>
-        <v>1303256</v>
+        <f t="shared" ref="A551:A561" si="34">D551*1000+B551*100+C551</f>
+        <v>1303252</v>
       </c>
       <c r="B551" s="6">
         <v>2</v>
       </c>
       <c r="C551" s="6">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="D551" s="6">
         <v>1303</v>
       </c>
       <c r="E551" s="6" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="F551" s="6" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
     </row>
     <row r="552" spans="1:6">
       <c r="A552" s="6">
         <f t="shared" si="34"/>
-        <v>1303257</v>
+        <v>1303253</v>
       </c>
       <c r="B552" s="6">
         <v>2</v>
       </c>
       <c r="C552" s="6">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="D552" s="6">
         <v>1303</v>
       </c>
       <c r="E552" s="6" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="F552" s="6" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
     </row>
     <row r="553" spans="1:6">
       <c r="A553" s="6">
         <f t="shared" si="34"/>
-        <v>1303258</v>
+        <v>1303254</v>
       </c>
       <c r="B553" s="6">
         <v>2</v>
       </c>
       <c r="C553" s="6">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D553" s="6">
         <v>1303</v>
       </c>
       <c r="E553" s="6" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="F553" s="6" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
     </row>
     <row r="554" spans="1:6">
       <c r="A554" s="6">
         <f t="shared" si="34"/>
-        <v>1303259</v>
+        <v>1303255</v>
       </c>
       <c r="B554" s="6">
         <v>2</v>
       </c>
       <c r="C554" s="6">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="D554" s="6">
         <v>1303</v>
       </c>
       <c r="E554" s="6" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="F554" s="6" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
     </row>
     <row r="555" spans="1:6">
       <c r="A555" s="6">
         <f t="shared" si="34"/>
-        <v>1303260</v>
+        <v>1303256</v>
       </c>
       <c r="B555" s="6">
         <v>2</v>
       </c>
       <c r="C555" s="6">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="D555" s="6">
         <v>1303</v>
       </c>
       <c r="E555" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="F555" s="6" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="556" spans="1:6">
+      <c r="A556" s="6">
+        <f t="shared" si="34"/>
+        <v>1303257</v>
+      </c>
+      <c r="B556" s="6">
+        <v>2</v>
+      </c>
+      <c r="C556" s="6">
+        <v>57</v>
+      </c>
+      <c r="D556" s="6">
+        <v>1303</v>
+      </c>
+      <c r="E556" s="6" t="s">
+        <v>151</v>
+      </c>
+      <c r="F556" s="6" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="557" spans="1:6">
+      <c r="A557" s="6">
+        <f t="shared" si="34"/>
+        <v>1303258</v>
+      </c>
+      <c r="B557" s="6">
+        <v>2</v>
+      </c>
+      <c r="C557" s="6">
+        <v>58</v>
+      </c>
+      <c r="D557" s="6">
+        <v>1303</v>
+      </c>
+      <c r="E557" s="6" t="s">
+        <v>152</v>
+      </c>
+      <c r="F557" s="6" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="558" spans="1:6">
+      <c r="A558" s="6">
+        <f t="shared" si="34"/>
+        <v>1303259</v>
+      </c>
+      <c r="B558" s="6">
+        <v>2</v>
+      </c>
+      <c r="C558" s="6">
+        <v>59</v>
+      </c>
+      <c r="D558" s="6">
+        <v>1303</v>
+      </c>
+      <c r="E558" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="F558" s="6" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="559" spans="1:6">
+      <c r="A559" s="6">
+        <f t="shared" si="34"/>
+        <v>1303260</v>
+      </c>
+      <c r="B559" s="6">
+        <v>2</v>
+      </c>
+      <c r="C559" s="6">
+        <v>60</v>
+      </c>
+      <c r="D559" s="6">
+        <v>1303</v>
+      </c>
+      <c r="E559" s="6" t="s">
         <v>154</v>
       </c>
-      <c r="F555" s="6" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="556" spans="1:6">
-      <c r="A556" s="2">
+      <c r="F559" s="6" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="560" spans="1:6">
+      <c r="A560" s="2">
         <f t="shared" si="34"/>
         <v>1304251</v>
       </c>
-      <c r="B556" s="2">
-        <v>2</v>
-      </c>
-      <c r="C556" s="2">
+      <c r="B560" s="2">
+        <v>2</v>
+      </c>
+      <c r="C560" s="2">
         <v>51</v>
-      </c>
-      <c r="D556" s="2">
-        <v>1304</v>
-      </c>
-      <c r="E556" s="2" t="s">
-        <v>144</v>
-      </c>
-      <c r="F556" s="2" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="557" spans="1:6">
-      <c r="A557" s="2">
-        <f t="shared" ref="A557:A564" si="35">D557*1000+B557*100+C557</f>
-        <v>1304252</v>
-      </c>
-      <c r="B557" s="2">
-        <v>2</v>
-      </c>
-      <c r="C557" s="2">
-        <v>52</v>
-      </c>
-      <c r="D557" s="2">
-        <v>1304</v>
-      </c>
-      <c r="E557" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="F557" s="2" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="558" spans="1:6">
-      <c r="A558" s="2">
-        <f t="shared" si="35"/>
-        <v>1304253</v>
-      </c>
-      <c r="B558" s="2">
-        <v>2</v>
-      </c>
-      <c r="C558" s="2">
-        <v>53</v>
-      </c>
-      <c r="D558" s="2">
-        <v>1304</v>
-      </c>
-      <c r="E558" s="2" t="s">
-        <v>147</v>
-      </c>
-      <c r="F558" s="2" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="559" spans="1:6">
-      <c r="A559" s="2">
-        <f t="shared" si="35"/>
-        <v>1304254</v>
-      </c>
-      <c r="B559" s="2">
-        <v>2</v>
-      </c>
-      <c r="C559" s="2">
-        <v>54</v>
-      </c>
-      <c r="D559" s="2">
-        <v>1304</v>
-      </c>
-      <c r="E559" s="2" t="s">
-        <v>148</v>
-      </c>
-      <c r="F559" s="2" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="560" spans="1:6">
-      <c r="A560" s="2">
-        <f t="shared" si="35"/>
-        <v>1304255</v>
-      </c>
-      <c r="B560" s="2">
-        <v>2</v>
-      </c>
-      <c r="C560" s="2">
-        <v>55</v>
       </c>
       <c r="D560" s="2">
         <v>1304</v>
       </c>
       <c r="E560" s="2" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="F560" s="2" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
     </row>
     <row r="561" spans="1:6">
       <c r="A561" s="2">
-        <f t="shared" si="35"/>
-        <v>1304256</v>
+        <f t="shared" ref="A561:A568" si="35">D561*1000+B561*100+C561</f>
+        <v>1304252</v>
       </c>
       <c r="B561" s="2">
         <v>2</v>
       </c>
       <c r="C561" s="2">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="D561" s="2">
         <v>1304</v>
       </c>
       <c r="E561" s="2" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="F561" s="2" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
     </row>
     <row r="562" spans="1:6">
       <c r="A562" s="2">
         <f t="shared" si="35"/>
-        <v>1304257</v>
+        <v>1304253</v>
       </c>
       <c r="B562" s="2">
         <v>2</v>
       </c>
       <c r="C562" s="2">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="D562" s="2">
         <v>1304</v>
       </c>
       <c r="E562" s="2" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="F562" s="2" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
     </row>
     <row r="563" spans="1:6">
       <c r="A563" s="2">
         <f t="shared" si="35"/>
-        <v>1304258</v>
+        <v>1304254</v>
       </c>
       <c r="B563" s="2">
         <v>2</v>
       </c>
       <c r="C563" s="2">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D563" s="2">
         <v>1304</v>
       </c>
       <c r="E563" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="F563" s="2" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="564" spans="1:6">
+      <c r="A564" s="2">
+        <f t="shared" si="35"/>
+        <v>1304255</v>
+      </c>
+      <c r="B564" s="2">
+        <v>2</v>
+      </c>
+      <c r="C564" s="2">
+        <v>55</v>
+      </c>
+      <c r="D564" s="2">
+        <v>1304</v>
+      </c>
+      <c r="E564" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="F564" s="2" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="565" spans="1:6">
+      <c r="A565" s="2">
+        <f t="shared" si="35"/>
+        <v>1304256</v>
+      </c>
+      <c r="B565" s="2">
+        <v>2</v>
+      </c>
+      <c r="C565" s="2">
+        <v>56</v>
+      </c>
+      <c r="D565" s="2">
+        <v>1304</v>
+      </c>
+      <c r="E565" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="F565" s="2" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="566" spans="1:6">
+      <c r="A566" s="2">
+        <f t="shared" si="35"/>
+        <v>1304257</v>
+      </c>
+      <c r="B566" s="2">
+        <v>2</v>
+      </c>
+      <c r="C566" s="2">
+        <v>57</v>
+      </c>
+      <c r="D566" s="2">
+        <v>1304</v>
+      </c>
+      <c r="E566" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="F566" s="2" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="567" spans="1:6">
+      <c r="A567" s="2">
+        <f t="shared" si="35"/>
+        <v>1304258</v>
+      </c>
+      <c r="B567" s="2">
+        <v>2</v>
+      </c>
+      <c r="C567" s="2">
+        <v>58</v>
+      </c>
+      <c r="D567" s="2">
+        <v>1304</v>
+      </c>
+      <c r="E567" s="2" t="s">
         <v>152</v>
       </c>
-      <c r="F563" s="2" t="s">
-        <v>156</v>
+      <c r="F567" s="2" t="s">
+        <v>160</v>
       </c>
     </row>
   </sheetData>
